--- a/evd_event_id_crosswalk_mapped.xlsx
+++ b/evd_event_id_crosswalk_mapped.xlsx
@@ -2285,6 +2285,9 @@
           <t>3233867</t>
         </is>
       </c>
+      <c r="T15" t="n">
+        <v>1335574</v>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>17956743</t>
@@ -2307,15 +2310,15 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB15" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date</t>
+          <t>aq_hub_opponent_date+gotickets_catalog_7d_pull</t>
         </is>
       </c>
     </row>
@@ -14448,6 +14451,9 @@
           <t>VZ3WVYX</t>
         </is>
       </c>
+      <c r="T138" t="n">
+        <v>1377027</v>
+      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>18033282</t>
@@ -14470,15 +14476,15 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB138" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date</t>
+          <t>aq_hub_opponent_date+gotickets_catalog_7d_pull</t>
         </is>
       </c>
     </row>
@@ -16414,13 +16420,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
         <v>145</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>0.1034</v>
+        <v>0.1172</v>
       </c>
     </row>
     <row r="4">

--- a/evd_event_id_crosswalk_mapped.xlsx
+++ b/evd_event_id_crosswalk_mapped.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC146"/>
+  <dimension ref="A1:AB146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -687,18 +687,17 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="19" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
     <col width="19" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
-    <col width="23" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -789,60 +788,55 @@
       </c>
       <c r="R1" s="11" t="inlineStr">
         <is>
-          <t>aq_short_event_id</t>
+          <t>tevo_event_id</t>
         </is>
       </c>
       <c r="S1" s="11" t="inlineStr">
         <is>
-          <t>tevo_event_id</t>
+          <t>gotickets_event_id</t>
         </is>
       </c>
       <c r="T1" s="11" t="inlineStr">
         <is>
-          <t>gotickets_event_id</t>
+          <t>seatgeek_event_id</t>
         </is>
       </c>
       <c r="U1" s="11" t="inlineStr">
         <is>
-          <t>seatgeek_event_id</t>
+          <t>stubhub_event_id</t>
         </is>
       </c>
       <c r="V1" s="11" t="inlineStr">
         <is>
-          <t>stubhub_event_id</t>
+          <t>vividseats_event_id</t>
         </is>
       </c>
       <c r="W1" s="11" t="inlineStr">
         <is>
-          <t>vividseats_event_id</t>
+          <t>tickpick_event_id</t>
         </is>
       </c>
       <c r="X1" s="11" t="inlineStr">
         <is>
-          <t>tickpick_event_id</t>
+          <t>gametime_event_id</t>
         </is>
       </c>
       <c r="Y1" s="11" t="inlineStr">
         <is>
-          <t>gametime_event_id</t>
+          <t>ticketmaster_event_id</t>
         </is>
       </c>
       <c r="Z1" s="11" t="inlineStr">
         <is>
-          <t>ticketmaster_event_id</t>
+          <t>sources_mapped</t>
         </is>
       </c>
       <c r="AA1" s="11" t="inlineStr">
         <is>
-          <t>sources_mapped</t>
+          <t>sources_mapped_count</t>
         </is>
       </c>
       <c r="AB1" s="11" t="inlineStr">
-        <is>
-          <t>sources_mapped_count</t>
-        </is>
-      </c>
-      <c r="AC1" s="11" t="inlineStr">
         <is>
           <t>match_method</t>
         </is>
@@ -928,22 +922,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1629863</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB2" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S2" t="n">
+        <v>1629863</v>
+      </c>
+      <c r="T2" t="n">
+        <v>18126596</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6288282</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA2" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1025,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T3" t="n">
+        <v>17965064</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6205721</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -1116,40 +1125,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>NZ59BD2</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>18024316</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>160324613</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>6185528</t>
-        </is>
+      <c r="T4" t="n">
+        <v>18024316</v>
+      </c>
+      <c r="U4" t="n">
+        <v>160324613</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6185528</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4827175</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4827175</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB4" s="12" t="n">
+      <c r="AA4" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -1235,12 +1231,26 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T5" t="n">
+        <v>17986058</v>
+      </c>
+      <c r="U5" t="n">
+        <v>159478580</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6178998</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA5" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -1324,40 +1334,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>BP3KYOD</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>17936149</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>160228320</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>6206351</t>
-        </is>
+      <c r="T6" t="n">
+        <v>17936149</v>
+      </c>
+      <c r="U6" t="n">
+        <v>160228320</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6206351</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4785738</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4785738</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB6" s="12" t="n">
+      <c r="AA6" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -1443,35 +1440,24 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Y5YDMDN</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>17997465</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>159927981</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>6207016</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="T7" t="n">
+        <v>17997465</v>
+      </c>
+      <c r="U7" t="n">
+        <v>159927981</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6207016</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AB7" s="12" t="n">
+      <c r="AA7" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -1557,40 +1543,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>36MJPMZ</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>17984356</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>159766135</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>6206530</t>
-        </is>
+      <c r="T8" t="n">
+        <v>17984356</v>
+      </c>
+      <c r="U8" t="n">
+        <v>159766135</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6206530</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4809738</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4809738</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB8" s="12" t="n">
+      <c r="AA8" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -1676,40 +1649,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>VYV5QZQ</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>18024460</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>160324181</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>6473651</t>
-        </is>
+      <c r="T9" t="n">
+        <v>18024460</v>
+      </c>
+      <c r="U9" t="n">
+        <v>160324181</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6473651</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>4835726</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4835726</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB9" s="12" t="n">
+      <c r="AA9" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -1795,45 +1755,30 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>5KNGB7G</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>3241022</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>17965050</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>159932593</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>6199860</t>
-        </is>
+      <c r="R10" t="n">
+        <v>3241022</v>
+      </c>
+      <c r="T10" t="n">
+        <v>17965050</v>
+      </c>
+      <c r="U10" t="n">
+        <v>159932593</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6199860</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4811641</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4811641</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB10" s="12" t="n">
+      <c r="AA10" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -1919,12 +1864,26 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="AB11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T11" t="n">
+        <v>18012988</v>
+      </c>
+      <c r="U11" t="n">
+        <v>160425521</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6498326</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA11" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -2008,12 +1967,26 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="AB12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T12" t="n">
+        <v>18028951</v>
+      </c>
+      <c r="U12" t="n">
+        <v>159955411</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6368029</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2070,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T13" t="n">
+        <v>18127621</v>
+      </c>
+      <c r="U13" t="n">
+        <v>160324460</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6482923</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA13" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2173,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T14" t="n">
+        <v>18024445</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6369854</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA14" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -2275,48 +2273,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>KBYGBV2</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>3233867</t>
-        </is>
+      <c r="R15" t="n">
+        <v>3233867</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1335574</v>
       </c>
       <c r="T15" t="n">
-        <v>1335574</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>17956743</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>160067992</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>6292262</t>
-        </is>
+        <v>17956743</v>
+      </c>
+      <c r="U15" t="n">
+        <v>160067992</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6292262</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4833758</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4833758</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
           <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB15" s="12" t="n">
+      <c r="AA15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date+gotickets_catalog_7d_pull</t>
         </is>
@@ -2402,12 +2385,26 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T16" t="n">
+        <v>17986060</v>
+      </c>
+      <c r="U16" t="n">
+        <v>160060118</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6178999</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA16" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2488,23 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T17" t="n">
+        <v>18150134</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6371814</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA17" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -2580,40 +2588,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>M7Y2QEO</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>18012530</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>160324269</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>6316172</t>
-        </is>
+      <c r="T18" t="n">
+        <v>18012530</v>
+      </c>
+      <c r="U18" t="n">
+        <v>160324269</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6316172</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>4826842</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4826842</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB18" s="12" t="n">
+      <c r="AA18" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -2699,40 +2694,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>ZQGPMJ7</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>17965046</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>160125590</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>6473725</t>
-        </is>
+      <c r="T19" t="n">
+        <v>17965046</v>
+      </c>
+      <c r="U19" t="n">
+        <v>160125590</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6473725</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>4767940</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4767940</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB19" s="12" t="n">
+      <c r="AA19" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -2818,40 +2800,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>WQKDXDJ</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>17997467</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>159927982</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>6207018</t>
-        </is>
+      <c r="T20" t="n">
+        <v>17997467</v>
+      </c>
+      <c r="U20" t="n">
+        <v>159927982</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6207018</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4768281</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4768281</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB20" s="12" t="n">
+      <c r="AA20" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -2937,40 +2906,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>7P7JGDD</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>17984355</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>159926164</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>6206529</t>
-        </is>
+      <c r="T21" t="n">
+        <v>17984355</v>
+      </c>
+      <c r="U21" t="n">
+        <v>159926164</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6206529</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4809739</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4809739</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB21" s="12" t="n">
+      <c r="AA21" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -3056,22 +3012,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1609722</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S22" t="n">
+        <v>1609722</v>
+      </c>
+      <c r="T22" t="n">
+        <v>18169350</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek</t>
+        </is>
+      </c>
+      <c r="AA22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -3155,40 +3112,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Z5AAAGX</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>18024476</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>160204370</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>6024630</t>
-        </is>
+      <c r="T23" t="n">
+        <v>18024476</v>
+      </c>
+      <c r="U23" t="n">
+        <v>160204370</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6024630</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>4827025</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4827025</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB23" s="12" t="n">
+      <c r="AA23" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -3274,45 +3218,30 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>6ZB34W4</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>3241020</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>17965052</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>160228473</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>6199861</t>
-        </is>
+      <c r="R24" t="n">
+        <v>3241020</v>
+      </c>
+      <c r="T24" t="n">
+        <v>17965052</v>
+      </c>
+      <c r="U24" t="n">
+        <v>160228473</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6199861</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>4811642</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>4811642</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB24" s="12" t="n">
+      <c r="AA24" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -3398,12 +3327,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T25" t="n">
+        <v>18094058</v>
+      </c>
+      <c r="U25" t="n">
+        <v>160201392</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6473150</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -3487,12 +3430,29 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T26" t="n">
+        <v>18077238</v>
+      </c>
+      <c r="U26" t="n">
+        <v>159997366</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6205546</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.305954083573142e+18</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AA26" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3536,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T27" t="n">
+        <v>18028953</v>
+      </c>
+      <c r="U27" t="n">
+        <v>159955419</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6368033</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA27" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3639,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T28" t="n">
+        <v>17971632</v>
+      </c>
+      <c r="U28" t="n">
+        <v>160109236</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6429659</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA28" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3742,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T29" t="n">
+        <v>18147714</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6802467</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA29" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -3843,45 +3842,30 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>MK5O4ZM</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>3231484</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>17936235</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>159927900</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>6169427</t>
-        </is>
+      <c r="R30" t="n">
+        <v>3231484</v>
+      </c>
+      <c r="T30" t="n">
+        <v>17936235</v>
+      </c>
+      <c r="U30" t="n">
+        <v>159927900</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6169427</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>4772196</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4772196</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB30" s="12" t="n">
+      <c r="AA30" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -3967,45 +3951,30 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>4B67WQJ</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>3241019</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>18033318</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>159996524</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>6206978</t>
-        </is>
+      <c r="R31" t="n">
+        <v>3241019</v>
+      </c>
+      <c r="T31" t="n">
+        <v>18033318</v>
+      </c>
+      <c r="U31" t="n">
+        <v>159996524</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6206978</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>4834989</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4834989</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB31" s="12" t="n">
+      <c r="AA31" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -4091,20 +4060,18 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>18033447</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
+      <c r="T32" t="n">
+        <v>18033447</v>
+      </c>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>SeatGeek</t>
         </is>
       </c>
-      <c r="AB32" s="12" t="n">
+      <c r="AA32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>sg_canonical_opponent_date</t>
         </is>
@@ -4190,17 +4157,26 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>SYS-cbc4849cee</t>
-        </is>
-      </c>
-      <c r="AB33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+      <c r="T33" t="n">
+        <v>17986062</v>
+      </c>
+      <c r="U33" t="n">
+        <v>160060119</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6179000</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA33" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -4284,40 +4260,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>WQ3ZMN6</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>17984354</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>159926163</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>6206528</t>
-        </is>
+      <c r="T34" t="n">
+        <v>17984354</v>
+      </c>
+      <c r="U34" t="n">
+        <v>159926163</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6206528</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>4809740</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>4809740</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB34" s="12" t="n">
+      <c r="AA34" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -4399,12 +4362,29 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>not_a_game_field_pass</t>
+      <c r="T35" t="n">
+        <v>17984354</v>
+      </c>
+      <c r="U35" t="n">
+        <v>159926163</v>
+      </c>
+      <c r="V35" t="n">
+        <v>6206528</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>4809740</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AA35" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>addon_parent_game(126:F26:03)</t>
         </is>
       </c>
     </row>
@@ -4488,40 +4468,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>PGOO239</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>18035333</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>159927978</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>6205008</t>
-        </is>
+      <c r="T36" t="n">
+        <v>18035333</v>
+      </c>
+      <c r="U36" t="n">
+        <v>159927978</v>
+      </c>
+      <c r="V36" t="n">
+        <v>6205008</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>4768250</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>4768250</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB36" s="12" t="n">
+      <c r="AA36" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -4607,35 +4574,24 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>34MYQZZ</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>18024478</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>160204385</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>6303970</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
+      <c r="T37" t="n">
+        <v>18024478</v>
+      </c>
+      <c r="U37" t="n">
+        <v>160204385</v>
+      </c>
+      <c r="V37" t="n">
+        <v>6303970</v>
+      </c>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AB37" s="12" t="n">
+      <c r="AA37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -4721,12 +4677,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T38" t="n">
+        <v>18176904</v>
+      </c>
+      <c r="U38" t="n">
+        <v>160379439</v>
+      </c>
+      <c r="V38" t="n">
+        <v>6482925</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA38" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -4810,20 +4780,18 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>18147716</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
+      <c r="T39" t="n">
+        <v>18147716</v>
+      </c>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>SeatGeek</t>
         </is>
       </c>
-      <c r="AB39" s="12" t="n">
+      <c r="AA39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>sg_canonical_opponent_date</t>
         </is>
@@ -4909,40 +4877,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>XQVO2P3</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>17962246</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>159927901</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>6169435</t>
-        </is>
+      <c r="T40" t="n">
+        <v>17962246</v>
+      </c>
+      <c r="U40" t="n">
+        <v>159927901</v>
+      </c>
+      <c r="V40" t="n">
+        <v>6169435</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>4772197</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>4772197</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB40" s="12" t="n">
+      <c r="AA40" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -5028,12 +4983,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T41" t="n">
+        <v>18069009</v>
+      </c>
+      <c r="U41" t="n">
+        <v>160479695</v>
+      </c>
+      <c r="V41" t="n">
+        <v>6205783</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA41" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -5117,12 +5086,23 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T42" t="n">
+        <v>18150136</v>
+      </c>
+      <c r="V42" t="n">
+        <v>6371816</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA42" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -5206,12 +5186,29 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T43" t="n">
+        <v>18093824</v>
+      </c>
+      <c r="U43" t="n">
+        <v>159997341</v>
+      </c>
+      <c r="V43" t="n">
+        <v>6296797</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.305954083573273e+18</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AA43" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -5295,45 +5292,30 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>63DDB2Y</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>3289280</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>17965054</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>160228480</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>6474958</t>
-        </is>
+      <c r="R44" t="n">
+        <v>3289280</v>
+      </c>
+      <c r="T44" t="n">
+        <v>17965054</v>
+      </c>
+      <c r="U44" t="n">
+        <v>160228480</v>
+      </c>
+      <c r="V44" t="n">
+        <v>6474958</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>4811643</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>4811643</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB44" s="12" t="n">
+      <c r="AA44" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -5415,22 +5397,29 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>1558273</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S45" t="n">
+        <v>1558273</v>
+      </c>
+      <c r="T45" t="n">
+        <v>18147684</v>
+      </c>
+      <c r="U45" t="n">
+        <v>160059769</v>
+      </c>
+      <c r="V45" t="n">
+        <v>6552184</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA45" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -5514,22 +5503,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>1722872</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB46" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S46" t="n">
+        <v>1722872</v>
+      </c>
+      <c r="T46" t="n">
+        <v>18208488</v>
+      </c>
+      <c r="U46" t="n">
+        <v>161208192</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AA46" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -5613,22 +5606,29 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>1535537</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB47" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S47" t="n">
+        <v>1535537</v>
+      </c>
+      <c r="T47" t="n">
+        <v>18012990</v>
+      </c>
+      <c r="U47" t="n">
+        <v>160238815</v>
+      </c>
+      <c r="V47" t="n">
+        <v>6498337</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA47" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -5708,37 +5708,29 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>GXAK3W9</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>18033350</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>6317771</t>
-        </is>
+      <c r="T48" t="n">
+        <v>18033350</v>
+      </c>
+      <c r="U48" t="n">
+        <v>160418583</v>
+      </c>
+      <c r="V48" t="n">
+        <v>6317771</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>4833771</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>4833771</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>SeatGeek, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AB48" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AA48" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+td_events_sg_links</t>
         </is>
       </c>
     </row>
@@ -5818,12 +5810,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T49" t="n">
+        <v>18094060</v>
+      </c>
+      <c r="U49" t="n">
+        <v>160212608</v>
+      </c>
+      <c r="V49" t="n">
+        <v>6473129</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA49" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -5903,12 +5909,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB50" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T50" t="n">
+        <v>18147718</v>
+      </c>
+      <c r="U50" t="n">
+        <v>160059827</v>
+      </c>
+      <c r="V50" t="n">
+        <v>6206980</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA50" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -5992,12 +6012,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB51" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T51" t="n">
+        <v>18041102</v>
+      </c>
+      <c r="U51" t="n">
+        <v>160479696</v>
+      </c>
+      <c r="V51" t="n">
+        <v>6205784</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA51" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -6081,17 +6115,26 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>SYS-25e700352d</t>
-        </is>
-      </c>
-      <c r="AB52" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+      <c r="T52" t="n">
+        <v>18068939</v>
+      </c>
+      <c r="U52" t="n">
+        <v>160479651</v>
+      </c>
+      <c r="V52" t="n">
+        <v>6651178</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA52" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -6171,12 +6214,23 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB53" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T53" t="n">
+        <v>18150140</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6783256</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA53" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -6256,12 +6310,20 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB54" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T54" t="n">
+        <v>18033444</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>SeatGeek</t>
+        </is>
+      </c>
+      <c r="AA54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -6341,40 +6403,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>BPNX76P</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>18024488</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>159917330</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>6172480</t>
-        </is>
+      <c r="T55" t="n">
+        <v>18024488</v>
+      </c>
+      <c r="U55" t="n">
+        <v>159917330</v>
+      </c>
+      <c r="V55" t="n">
+        <v>6172480</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>4827164</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>4827164</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB55" s="12" t="n">
+      <c r="AA55" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -6456,40 +6505,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>APVNOKQ</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>17965048</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>160125607</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>6096061</t>
-        </is>
+      <c r="T56" t="n">
+        <v>17965048</v>
+      </c>
+      <c r="U56" t="n">
+        <v>160125607</v>
+      </c>
+      <c r="V56" t="n">
+        <v>6096061</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>4739426</v>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>4739426</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB56" s="12" t="n">
+      <c r="AA56" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -6571,40 +6607,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>K45OAVB</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>18035439</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>159926143</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>6170682</t>
-        </is>
+      <c r="T57" t="n">
+        <v>18035439</v>
+      </c>
+      <c r="U57" t="n">
+        <v>159926143</v>
+      </c>
+      <c r="V57" t="n">
+        <v>6170682</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>4809742</v>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>4809742</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB57" s="12" t="n">
+      <c r="AA57" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -6686,12 +6709,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB58" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T58" t="n">
+        <v>18024447</v>
+      </c>
+      <c r="V58" t="n">
+        <v>6556971</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA58" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6805,29 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>1558274</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB59" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S59" t="n">
+        <v>1558274</v>
+      </c>
+      <c r="T59" t="n">
+        <v>18147686</v>
+      </c>
+      <c r="U59" t="n">
+        <v>160059760</v>
+      </c>
+      <c r="V59" t="n">
+        <v>6823804</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA59" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -6870,12 +6911,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T60" t="n">
+        <v>18012992</v>
+      </c>
+      <c r="U60" t="n">
+        <v>160231319</v>
+      </c>
+      <c r="V60" t="n">
+        <v>6498399</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA60" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -6959,22 +7014,32 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>1437527</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB61" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S61" t="n">
+        <v>1437527</v>
+      </c>
+      <c r="T61" t="n">
+        <v>18077240</v>
+      </c>
+      <c r="U61" t="n">
+        <v>159997368</v>
+      </c>
+      <c r="V61" t="n">
+        <v>6297179</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>2.305954083573339e+18</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AA61" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -7058,12 +7123,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB62" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T62" t="n">
+        <v>18028955</v>
+      </c>
+      <c r="U62" t="n">
+        <v>159955430</v>
+      </c>
+      <c r="V62" t="n">
+        <v>6368040</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA62" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7226,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB63" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T63" t="n">
+        <v>17971634</v>
+      </c>
+      <c r="U63" t="n">
+        <v>160106809</v>
+      </c>
+      <c r="V63" t="n">
+        <v>6429661</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA63" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -7232,12 +7325,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB64" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T64" t="n">
+        <v>18176907</v>
+      </c>
+      <c r="U64" t="n">
+        <v>160686057</v>
+      </c>
+      <c r="V64" t="n">
+        <v>6783439</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA64" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -7317,40 +7424,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>PG5MJ29</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>18035548</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>159927892</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>6169440</t>
-        </is>
+      <c r="T65" t="n">
+        <v>18035548</v>
+      </c>
+      <c r="U65" t="n">
+        <v>159927892</v>
+      </c>
+      <c r="V65" t="n">
+        <v>6169440</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>4838321</v>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>4838321</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB65" s="12" t="n">
+      <c r="AA65" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -7436,12 +7530,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB66" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T66" t="n">
+        <v>18069011</v>
+      </c>
+      <c r="U66" t="n">
+        <v>160479697</v>
+      </c>
+      <c r="V66" t="n">
+        <v>6651240</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA66" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -7521,40 +7629,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>K45OA2P</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>18035349</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>159926144</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>6170684</t>
-        </is>
+      <c r="T67" t="n">
+        <v>18035349</v>
+      </c>
+      <c r="U67" t="n">
+        <v>159926144</v>
+      </c>
+      <c r="V67" t="n">
+        <v>6170684</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>4809741</v>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>4809741</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB67" s="12" t="n">
+      <c r="AA67" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -7640,22 +7735,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>1286333</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB68" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S68" t="n">
+        <v>1286333</v>
+      </c>
+      <c r="T68" t="n">
+        <v>18169352</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek</t>
+        </is>
+      </c>
+      <c r="AA68" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -7735,40 +7831,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>PG57EVW</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>18024480</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>159917186</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>6172360</t>
-        </is>
+      <c r="T69" t="n">
+        <v>18024480</v>
+      </c>
+      <c r="U69" t="n">
+        <v>159917186</v>
+      </c>
+      <c r="V69" t="n">
+        <v>6172360</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>4836401</v>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>4836401</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB69" s="12" t="n">
+      <c r="AA69" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -7850,45 +7933,30 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>369O3WZ</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>3241024</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>18033319</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>159996527</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>6206976</t>
-        </is>
+      <c r="R70" t="n">
+        <v>3241024</v>
+      </c>
+      <c r="T70" t="n">
+        <v>18033319</v>
+      </c>
+      <c r="U70" t="n">
+        <v>159996527</v>
+      </c>
+      <c r="V70" t="n">
+        <v>6206976</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>4834990</v>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>4834990</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB70" s="12" t="n">
+      <c r="AA70" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="AC70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -7970,12 +8038,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB71" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T71" t="n">
+        <v>18147720</v>
+      </c>
+      <c r="U71" t="n">
+        <v>160059834</v>
+      </c>
+      <c r="V71" t="n">
+        <v>6823662</v>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA71" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -8059,22 +8141,32 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>1437524</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB72" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S72" t="n">
+        <v>1437524</v>
+      </c>
+      <c r="T72" t="n">
+        <v>18093826</v>
+      </c>
+      <c r="U72" t="n">
+        <v>159997340</v>
+      </c>
+      <c r="V72" t="n">
+        <v>6296791</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>2.30595408357347e+18</v>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AA72" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -8158,12 +8250,23 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB73" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T73" t="n">
+        <v>18150142</v>
+      </c>
+      <c r="V73" t="n">
+        <v>6783269</v>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA73" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -8247,12 +8350,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T74" t="n">
+        <v>18094062</v>
+      </c>
+      <c r="U74" t="n">
+        <v>160021916</v>
+      </c>
+      <c r="V74" t="n">
+        <v>6297079</v>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA74" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -8332,40 +8449,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>6ZO9K94</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>18033437</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>159956994</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>6207021</t>
-        </is>
+      <c r="T75" t="n">
+        <v>18033437</v>
+      </c>
+      <c r="U75" t="n">
+        <v>159956994</v>
+      </c>
+      <c r="V75" t="n">
+        <v>6207021</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4768283</v>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>4768283</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB75" s="12" t="n">
+      <c r="AA75" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -8451,22 +8555,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>1629864</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB76" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S76" t="n">
+        <v>1629864</v>
+      </c>
+      <c r="T76" t="n">
+        <v>18169354</v>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek</t>
+        </is>
+      </c>
+      <c r="AA76" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -8546,22 +8651,29 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>1558275</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB77" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S77" t="n">
+        <v>1558275</v>
+      </c>
+      <c r="T77" t="n">
+        <v>18147688</v>
+      </c>
+      <c r="U77" t="n">
+        <v>160752383</v>
+      </c>
+      <c r="V77" t="n">
+        <v>6823816</v>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA77" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -8645,12 +8757,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB78" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T78" t="n">
+        <v>18012388</v>
+      </c>
+      <c r="U78" t="n">
+        <v>160285974</v>
+      </c>
+      <c r="V78" t="n">
+        <v>6529858</v>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA78" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -8730,40 +8856,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>Y3OBZQV</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>18033352</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>159996565</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>6209678</t>
-        </is>
+      <c r="T79" t="n">
+        <v>18033352</v>
+      </c>
+      <c r="U79" t="n">
+        <v>159996565</v>
+      </c>
+      <c r="V79" t="n">
+        <v>6209678</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>4833773</v>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>4833773</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB79" s="12" t="n">
+      <c r="AA79" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -8849,12 +8962,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB80" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T80" t="n">
+        <v>18028959</v>
+      </c>
+      <c r="U80" t="n">
+        <v>159955440</v>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AA80" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -8938,12 +9062,26 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB81" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T81" t="n">
+        <v>18068940</v>
+      </c>
+      <c r="U81" t="n">
+        <v>160479652</v>
+      </c>
+      <c r="V81" t="n">
+        <v>6651180</v>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA81" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -9023,40 +9161,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>55BOEYM</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>18033280</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>159996816</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>6209623</t>
-        </is>
+      <c r="T82" t="n">
+        <v>18033280</v>
+      </c>
+      <c r="U82" t="n">
+        <v>159996816</v>
+      </c>
+      <c r="V82" t="n">
+        <v>6209623</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>4767956</v>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>4767956</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB82" s="12" t="n">
+      <c r="AA82" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -9138,12 +9263,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB83" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T83" t="n">
+        <v>18024449</v>
+      </c>
+      <c r="V83" t="n">
+        <v>6172353</v>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA83" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -9223,40 +9359,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>Y5V9NEN</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>18024482</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>159917188</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>6172357</t>
-        </is>
+      <c r="T84" t="n">
+        <v>18024482</v>
+      </c>
+      <c r="U84" t="n">
+        <v>159917188</v>
+      </c>
+      <c r="V84" t="n">
+        <v>6172357</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>4827026</v>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>4827026</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB84" s="12" t="n">
+      <c r="AA84" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -9342,12 +9465,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB85" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T85" t="n">
+        <v>18012994</v>
+      </c>
+      <c r="U85" t="n">
+        <v>160231330</v>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AA85" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -9427,35 +9561,24 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>AA43G5B</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>18033351</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>159996563</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>6209669</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
+      <c r="T86" t="n">
+        <v>18033351</v>
+      </c>
+      <c r="U86" t="n">
+        <v>159996563</v>
+      </c>
+      <c r="V86" t="n">
+        <v>6209669</v>
+      </c>
+      <c r="Z86" t="inlineStr">
         <is>
           <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AB86" s="12" t="n">
+      <c r="AA86" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="AC86" t="inlineStr">
+      <c r="AB86" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -9537,12 +9660,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB87" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T87" t="n">
+        <v>18094064</v>
+      </c>
+      <c r="U87" t="n">
+        <v>160021919</v>
+      </c>
+      <c r="V87" t="n">
+        <v>6297071</v>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA87" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -9626,12 +9763,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB88" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T88" t="n">
+        <v>17971636</v>
+      </c>
+      <c r="U88" t="n">
+        <v>160106945</v>
+      </c>
+      <c r="V88" t="n">
+        <v>6429657</v>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA88" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -9711,12 +9862,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB89" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T89" t="n">
+        <v>18147786</v>
+      </c>
+      <c r="U89" t="n">
+        <v>160059837</v>
+      </c>
+      <c r="V89" t="n">
+        <v>6823682</v>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA89" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -9796,40 +9961,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>6ZMDYB7</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>18035549</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>159927890</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>6169446</t>
-        </is>
+      <c r="T90" t="n">
+        <v>18035549</v>
+      </c>
+      <c r="U90" t="n">
+        <v>159927890</v>
+      </c>
+      <c r="V90" t="n">
+        <v>6169446</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>4838322</v>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>4838322</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB90" s="12" t="n">
+      <c r="AA90" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC90" t="inlineStr">
+      <c r="AB90" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -9915,12 +10067,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB91" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T91" t="n">
+        <v>18069013</v>
+      </c>
+      <c r="U91" t="n">
+        <v>160479699</v>
+      </c>
+      <c r="V91" t="n">
+        <v>6651242</v>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA91" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -10000,12 +10166,20 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB92" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T92" t="n">
+        <v>18033446</v>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>SeatGeek</t>
+        </is>
+      </c>
+      <c r="AA92" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -10085,40 +10259,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>V6P9B2Q</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>18024492</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>159917329</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>6172488</t>
-        </is>
+      <c r="T93" t="n">
+        <v>18024492</v>
+      </c>
+      <c r="U93" t="n">
+        <v>159917329</v>
+      </c>
+      <c r="V93" t="n">
+        <v>6172488</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>4827163</v>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>4827163</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB93" s="12" t="n">
+      <c r="AA93" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC93" t="inlineStr">
+      <c r="AB93" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -10200,40 +10361,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>6D5POJY</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>18033281</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>159996813</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>6209621</t>
-        </is>
+      <c r="T94" t="n">
+        <v>18033281</v>
+      </c>
+      <c r="U94" t="n">
+        <v>159996813</v>
+      </c>
+      <c r="V94" t="n">
+        <v>6209621</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>4767957</v>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>4767957</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB94" s="12" t="n">
+      <c r="AA94" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC94" t="inlineStr">
+      <c r="AB94" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -10315,40 +10463,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>OOMOYZP</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>18035437</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>159918372</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>6166307</t>
-        </is>
+      <c r="T95" t="n">
+        <v>18035437</v>
+      </c>
+      <c r="U95" t="n">
+        <v>159918372</v>
+      </c>
+      <c r="V95" t="n">
+        <v>6166307</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>4844013</v>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>4844013</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB95" s="12" t="n">
+      <c r="AA95" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC95" t="inlineStr">
+      <c r="AB95" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -10430,40 +10565,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>DPNZQXA</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>18035447</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>159926145</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>6170681</t>
-        </is>
+      <c r="T96" t="n">
+        <v>18035447</v>
+      </c>
+      <c r="U96" t="n">
+        <v>159926145</v>
+      </c>
+      <c r="V96" t="n">
+        <v>6170681</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>4809744</v>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>4809744</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB96" s="12" t="n">
+      <c r="AA96" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC96" t="inlineStr">
+      <c r="AB96" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -10545,45 +10667,30 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>K4EKY6B</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>3241023</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>18033320</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>159996525</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>6206973</t>
-        </is>
+      <c r="R97" t="n">
+        <v>3241023</v>
+      </c>
+      <c r="T97" t="n">
+        <v>18033320</v>
+      </c>
+      <c r="U97" t="n">
+        <v>159996525</v>
+      </c>
+      <c r="V97" t="n">
+        <v>6206973</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>4834991</v>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>4834991</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB97" s="12" t="n">
+      <c r="AA97" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="AC97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -10669,12 +10776,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB98" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T98" t="n">
+        <v>18012390</v>
+      </c>
+      <c r="U98" t="n">
+        <v>160418142</v>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AA98" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -10758,12 +10876,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB99" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T99" t="n">
+        <v>18012996</v>
+      </c>
+      <c r="U99" t="n">
+        <v>160231338</v>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AA99" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -10847,12 +10976,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB100" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T100" t="n">
+        <v>17971638</v>
+      </c>
+      <c r="U100" t="n">
+        <v>160107010</v>
+      </c>
+      <c r="V100" t="n">
+        <v>6429653</v>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA100" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -10932,12 +11075,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB101" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T101" t="n">
+        <v>18176906</v>
+      </c>
+      <c r="U101" t="n">
+        <v>160712004</v>
+      </c>
+      <c r="V101" t="n">
+        <v>6783443</v>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA101" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -11021,12 +11178,26 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="AB102" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T102" t="n">
+        <v>18147690</v>
+      </c>
+      <c r="U102" t="n">
+        <v>160059758</v>
+      </c>
+      <c r="V102" t="n">
+        <v>6823826</v>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA102" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -11110,40 +11281,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>D4DWYDA</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>18033353</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>160102222</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>6432387</t>
-        </is>
+      <c r="T103" t="n">
+        <v>18033353</v>
+      </c>
+      <c r="U103" t="n">
+        <v>160102222</v>
+      </c>
+      <c r="V103" t="n">
+        <v>6432387</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>4833775</v>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>4833775</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB103" s="12" t="n">
+      <c r="AA103" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC103" t="inlineStr">
+      <c r="AB103" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -11229,12 +11387,26 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB104" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T104" t="n">
+        <v>18068941</v>
+      </c>
+      <c r="U104" t="n">
+        <v>160479653</v>
+      </c>
+      <c r="V104" t="n">
+        <v>6651182</v>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA104" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -11314,12 +11486,23 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB105" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T105" t="n">
+        <v>18150144</v>
+      </c>
+      <c r="V105" t="n">
+        <v>6783285</v>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA105" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -11399,22 +11582,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>1387473</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB106" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S106" t="n">
+        <v>1387473</v>
+      </c>
+      <c r="T106" t="n">
+        <v>17965066</v>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek</t>
+        </is>
+      </c>
+      <c r="AA106" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -11494,12 +11678,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB107" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T107" t="n">
+        <v>18024451</v>
+      </c>
+      <c r="V107" t="n">
+        <v>6172354</v>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA107" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -11579,12 +11774,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB108" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T108" t="n">
+        <v>18094066</v>
+      </c>
+      <c r="U108" t="n">
+        <v>160021918</v>
+      </c>
+      <c r="V108" t="n">
+        <v>6297075</v>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA108" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -11664,12 +11873,29 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB109" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T109" t="n">
+        <v>18093828</v>
+      </c>
+      <c r="U109" t="n">
+        <v>159997343</v>
+      </c>
+      <c r="V109" t="n">
+        <v>6296787</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>2.305954083573535e+18</v>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AA109" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -11753,12 +11979,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB110" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T110" t="n">
+        <v>18028957</v>
+      </c>
+      <c r="U110" t="n">
+        <v>160357737</v>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AA110" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -11838,40 +12075,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>NZ5D9A6</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>18035551</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>159927891</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>6169441</t>
-        </is>
+      <c r="T111" t="n">
+        <v>18035551</v>
+      </c>
+      <c r="U111" t="n">
+        <v>159927891</v>
+      </c>
+      <c r="V111" t="n">
+        <v>6169441</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>4838323</v>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>4838323</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB111" s="12" t="n">
+      <c r="AA111" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC111" t="inlineStr">
+      <c r="AB111" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -11957,12 +12181,26 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="AB112" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T112" t="n">
+        <v>18147692</v>
+      </c>
+      <c r="U112" t="n">
+        <v>160059759</v>
+      </c>
+      <c r="V112" t="n">
+        <v>6823838</v>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA112" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -12042,12 +12280,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB113" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T113" t="n">
+        <v>18147788</v>
+      </c>
+      <c r="U113" t="n">
+        <v>160752729</v>
+      </c>
+      <c r="V113" t="n">
+        <v>6823708</v>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA113" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -12131,45 +12383,30 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>DPGW54A</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>3241021</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>18033321</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>159996526</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>6206972</t>
-        </is>
+      <c r="R114" t="n">
+        <v>3241021</v>
+      </c>
+      <c r="T114" t="n">
+        <v>18033321</v>
+      </c>
+      <c r="U114" t="n">
+        <v>159996526</v>
+      </c>
+      <c r="V114" t="n">
+        <v>6206972</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>4834992</v>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>4834992</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB114" s="12" t="n">
+      <c r="AA114" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="AC114" t="inlineStr">
+      <c r="AB114" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -12251,12 +12488,23 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB115" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T115" t="n">
+        <v>18150146</v>
+      </c>
+      <c r="V115" t="n">
+        <v>6783298</v>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA115" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -12336,40 +12584,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr">
-        <is>
-          <t>Y3ONYX5</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>18033283</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>159996812</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>6209619</t>
-        </is>
+      <c r="T116" t="n">
+        <v>18033283</v>
+      </c>
+      <c r="U116" t="n">
+        <v>159996812</v>
+      </c>
+      <c r="V116" t="n">
+        <v>6209619</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>4767955</v>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>4767955</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB116" s="12" t="n">
+      <c r="AA116" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC116" t="inlineStr">
+      <c r="AB116" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -12451,40 +12686,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>369WXW2</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>18033438</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>160102210</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>6207022</t>
-        </is>
+      <c r="T117" t="n">
+        <v>18033438</v>
+      </c>
+      <c r="U117" t="n">
+        <v>160102210</v>
+      </c>
+      <c r="V117" t="n">
+        <v>6207022</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>4768280</v>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>4768280</t>
-        </is>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB117" s="12" t="n">
+      <c r="AA117" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC117" t="inlineStr">
+      <c r="AB117" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -12570,22 +12792,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>1629873</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB118" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S118" t="n">
+        <v>1629873</v>
+      </c>
+      <c r="T118" t="n">
+        <v>18169356</v>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek</t>
+        </is>
+      </c>
+      <c r="AA118" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -12665,40 +12888,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>WQV629J</t>
-        </is>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>18024484</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>159917189</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>6172358</t>
-        </is>
+      <c r="T119" t="n">
+        <v>18024484</v>
+      </c>
+      <c r="U119" t="n">
+        <v>159917189</v>
+      </c>
+      <c r="V119" t="n">
+        <v>6172358</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>4836402</v>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>4836402</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB119" s="12" t="n">
+      <c r="AA119" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC119" t="inlineStr">
+      <c r="AB119" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -12780,40 +12990,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>44MKXOD</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>18033360</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>159996564</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>6209682</t>
-        </is>
+      <c r="T120" t="n">
+        <v>18033360</v>
+      </c>
+      <c r="U120" t="n">
+        <v>159996564</v>
+      </c>
+      <c r="V120" t="n">
+        <v>6209682</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>4833776</v>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>4833776</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB120" s="12" t="n">
+      <c r="AA120" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC120" t="inlineStr">
+      <c r="AB120" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -12899,12 +13096,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB121" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T121" t="n">
+        <v>18028961</v>
+      </c>
+      <c r="U121" t="n">
+        <v>159955445</v>
+      </c>
+      <c r="V121" t="n">
+        <v>6368052</v>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA121" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -12988,12 +13199,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T122" t="n">
+        <v>17971640</v>
+      </c>
+      <c r="U122" t="n">
+        <v>160106817</v>
+      </c>
+      <c r="V122" t="n">
+        <v>6429655</v>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA122" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -13073,12 +13298,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB123" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T123" t="n">
+        <v>18176909</v>
+      </c>
+      <c r="U123" t="n">
+        <v>160686058</v>
+      </c>
+      <c r="V123" t="n">
+        <v>6783447</v>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA123" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -13162,12 +13401,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB124" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T124" t="n">
+        <v>18069010</v>
+      </c>
+      <c r="V124" t="n">
+        <v>6651244</v>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>SeatGeek, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA124" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -13251,12 +13501,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB125" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T125" t="n">
+        <v>18012998</v>
+      </c>
+      <c r="U125" t="n">
+        <v>160230939</v>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AA125" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -13340,12 +13601,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB126" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T126" t="n">
+        <v>18147790</v>
+      </c>
+      <c r="U126" t="n">
+        <v>160059836</v>
+      </c>
+      <c r="V126" t="n">
+        <v>6823717</v>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA126" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -13425,40 +13700,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>DPNZQ76</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>18035351</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>159926142</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>6170683</t>
-        </is>
+      <c r="T127" t="n">
+        <v>18035351</v>
+      </c>
+      <c r="U127" t="n">
+        <v>159926142</v>
+      </c>
+      <c r="V127" t="n">
+        <v>6170683</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>4809743</v>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>4809743</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB127" s="12" t="n">
+      <c r="AA127" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC127" t="inlineStr">
+      <c r="AB127" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -13540,12 +13802,20 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB128" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T128" t="n">
+        <v>18024453</v>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>SeatGeek</t>
+        </is>
+      </c>
+      <c r="AA128" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -13625,40 +13895,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>EQ5QW2Q</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>18035343</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>159918404</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>6166344</t>
-        </is>
+      <c r="T129" t="n">
+        <v>18035343</v>
+      </c>
+      <c r="U129" t="n">
+        <v>159918404</v>
+      </c>
+      <c r="V129" t="n">
+        <v>6166344</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>4844064</v>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>4844064</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB129" s="12" t="n">
+      <c r="AA129" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC129" t="inlineStr">
+      <c r="AB129" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -13744,22 +14001,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>1629870</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="AB130" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date</t>
+      <c r="S130" t="n">
+        <v>1629870</v>
+      </c>
+      <c r="T130" t="n">
+        <v>18169358</v>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>GoTickets, SeatGeek</t>
+        </is>
+      </c>
+      <c r="AA130" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -13843,12 +14101,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB131" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T131" t="n">
+        <v>18012392</v>
+      </c>
+      <c r="U131" t="n">
+        <v>160305642</v>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AA131" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -13928,12 +14197,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB132" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T132" t="n">
+        <v>18094071</v>
+      </c>
+      <c r="U132" t="n">
+        <v>160021917</v>
+      </c>
+      <c r="V132" t="n">
+        <v>6297077</v>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA132" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -14013,12 +14296,29 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB133" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T133" t="n">
+        <v>18093830</v>
+      </c>
+      <c r="U133" t="n">
+        <v>159997342</v>
+      </c>
+      <c r="V133" t="n">
+        <v>6296793</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>2.305954083573666e+18</v>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AA133" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime</t>
         </is>
       </c>
     </row>
@@ -14102,12 +14402,23 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB134" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T134" t="n">
+        <v>18028963</v>
+      </c>
+      <c r="U134" t="n">
+        <v>160531089</v>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AA134" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -14191,12 +14502,26 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB135" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T135" t="n">
+        <v>18176908</v>
+      </c>
+      <c r="U135" t="n">
+        <v>160686141</v>
+      </c>
+      <c r="V135" t="n">
+        <v>6783457</v>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AA135" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -14276,12 +14601,23 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB136" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>opponent_tbd</t>
+      <c r="T136" t="n">
+        <v>18068942</v>
+      </c>
+      <c r="U136" t="n">
+        <v>160479655</v>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AA136" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>opponent_tbd+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -14361,12 +14697,20 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB137" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>unresolved</t>
+      <c r="T137" t="n">
+        <v>18033445</v>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>SeatGeek</t>
+        </is>
+      </c>
+      <c r="AA137" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -14446,43 +14790,30 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>VZ3WVYX</t>
-        </is>
+      <c r="S138" t="n">
+        <v>1377027</v>
       </c>
       <c r="T138" t="n">
-        <v>1377027</v>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>18033282</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>159996814</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>6209622</t>
-        </is>
+        <v>18033282</v>
+      </c>
+      <c r="U138" t="n">
+        <v>159996814</v>
+      </c>
+      <c r="V138" t="n">
+        <v>6209622</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>4767954</v>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>4767954</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
           <t>GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB138" s="12" t="n">
+      <c r="AA138" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="AC138" t="inlineStr">
+      <c r="AB138" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date+gotickets_catalog_7d_pull</t>
         </is>
@@ -14564,35 +14895,24 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>OO7G4GN</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>18033439</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>159956993</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>6207020</t>
-        </is>
-      </c>
-      <c r="AA139" t="inlineStr">
+      <c r="T139" t="n">
+        <v>18033439</v>
+      </c>
+      <c r="U139" t="n">
+        <v>159956993</v>
+      </c>
+      <c r="V139" t="n">
+        <v>6207020</v>
+      </c>
+      <c r="Z139" t="inlineStr">
         <is>
           <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AB139" s="12" t="n">
+      <c r="AA139" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="AC139" t="inlineStr">
+      <c r="AB139" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -14674,40 +14994,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>MK57Y9O</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>18024486</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>159917187</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>6172359</t>
-        </is>
+      <c r="T140" t="n">
+        <v>18024486</v>
+      </c>
+      <c r="U140" t="n">
+        <v>159917187</v>
+      </c>
+      <c r="V140" t="n">
+        <v>6172359</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>4836403</v>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>4836403</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AB140" s="12" t="n">
+      <c r="AA140" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC140" t="inlineStr">
+      <c r="AB140" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -14789,12 +15096,20 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="AB141" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>opponent_tbd_flex</t>
+      <c r="T141" t="n">
+        <v>18069012</v>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>SeatGeek</t>
+        </is>
+      </c>
+      <c r="AA141" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>opponent_tbd_flex+sg_events_paciolan_link</t>
         </is>
       </c>
     </row>
@@ -14870,45 +15185,30 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>7P63X9D</t>
-        </is>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>3101506</t>
-        </is>
-      </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>1190236</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>17694063</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>159262247</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>5966797</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
+      <c r="R142" t="n">
+        <v>3101506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>1190236</v>
+      </c>
+      <c r="T142" t="n">
+        <v>17694063</v>
+      </c>
+      <c r="U142" t="n">
+        <v>159262247</v>
+      </c>
+      <c r="V142" t="n">
+        <v>5966797</v>
+      </c>
+      <c r="Z142" t="inlineStr">
         <is>
           <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AB142" s="12" t="n">
+      <c r="AA142" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="AC142" t="inlineStr">
+      <c r="AB142" t="inlineStr">
         <is>
           <t>venue_date_name_exact</t>
         </is>
@@ -14982,40 +15282,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>PGJDA73</t>
-        </is>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>3026271</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>17565134</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>158487337</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>5809770</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
+      <c r="R143" t="n">
+        <v>3026271</v>
+      </c>
+      <c r="T143" t="n">
+        <v>17565134</v>
+      </c>
+      <c r="U143" t="n">
+        <v>158487337</v>
+      </c>
+      <c r="V143" t="n">
+        <v>5809770</v>
+      </c>
+      <c r="Z143" t="inlineStr">
         <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AB143" s="12" t="n">
+      <c r="AA143" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC143" t="inlineStr">
+      <c r="AB143" t="inlineStr">
         <is>
           <t>day_level_zone_product</t>
         </is>
@@ -15089,40 +15376,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>PGJDA73</t>
-        </is>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>3026271</t>
-        </is>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>17565134</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>158487337</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>5809770</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
+      <c r="R144" t="n">
+        <v>3026271</v>
+      </c>
+      <c r="T144" t="n">
+        <v>17565134</v>
+      </c>
+      <c r="U144" t="n">
+        <v>158487337</v>
+      </c>
+      <c r="V144" t="n">
+        <v>5809770</v>
+      </c>
+      <c r="Z144" t="inlineStr">
         <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AB144" s="12" t="n">
+      <c r="AA144" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC144" t="inlineStr">
+      <c r="AB144" t="inlineStr">
         <is>
           <t>day_level_zone_product</t>
         </is>
@@ -15196,40 +15470,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>V6JQY9J</t>
-        </is>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>3026272</t>
-        </is>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>17565136</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>158487348</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>5809771</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
+      <c r="R145" t="n">
+        <v>3026272</v>
+      </c>
+      <c r="T145" t="n">
+        <v>17565136</v>
+      </c>
+      <c r="U145" t="n">
+        <v>158487348</v>
+      </c>
+      <c r="V145" t="n">
+        <v>5809771</v>
+      </c>
+      <c r="Z145" t="inlineStr">
         <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AB145" s="12" t="n">
+      <c r="AA145" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC145" t="inlineStr">
+      <c r="AB145" t="inlineStr">
         <is>
           <t>day_level_zone_product</t>
         </is>
@@ -15303,40 +15564,27 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>APYE67J</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>3017608</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>17565120</t>
-        </is>
-      </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>158501986</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>5809736</t>
-        </is>
-      </c>
-      <c r="AA146" t="inlineStr">
+      <c r="R146" t="n">
+        <v>3017608</v>
+      </c>
+      <c r="T146" t="n">
+        <v>17565120</v>
+      </c>
+      <c r="U146" t="n">
+        <v>158501986</v>
+      </c>
+      <c r="V146" t="n">
+        <v>5809736</v>
+      </c>
+      <c r="Z146" t="inlineStr">
         <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AB146" s="12" t="n">
+      <c r="AA146" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="AC146" t="inlineStr">
+      <c r="AB146" t="inlineStr">
         <is>
           <t>venue_date_name_exact</t>
         </is>
@@ -16350,7 +16598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16441,13 +16689,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="D4" t="n">
         <v>145</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -16462,13 +16710,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="D5" t="n">
         <v>145</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.3793</v>
+        <v>0.8138</v>
       </c>
     </row>
     <row r="6">
@@ -16483,13 +16731,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="D6" t="n">
         <v>145</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.3862</v>
+        <v>0.8414</v>
       </c>
     </row>
     <row r="7">
@@ -16546,13 +16794,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D9" t="n">
         <v>145</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.3241</v>
+        <v>0.3724</v>
       </c>
     </row>
     <row r="10"/>
@@ -16568,31 +16816,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
         <v>145</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0.4966</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>canonical hub row</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>aq_short_event_id</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>58</v>
-      </c>
-      <c r="D12" t="n">
-        <v>145</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/evd_event_id_crosswalk_mapped.xlsx
+++ b/evd_event_id_crosswalk_mapped.xlsx
@@ -928,20 +928,23 @@
       <c r="T2" t="n">
         <v>18126596</v>
       </c>
+      <c r="U2" t="n">
+        <v>160427467</v>
+      </c>
       <c r="V2" t="n">
         <v>6288282</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>GoTickets, SeatGeek, Vivid Seats</t>
+          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA2" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -1028,20 +1031,23 @@
       <c r="T3" t="n">
         <v>17965064</v>
       </c>
+      <c r="U3" t="n">
+        <v>160265549</v>
+      </c>
       <c r="V3" t="n">
         <v>6205721</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA3" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -2176,20 +2182,23 @@
       <c r="T14" t="n">
         <v>18024445</v>
       </c>
+      <c r="U14" t="n">
+        <v>160324383</v>
+      </c>
       <c r="V14" t="n">
         <v>6369854</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -2491,20 +2500,23 @@
       <c r="T17" t="n">
         <v>18150134</v>
       </c>
+      <c r="U17" t="n">
+        <v>160379220</v>
+      </c>
       <c r="V17" t="n">
         <v>6371814</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -3018,17 +3030,20 @@
       <c r="T22" t="n">
         <v>18169350</v>
       </c>
+      <c r="U22" t="n">
+        <v>160206469</v>
+      </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>GoTickets, SeatGeek</t>
+          <t>GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -3745,20 +3760,23 @@
       <c r="T29" t="n">
         <v>18147714</v>
       </c>
+      <c r="U29" t="n">
+        <v>160416796</v>
+      </c>
       <c r="V29" t="n">
         <v>6802467</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime</t>
+          <t>sg_events_venue_datetime+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -4063,17 +4081,20 @@
       <c r="T32" t="n">
         <v>18033447</v>
       </c>
+      <c r="U32" t="n">
+        <v>159996706</v>
+      </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>SeatGeek</t>
+          <t>SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>sg_canonical_opponent_date</t>
+          <t>sg_canonical_opponent_date+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -4783,17 +4804,20 @@
       <c r="T39" t="n">
         <v>18147716</v>
       </c>
+      <c r="U39" t="n">
+        <v>160203438</v>
+      </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>SeatGeek</t>
+          <t>SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>sg_canonical_opponent_date</t>
+          <t>sg_canonical_opponent_date+sg_links_sh</t>
         </is>
       </c>
     </row>
@@ -5089,20 +5113,23 @@
       <c r="T42" t="n">
         <v>18150136</v>
       </c>
+      <c r="U42" t="n">
+        <v>160379251</v>
+      </c>
       <c r="V42" t="n">
         <v>6371816</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -6217,20 +6244,23 @@
       <c r="T53" t="n">
         <v>18150140</v>
       </c>
+      <c r="U53" t="n">
+        <v>160686463</v>
+      </c>
       <c r="V53" t="n">
         <v>6783256</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA53" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -6313,17 +6343,20 @@
       <c r="T54" t="n">
         <v>18033444</v>
       </c>
+      <c r="U54" t="n">
+        <v>159996705</v>
+      </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>SeatGeek</t>
+          <t>SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA54" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -6712,20 +6745,23 @@
       <c r="T58" t="n">
         <v>18024447</v>
       </c>
+      <c r="U58" t="n">
+        <v>160324388</v>
+      </c>
       <c r="V58" t="n">
         <v>6556971</v>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA58" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -7741,17 +7777,20 @@
       <c r="T68" t="n">
         <v>18169352</v>
       </c>
+      <c r="U68" t="n">
+        <v>160427474</v>
+      </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>GoTickets, SeatGeek</t>
+          <t>GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA68" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -8253,20 +8292,23 @@
       <c r="T73" t="n">
         <v>18150142</v>
       </c>
+      <c r="U73" t="n">
+        <v>160387041</v>
+      </c>
       <c r="V73" t="n">
         <v>6783269</v>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA73" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -8561,17 +8603,20 @@
       <c r="T76" t="n">
         <v>18169354</v>
       </c>
+      <c r="U76" t="n">
+        <v>160427482</v>
+      </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>GoTickets, SeatGeek</t>
+          <t>GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA76" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -9266,20 +9311,23 @@
       <c r="T83" t="n">
         <v>18024449</v>
       </c>
+      <c r="U83" t="n">
+        <v>159917034</v>
+      </c>
       <c r="V83" t="n">
         <v>6172353</v>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA83" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -10169,17 +10217,20 @@
       <c r="T92" t="n">
         <v>18033446</v>
       </c>
+      <c r="U92" t="n">
+        <v>159996707</v>
+      </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>SeatGeek</t>
+          <t>SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA92" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -11489,20 +11540,23 @@
       <c r="T105" t="n">
         <v>18150144</v>
       </c>
+      <c r="U105" t="n">
+        <v>160686465</v>
+      </c>
       <c r="V105" t="n">
         <v>6783285</v>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA105" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -11588,17 +11642,20 @@
       <c r="T106" t="n">
         <v>17965066</v>
       </c>
+      <c r="U106" t="n">
+        <v>160276830</v>
+      </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>GoTickets, SeatGeek</t>
+          <t>GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA106" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -11681,20 +11738,23 @@
       <c r="T107" t="n">
         <v>18024451</v>
       </c>
+      <c r="U107" t="n">
+        <v>159917031</v>
+      </c>
       <c r="V107" t="n">
         <v>6172354</v>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA107" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -12491,20 +12551,23 @@
       <c r="T115" t="n">
         <v>18150146</v>
       </c>
+      <c r="U115" t="n">
+        <v>160686469</v>
+      </c>
       <c r="V115" t="n">
         <v>6783298</v>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA115" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -12798,17 +12861,20 @@
       <c r="T118" t="n">
         <v>18169356</v>
       </c>
+      <c r="U118" t="n">
+        <v>160427498</v>
+      </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>GoTickets, SeatGeek</t>
+          <t>GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA118" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -13404,20 +13470,23 @@
       <c r="T124" t="n">
         <v>18069010</v>
       </c>
+      <c r="U124" t="n">
+        <v>160479701</v>
+      </c>
       <c r="V124" t="n">
         <v>6651244</v>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>SeatGeek, Vivid Seats</t>
+          <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AA124" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -13805,17 +13874,20 @@
       <c r="T128" t="n">
         <v>18024453</v>
       </c>
+      <c r="U128" t="n">
+        <v>159917033</v>
+      </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>SeatGeek</t>
+          <t>SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA128" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -14007,17 +14079,20 @@
       <c r="T130" t="n">
         <v>18169358</v>
       </c>
+      <c r="U130" t="n">
+        <v>160427509</v>
+      </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>GoTickets, SeatGeek</t>
+          <t>GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA130" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link</t>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -14700,17 +14775,20 @@
       <c r="T137" t="n">
         <v>18033445</v>
       </c>
+      <c r="U137" t="n">
+        <v>159996704</v>
+      </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>SeatGeek</t>
+          <t>SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA137" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -15099,17 +15177,20 @@
       <c r="T141" t="n">
         <v>18069012</v>
       </c>
+      <c r="U141" t="n">
+        <v>160479705</v>
+      </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>SeatGeek</t>
+          <t>SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AA141" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>opponent_tbd_flex+sg_events_paciolan_link</t>
+          <t>opponent_tbd_flex+sg_events_paciolan_link+sh_performer_events</t>
         </is>
       </c>
     </row>
@@ -16710,13 +16791,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="D5" t="n">
         <v>145</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.8138</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/evd_event_id_crosswalk_mapped.xlsx
+++ b/evd_event_id_crosswalk_mapped.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Event ID Crosswalk" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="By Source" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Paciolan Tenants" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Source Coverage" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Source Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="By Source" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Paciolan Tenants" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Event ID Crosswalk'!$A$1:$Q$146</definedName>
@@ -22,9 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -126,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -153,14 +151,9 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -667,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB146"/>
+  <dimension ref="A1:AC146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -687,17 +680,18 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
-    <col width="23" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="34" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -828,15 +822,20 @@
       </c>
       <c r="Z1" s="11" t="inlineStr">
         <is>
+          <t>aq_short_event_id</t>
+        </is>
+      </c>
+      <c r="AA1" s="11" t="inlineStr">
+        <is>
           <t>sources_mapped</t>
         </is>
       </c>
-      <c r="AA1" s="11" t="inlineStr">
+      <c r="AB1" s="11" t="inlineStr">
         <is>
           <t>sources_mapped_count</t>
         </is>
       </c>
-      <c r="AB1" s="11" t="inlineStr">
+      <c r="AC1" s="11" t="inlineStr">
         <is>
           <t>match_method</t>
         </is>
@@ -922,29 +921,35 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="R2" s="12" t="n">
+        <v>3433351</v>
+      </c>
+      <c r="S2" s="12" t="n">
         <v>1629863</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="12" t="n">
         <v>18126596</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2" s="12" t="n">
         <v>160427467</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2" s="12" t="n">
         <v>6288282</v>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA2" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W2" s="13" t="n"/>
+      <c r="X2" s="13" t="n"/>
+      <c r="Y2" s="13" t="n"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -1028,26 +1033,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="R3" s="12" t="n">
+        <v>3400622</v>
+      </c>
+      <c r="S3" s="13" t="n"/>
+      <c r="T3" s="12" t="n">
         <v>17965064</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3" s="12" t="n">
         <v>160265549</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3" s="12" t="n">
         <v>6205721</v>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA3" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W3" s="13" t="n"/>
+      <c r="X3" s="13" t="n"/>
+      <c r="Y3" s="13" t="n"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -1131,29 +1143,40 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="R4" s="12" t="n">
+        <v>3330200</v>
+      </c>
+      <c r="S4" s="13" t="n"/>
+      <c r="T4" s="12" t="n">
         <v>18024316</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4" s="12" t="n">
         <v>160324613</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4" s="12" t="n">
         <v>6185528</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="W4" s="13" t="n"/>
+      <c r="X4" s="13" t="n"/>
+      <c r="Y4" s="12" t="n">
         <v>4827175</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA4" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>NZ59BD2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -1237,26 +1260,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="R5" s="12" t="n">
+        <v>3241119</v>
+      </c>
+      <c r="S5" s="13" t="n"/>
+      <c r="T5" s="12" t="n">
         <v>17986058</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5" s="12" t="n">
         <v>159478580</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5" s="12" t="n">
         <v>6178998</v>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA5" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W5" s="13" t="n"/>
+      <c r="X5" s="13" t="n"/>
+      <c r="Y5" s="13" t="n"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -1340,29 +1370,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="R6" s="12" t="n">
+        <v>3312472</v>
+      </c>
+      <c r="S6" s="13" t="n"/>
+      <c r="T6" s="12" t="n">
         <v>17936149</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U6" s="12" t="n">
         <v>160228320</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6" s="12" t="n">
         <v>6206351</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="W6" s="13" t="n"/>
+      <c r="X6" s="13" t="n"/>
+      <c r="Y6" s="12" t="n">
         <v>4785738</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA6" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>BP3KYOD</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -1446,26 +1487,38 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="R7" s="12" t="n">
+        <v>3250473</v>
+      </c>
+      <c r="S7" s="13" t="n"/>
+      <c r="T7" s="12" t="n">
         <v>17997465</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U7" s="12" t="n">
         <v>159927981</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7" s="12" t="n">
         <v>6207016</v>
       </c>
+      <c r="W7" s="13" t="n"/>
+      <c r="X7" s="13" t="n"/>
+      <c r="Y7" s="13" t="n"/>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>Y5YDMDN</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -1549,29 +1602,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="R8" s="12" t="n">
+        <v>3292251</v>
+      </c>
+      <c r="S8" s="13" t="n"/>
+      <c r="T8" s="12" t="n">
         <v>17984356</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U8" s="12" t="n">
         <v>159766135</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8" s="12" t="n">
         <v>6206530</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="W8" s="13" t="n"/>
+      <c r="X8" s="13" t="n"/>
+      <c r="Y8" s="12" t="n">
         <v>4809738</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA8" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>36MJPMZ</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -1655,29 +1719,40 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="R9" s="12" t="n">
+        <v>3243786</v>
+      </c>
+      <c r="S9" s="13" t="n"/>
+      <c r="T9" s="12" t="n">
         <v>18024460</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U9" s="12" t="n">
         <v>160324181</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9" s="12" t="n">
         <v>6473651</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="W9" s="13" t="n"/>
+      <c r="X9" s="13" t="n"/>
+      <c r="Y9" s="12" t="n">
         <v>4835726</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA9" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>VYV5QZQ</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -1761,30 +1836,38 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="R10" s="12" t="n">
         <v>3241022</v>
       </c>
-      <c r="T10" t="n">
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="12" t="n">
         <v>17965050</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U10" s="12" t="n">
         <v>159932593</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10" s="12" t="n">
         <v>6199860</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="W10" s="13" t="n"/>
+      <c r="X10" s="13" t="n"/>
+      <c r="Y10" s="12" t="n">
         <v>4811641</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
+          <t>5KNGB7G</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AA10" s="12" t="n">
+      <c r="AB10" t="n">
         <v>5</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -1870,24 +1953,29 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="R11" s="13" t="n"/>
+      <c r="S11" s="13" t="n"/>
+      <c r="T11" s="12" t="n">
         <v>18012988</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U11" s="12" t="n">
         <v>160425521</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V11" s="12" t="n">
         <v>6498326</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="W11" s="13" t="n"/>
+      <c r="X11" s="13" t="n"/>
+      <c r="Y11" s="13" t="n"/>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AA11" s="12" t="n">
+      <c r="AB11" t="n">
         <v>3</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>sg_events_venue_datetime</t>
         </is>
@@ -1973,26 +2061,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="R12" s="12" t="n">
+        <v>3305715</v>
+      </c>
+      <c r="S12" s="13" t="n"/>
+      <c r="T12" s="12" t="n">
         <v>18028951</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U12" s="12" t="n">
         <v>159955411</v>
       </c>
-      <c r="V12" t="n">
+      <c r="V12" s="12" t="n">
         <v>6368029</v>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA12" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W12" s="13" t="n"/>
+      <c r="X12" s="13" t="n"/>
+      <c r="Y12" s="13" t="n"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -2076,26 +2171,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="R13" s="12" t="n">
+        <v>3411070</v>
+      </c>
+      <c r="S13" s="13" t="n"/>
+      <c r="T13" s="12" t="n">
         <v>18127621</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U13" s="12" t="n">
         <v>160324460</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V13" s="12" t="n">
         <v>6482923</v>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA13" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W13" s="13" t="n"/>
+      <c r="X13" s="13" t="n"/>
+      <c r="Y13" s="13" t="n"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -2179,26 +2281,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="R14" s="12" t="n">
+        <v>3230772</v>
+      </c>
+      <c r="S14" s="13" t="n"/>
+      <c r="T14" s="12" t="n">
         <v>18024445</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U14" s="12" t="n">
         <v>160324383</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V14" s="12" t="n">
         <v>6369854</v>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA14" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W14" s="13" t="n"/>
+      <c r="X14" s="13" t="n"/>
+      <c r="Y14" s="13" t="n"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -2282,33 +2391,40 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R15" s="12" t="n">
         <v>3233867</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" s="12" t="n">
         <v>1335574</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" s="12" t="n">
         <v>17956743</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U15" s="12" t="n">
         <v>160067992</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V15" s="12" t="n">
         <v>6292262</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="W15" s="13" t="n"/>
+      <c r="X15" s="13" t="n"/>
+      <c r="Y15" s="12" t="n">
         <v>4833758</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
+          <t>KBYGBV2</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AA15" s="12" t="n">
+      <c r="AB15" t="n">
         <v>6</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date+gotickets_catalog_7d_pull</t>
         </is>
@@ -2394,26 +2510,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="R16" s="12" t="n">
+        <v>3241118</v>
+      </c>
+      <c r="S16" s="13" t="n"/>
+      <c r="T16" s="12" t="n">
         <v>17986060</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U16" s="12" t="n">
         <v>160060118</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V16" s="12" t="n">
         <v>6178999</v>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA16" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W16" s="13" t="n"/>
+      <c r="X16" s="13" t="n"/>
+      <c r="Y16" s="13" t="n"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -2497,26 +2620,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="R17" s="12" t="n">
+        <v>3374128</v>
+      </c>
+      <c r="S17" s="13" t="n"/>
+      <c r="T17" s="12" t="n">
         <v>18150134</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U17" s="12" t="n">
         <v>160379220</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V17" s="12" t="n">
         <v>6371814</v>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA17" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W17" s="13" t="n"/>
+      <c r="X17" s="13" t="n"/>
+      <c r="Y17" s="13" t="n"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -2600,29 +2730,40 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T18" t="n">
+      <c r="R18" s="12" t="n">
+        <v>3257923</v>
+      </c>
+      <c r="S18" s="13" t="n"/>
+      <c r="T18" s="12" t="n">
         <v>18012530</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U18" s="12" t="n">
         <v>160324269</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V18" s="12" t="n">
         <v>6316172</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="W18" s="13" t="n"/>
+      <c r="X18" s="13" t="n"/>
+      <c r="Y18" s="12" t="n">
         <v>4826842</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA18" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>M7Y2QEO</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -2706,29 +2847,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T19" t="n">
+      <c r="R19" s="12" t="n">
+        <v>3392398</v>
+      </c>
+      <c r="S19" s="13" t="n"/>
+      <c r="T19" s="12" t="n">
         <v>17965046</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U19" s="12" t="n">
         <v>160125590</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V19" s="12" t="n">
         <v>6473725</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="W19" s="13" t="n"/>
+      <c r="X19" s="13" t="n"/>
+      <c r="Y19" s="12" t="n">
         <v>4767940</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA19" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>ZQGPMJ7</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -2812,29 +2964,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T20" t="n">
+      <c r="R20" s="12" t="n">
+        <v>3238532</v>
+      </c>
+      <c r="S20" s="13" t="n"/>
+      <c r="T20" s="12" t="n">
         <v>17997467</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U20" s="12" t="n">
         <v>159927982</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V20" s="12" t="n">
         <v>6207018</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="W20" s="13" t="n"/>
+      <c r="X20" s="13" t="n"/>
+      <c r="Y20" s="12" t="n">
         <v>4768281</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA20" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>WQKDXDJ</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -2918,29 +3081,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T21" t="n">
+      <c r="R21" s="12" t="n">
+        <v>3292249</v>
+      </c>
+      <c r="S21" s="13" t="n"/>
+      <c r="T21" s="12" t="n">
         <v>17984355</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U21" s="12" t="n">
         <v>159926164</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V21" s="12" t="n">
         <v>6206529</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="W21" s="13" t="n"/>
+      <c r="X21" s="13" t="n"/>
+      <c r="Y21" s="12" t="n">
         <v>4809739</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA21" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>7P7JGDD</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -3024,26 +3198,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S22" t="n">
+      <c r="R22" s="12" t="n">
+        <v>3433352</v>
+      </c>
+      <c r="S22" s="12" t="n">
         <v>1609722</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T22" s="12" t="n">
         <v>18169350</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U22" s="12" t="n">
         <v>160206469</v>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA22" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
+      <c r="V22" s="13" t="n"/>
+      <c r="W22" s="13" t="n"/>
+      <c r="X22" s="13" t="n"/>
+      <c r="Y22" s="13" t="n"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -3127,29 +3308,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T23" t="n">
+      <c r="R23" s="12" t="n">
+        <v>3283497</v>
+      </c>
+      <c r="S23" s="13" t="n"/>
+      <c r="T23" s="12" t="n">
         <v>18024476</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U23" s="12" t="n">
         <v>160204370</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V23" s="12" t="n">
         <v>6024630</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="W23" s="13" t="n"/>
+      <c r="X23" s="13" t="n"/>
+      <c r="Y23" s="12" t="n">
         <v>4827025</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA23" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>Z5AAAGX</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -3233,30 +3425,38 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="R24" s="12" t="n">
         <v>3241020</v>
       </c>
-      <c r="T24" t="n">
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="12" t="n">
         <v>17965052</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U24" s="12" t="n">
         <v>160228473</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V24" s="12" t="n">
         <v>6199861</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="W24" s="13" t="n"/>
+      <c r="X24" s="13" t="n"/>
+      <c r="Y24" s="12" t="n">
         <v>4811642</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
+          <t>6ZB34W4</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AA24" s="12" t="n">
+      <c r="AB24" t="n">
         <v>5</v>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -3342,26 +3542,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T25" t="n">
+      <c r="R25" s="12" t="n">
+        <v>3258720</v>
+      </c>
+      <c r="S25" s="13" t="n"/>
+      <c r="T25" s="12" t="n">
         <v>18094058</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U25" s="12" t="n">
         <v>160201392</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V25" s="12" t="n">
         <v>6473150</v>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA25" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W25" s="13" t="n"/>
+      <c r="X25" s="13" t="n"/>
+      <c r="Y25" s="13" t="n"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -3445,29 +3652,35 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T26" t="n">
+      <c r="R26" s="12" t="n">
+        <v>3400156</v>
+      </c>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="12" t="n">
         <v>18077238</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U26" s="12" t="n">
         <v>159997366</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V26" s="12" t="n">
         <v>6205546</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="W26" s="13" t="n"/>
+      <c r="X26" s="13" t="n"/>
+      <c r="Y26" s="12" t="n">
         <v>2.305954083573142e+18</v>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA26" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -3551,26 +3764,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T27" t="n">
+      <c r="R27" s="12" t="n">
+        <v>3291900</v>
+      </c>
+      <c r="S27" s="13" t="n"/>
+      <c r="T27" s="12" t="n">
         <v>18028953</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U27" s="12" t="n">
         <v>159955419</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V27" s="12" t="n">
         <v>6368033</v>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA27" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W27" s="13" t="n"/>
+      <c r="X27" s="13" t="n"/>
+      <c r="Y27" s="13" t="n"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -3654,26 +3874,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T28" t="n">
+      <c r="R28" s="12" t="n">
+        <v>3405791</v>
+      </c>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="12" t="n">
         <v>17971632</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U28" s="12" t="n">
         <v>160109236</v>
       </c>
-      <c r="V28" t="n">
+      <c r="V28" s="12" t="n">
         <v>6429659</v>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA28" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W28" s="13" t="n"/>
+      <c r="X28" s="13" t="n"/>
+      <c r="Y28" s="13" t="n"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -3757,26 +3984,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T29" t="n">
+      <c r="R29" s="12" t="n">
+        <v>3428106</v>
+      </c>
+      <c r="S29" s="13" t="n"/>
+      <c r="T29" s="12" t="n">
         <v>18147714</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U29" s="12" t="n">
         <v>160416796</v>
       </c>
-      <c r="V29" t="n">
+      <c r="V29" s="12" t="n">
         <v>6802467</v>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA29" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime+sh_performer_events</t>
+      <c r="W29" s="13" t="n"/>
+      <c r="X29" s="13" t="n"/>
+      <c r="Y29" s="13" t="n"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -3860,30 +4094,38 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R30" s="12" t="n">
         <v>3231484</v>
       </c>
-      <c r="T30" t="n">
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="12" t="n">
         <v>17936235</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U30" s="12" t="n">
         <v>159927900</v>
       </c>
-      <c r="V30" t="n">
+      <c r="V30" s="12" t="n">
         <v>6169427</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="W30" s="13" t="n"/>
+      <c r="X30" s="13" t="n"/>
+      <c r="Y30" s="12" t="n">
         <v>4772196</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
+          <t>MK5O4ZM</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AA30" s="12" t="n">
+      <c r="AB30" t="n">
         <v>5</v>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -3969,30 +4211,38 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R31" s="12" t="n">
         <v>3241019</v>
       </c>
-      <c r="T31" t="n">
+      <c r="S31" s="13" t="n"/>
+      <c r="T31" s="12" t="n">
         <v>18033318</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U31" s="12" t="n">
         <v>159996524</v>
       </c>
-      <c r="V31" t="n">
+      <c r="V31" s="12" t="n">
         <v>6206978</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="W31" s="13" t="n"/>
+      <c r="X31" s="13" t="n"/>
+      <c r="Y31" s="12" t="n">
         <v>4834989</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
+          <t>4B67WQJ</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AA31" s="12" t="n">
+      <c r="AB31" t="n">
         <v>5</v>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -4078,23 +4328,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T32" t="n">
+      <c r="R32" s="12" t="n">
+        <v>3188803</v>
+      </c>
+      <c r="S32" s="13" t="n"/>
+      <c r="T32" s="12" t="n">
         <v>18033447</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U32" s="12" t="n">
         <v>159996706</v>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA32" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>sg_canonical_opponent_date+sh_performer_events</t>
+      <c r="V32" s="13" t="n"/>
+      <c r="W32" s="13" t="n"/>
+      <c r="X32" s="13" t="n"/>
+      <c r="Y32" s="13" t="n"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sg_canonical_opponent_date+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -4178,26 +4436,38 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T33" t="n">
+      <c r="R33" s="12" t="n">
+        <v>3241117</v>
+      </c>
+      <c r="S33" s="13" t="n"/>
+      <c r="T33" s="12" t="n">
         <v>17986062</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U33" s="12" t="n">
         <v>160060119</v>
       </c>
-      <c r="V33" t="n">
+      <c r="V33" s="12" t="n">
         <v>6179000</v>
       </c>
+      <c r="W33" s="13" t="n"/>
+      <c r="X33" s="13" t="n"/>
+      <c r="Y33" s="13" t="n"/>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA33" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date+sg_events_paciolan_link</t>
+          <t>SYS-cbc4849cee</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -4281,29 +4551,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T34" t="n">
+      <c r="R34" s="12" t="n">
+        <v>3292250</v>
+      </c>
+      <c r="S34" s="13" t="n"/>
+      <c r="T34" s="12" t="n">
         <v>17984354</v>
       </c>
-      <c r="U34" t="n">
+      <c r="U34" s="12" t="n">
         <v>159926163</v>
       </c>
-      <c r="V34" t="n">
+      <c r="V34" s="12" t="n">
         <v>6206528</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="W34" s="13" t="n"/>
+      <c r="X34" s="13" t="n"/>
+      <c r="Y34" s="12" t="n">
         <v>4809740</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA34" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>WQ3ZMN6</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -4383,27 +4664,36 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T35" t="n">
+      <c r="R35" s="13" t="n"/>
+      <c r="S35" s="13" t="n"/>
+      <c r="T35" s="12" t="n">
         <v>17984354</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U35" s="12" t="n">
         <v>159926163</v>
       </c>
-      <c r="V35" t="n">
+      <c r="V35" s="12" t="n">
         <v>6206528</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="W35" s="13" t="n"/>
+      <c r="X35" s="13" t="n"/>
+      <c r="Y35" s="12" t="n">
         <v>4809740</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
+          <t>WQ3ZMN6</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
           <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AA35" s="13" t="n">
+      <c r="AB35" t="n">
         <v>4</v>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>addon_parent_game(126:F26:03)</t>
         </is>
@@ -4489,29 +4779,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T36" t="n">
+      <c r="R36" s="12" t="n">
+        <v>3244108</v>
+      </c>
+      <c r="S36" s="13" t="n"/>
+      <c r="T36" s="12" t="n">
         <v>18035333</v>
       </c>
-      <c r="U36" t="n">
+      <c r="U36" s="12" t="n">
         <v>159927978</v>
       </c>
-      <c r="V36" t="n">
+      <c r="V36" s="12" t="n">
         <v>6205008</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="W36" s="13" t="n"/>
+      <c r="X36" s="13" t="n"/>
+      <c r="Y36" s="12" t="n">
         <v>4768250</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA36" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>PGOO239</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -4595,26 +4896,38 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T37" t="n">
+      <c r="R37" s="12" t="n">
+        <v>3282210</v>
+      </c>
+      <c r="S37" s="13" t="n"/>
+      <c r="T37" s="12" t="n">
         <v>18024478</v>
       </c>
-      <c r="U37" t="n">
+      <c r="U37" s="12" t="n">
         <v>160204385</v>
       </c>
-      <c r="V37" t="n">
+      <c r="V37" s="12" t="n">
         <v>6303970</v>
       </c>
+      <c r="W37" s="13" t="n"/>
+      <c r="X37" s="13" t="n"/>
+      <c r="Y37" s="13" t="n"/>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA37" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>34MYQZZ</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -4698,26 +5011,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T38" t="n">
+      <c r="R38" s="12" t="n">
+        <v>3405808</v>
+      </c>
+      <c r="S38" s="13" t="n"/>
+      <c r="T38" s="12" t="n">
         <v>18176904</v>
       </c>
-      <c r="U38" t="n">
+      <c r="U38" s="12" t="n">
         <v>160379439</v>
       </c>
-      <c r="V38" t="n">
+      <c r="V38" s="12" t="n">
         <v>6482925</v>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA38" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W38" s="13" t="n"/>
+      <c r="X38" s="13" t="n"/>
+      <c r="Y38" s="13" t="n"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -4801,23 +5121,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T39" t="n">
+      <c r="R39" s="12" t="n">
+        <v>3320459</v>
+      </c>
+      <c r="S39" s="13" t="n"/>
+      <c r="T39" s="12" t="n">
         <v>18147716</v>
       </c>
-      <c r="U39" t="n">
+      <c r="U39" s="12" t="n">
         <v>160203438</v>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA39" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>sg_canonical_opponent_date+sg_links_sh</t>
+      <c r="V39" s="13" t="n"/>
+      <c r="W39" s="13" t="n"/>
+      <c r="X39" s="13" t="n"/>
+      <c r="Y39" s="13" t="n"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sg_canonical_opponent_date+sg_links_sh+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -4901,29 +5229,40 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T40" t="n">
+      <c r="R40" s="12" t="n">
+        <v>3290889</v>
+      </c>
+      <c r="S40" s="13" t="n"/>
+      <c r="T40" s="12" t="n">
         <v>17962246</v>
       </c>
-      <c r="U40" t="n">
+      <c r="U40" s="12" t="n">
         <v>159927901</v>
       </c>
-      <c r="V40" t="n">
+      <c r="V40" s="12" t="n">
         <v>6169435</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="W40" s="13" t="n"/>
+      <c r="X40" s="13" t="n"/>
+      <c r="Y40" s="12" t="n">
         <v>4772197</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA40" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>XQVO2P3</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -5007,26 +5346,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T41" t="n">
+      <c r="R41" s="12" t="n">
+        <v>3348484</v>
+      </c>
+      <c r="S41" s="13" t="n"/>
+      <c r="T41" s="12" t="n">
         <v>18069009</v>
       </c>
-      <c r="U41" t="n">
+      <c r="U41" s="12" t="n">
         <v>160479695</v>
       </c>
-      <c r="V41" t="n">
+      <c r="V41" s="12" t="n">
         <v>6205783</v>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA41" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W41" s="13" t="n"/>
+      <c r="X41" s="13" t="n"/>
+      <c r="Y41" s="13" t="n"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -5110,26 +5456,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T42" t="n">
+      <c r="R42" s="12" t="n">
+        <v>3352338</v>
+      </c>
+      <c r="S42" s="13" t="n"/>
+      <c r="T42" s="12" t="n">
         <v>18150136</v>
       </c>
-      <c r="U42" t="n">
+      <c r="U42" s="12" t="n">
         <v>160379251</v>
       </c>
-      <c r="V42" t="n">
+      <c r="V42" s="12" t="n">
         <v>6371816</v>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA42" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W42" s="13" t="n"/>
+      <c r="X42" s="13" t="n"/>
+      <c r="Y42" s="13" t="n"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -5213,29 +5566,35 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T43" t="n">
+      <c r="R43" s="12" t="n">
+        <v>3215527</v>
+      </c>
+      <c r="S43" s="13" t="n"/>
+      <c r="T43" s="12" t="n">
         <v>18093824</v>
       </c>
-      <c r="U43" t="n">
+      <c r="U43" s="12" t="n">
         <v>159997341</v>
       </c>
-      <c r="V43" t="n">
+      <c r="V43" s="12" t="n">
         <v>6296797</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="W43" s="13" t="n"/>
+      <c r="X43" s="13" t="n"/>
+      <c r="Y43" s="12" t="n">
         <v>2.305954083573273e+18</v>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA43" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -5319,30 +5678,38 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R44" t="n">
+      <c r="R44" s="12" t="n">
         <v>3289280</v>
       </c>
-      <c r="T44" t="n">
+      <c r="S44" s="13" t="n"/>
+      <c r="T44" s="12" t="n">
         <v>17965054</v>
       </c>
-      <c r="U44" t="n">
+      <c r="U44" s="12" t="n">
         <v>160228480</v>
       </c>
-      <c r="V44" t="n">
+      <c r="V44" s="12" t="n">
         <v>6474958</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="W44" s="13" t="n"/>
+      <c r="X44" s="13" t="n"/>
+      <c r="Y44" s="12" t="n">
         <v>4811643</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
+          <t>63DDB2Y</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AA44" s="12" t="n">
+      <c r="AB44" t="n">
         <v>5</v>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -5424,29 +5791,35 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="S45" t="n">
+      <c r="R45" s="12" t="n">
+        <v>3411020</v>
+      </c>
+      <c r="S45" s="12" t="n">
         <v>1558273</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T45" s="12" t="n">
         <v>18147684</v>
       </c>
-      <c r="U45" t="n">
+      <c r="U45" s="12" t="n">
         <v>160059769</v>
       </c>
-      <c r="V45" t="n">
+      <c r="V45" s="12" t="n">
         <v>6552184</v>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA45" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
+      <c r="W45" s="13" t="n"/>
+      <c r="X45" s="13" t="n"/>
+      <c r="Y45" s="13" t="n"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -5530,24 +5903,29 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S46" t="n">
+      <c r="R46" s="13" t="n"/>
+      <c r="S46" s="12" t="n">
         <v>1722872</v>
       </c>
-      <c r="T46" t="n">
+      <c r="T46" s="12" t="n">
         <v>18208488</v>
       </c>
-      <c r="U46" t="n">
+      <c r="U46" s="12" t="n">
         <v>161208192</v>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="V46" s="13" t="n"/>
+      <c r="W46" s="13" t="n"/>
+      <c r="X46" s="13" t="n"/>
+      <c r="Y46" s="13" t="n"/>
+      <c r="AA46" t="inlineStr">
         <is>
           <t>GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
-      <c r="AA46" s="12" t="n">
+      <c r="AB46" t="n">
         <v>3</v>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>gotickets_opponent_date+sg_events_paciolan_link</t>
         </is>
@@ -5633,29 +6011,35 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S47" t="n">
+      <c r="R47" s="12" t="n">
+        <v>3373063</v>
+      </c>
+      <c r="S47" s="12" t="n">
         <v>1535537</v>
       </c>
-      <c r="T47" t="n">
+      <c r="T47" s="12" t="n">
         <v>18012990</v>
       </c>
-      <c r="U47" t="n">
+      <c r="U47" s="12" t="n">
         <v>160238815</v>
       </c>
-      <c r="V47" t="n">
+      <c r="V47" s="12" t="n">
         <v>6498337</v>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA47" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
+      <c r="W47" s="13" t="n"/>
+      <c r="X47" s="13" t="n"/>
+      <c r="Y47" s="13" t="n"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -5735,29 +6119,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T48" t="n">
+      <c r="R48" s="12" t="n">
+        <v>3219684</v>
+      </c>
+      <c r="S48" s="13" t="n"/>
+      <c r="T48" s="12" t="n">
         <v>18033350</v>
       </c>
-      <c r="U48" t="n">
+      <c r="U48" s="12" t="n">
         <v>160418583</v>
       </c>
-      <c r="V48" t="n">
+      <c r="V48" s="12" t="n">
         <v>6317771</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="W48" s="13" t="n"/>
+      <c r="X48" s="13" t="n"/>
+      <c r="Y48" s="12" t="n">
         <v>4833771</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA48" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date+td_events_sg_links</t>
+          <t>GXAK3W9</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+td_events_sg_links+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -5837,26 +6232,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T49" t="n">
+      <c r="R49" s="12" t="n">
+        <v>3261229</v>
+      </c>
+      <c r="S49" s="13" t="n"/>
+      <c r="T49" s="12" t="n">
         <v>18094060</v>
       </c>
-      <c r="U49" t="n">
+      <c r="U49" s="12" t="n">
         <v>160212608</v>
       </c>
-      <c r="V49" t="n">
+      <c r="V49" s="12" t="n">
         <v>6473129</v>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA49" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W49" s="13" t="n"/>
+      <c r="X49" s="13" t="n"/>
+      <c r="Y49" s="13" t="n"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB49" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -5936,26 +6338,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T50" t="n">
+      <c r="R50" s="12" t="n">
+        <v>3336180</v>
+      </c>
+      <c r="S50" s="13" t="n"/>
+      <c r="T50" s="12" t="n">
         <v>18147718</v>
       </c>
-      <c r="U50" t="n">
+      <c r="U50" s="12" t="n">
         <v>160059827</v>
       </c>
-      <c r="V50" t="n">
+      <c r="V50" s="12" t="n">
         <v>6206980</v>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA50" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="W50" s="13" t="n"/>
+      <c r="X50" s="13" t="n"/>
+      <c r="Y50" s="13" t="n"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB50" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -6039,26 +6448,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T51" t="n">
+      <c r="R51" s="12" t="n">
+        <v>3348485</v>
+      </c>
+      <c r="S51" s="13" t="n"/>
+      <c r="T51" s="12" t="n">
         <v>18041102</v>
       </c>
-      <c r="U51" t="n">
+      <c r="U51" s="12" t="n">
         <v>160479696</v>
       </c>
-      <c r="V51" t="n">
+      <c r="V51" s="12" t="n">
         <v>6205784</v>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA51" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W51" s="13" t="n"/>
+      <c r="X51" s="13" t="n"/>
+      <c r="Y51" s="13" t="n"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -6142,26 +6558,38 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T52" t="n">
+      <c r="R52" s="12" t="n">
+        <v>3320999</v>
+      </c>
+      <c r="S52" s="13" t="n"/>
+      <c r="T52" s="12" t="n">
         <v>18068939</v>
       </c>
-      <c r="U52" t="n">
+      <c r="U52" s="12" t="n">
         <v>160479651</v>
       </c>
-      <c r="V52" t="n">
+      <c r="V52" s="12" t="n">
         <v>6651178</v>
       </c>
+      <c r="W52" s="13" t="n"/>
+      <c r="X52" s="13" t="n"/>
+      <c r="Y52" s="13" t="n"/>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA52" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date+sg_events_paciolan_link</t>
+          <t>SYS-25e700352d</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB52" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -6241,26 +6669,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T53" t="n">
+      <c r="R53" s="12" t="n">
+        <v>3411023</v>
+      </c>
+      <c r="S53" s="13" t="n"/>
+      <c r="T53" s="12" t="n">
         <v>18150140</v>
       </c>
-      <c r="U53" t="n">
+      <c r="U53" s="12" t="n">
         <v>160686463</v>
       </c>
-      <c r="V53" t="n">
+      <c r="V53" s="12" t="n">
         <v>6783256</v>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA53" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W53" s="13" t="n"/>
+      <c r="X53" s="13" t="n"/>
+      <c r="Y53" s="13" t="n"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -6340,23 +6775,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T54" t="n">
+      <c r="R54" s="12" t="n">
+        <v>3188735</v>
+      </c>
+      <c r="S54" s="13" t="n"/>
+      <c r="T54" s="12" t="n">
         <v>18033444</v>
       </c>
-      <c r="U54" t="n">
+      <c r="U54" s="12" t="n">
         <v>159996705</v>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA54" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="V54" s="13" t="n"/>
+      <c r="W54" s="13" t="n"/>
+      <c r="X54" s="13" t="n"/>
+      <c r="Y54" s="13" t="n"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -6436,29 +6879,40 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T55" t="n">
+      <c r="R55" s="12" t="n">
+        <v>3241048</v>
+      </c>
+      <c r="S55" s="13" t="n"/>
+      <c r="T55" s="12" t="n">
         <v>18024488</v>
       </c>
-      <c r="U55" t="n">
+      <c r="U55" s="12" t="n">
         <v>159917330</v>
       </c>
-      <c r="V55" t="n">
+      <c r="V55" s="12" t="n">
         <v>6172480</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="W55" s="13" t="n"/>
+      <c r="X55" s="13" t="n"/>
+      <c r="Y55" s="12" t="n">
         <v>4827164</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA55" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>BPNX76P</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -6538,29 +6992,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T56" t="n">
+      <c r="R56" s="12" t="n">
+        <v>3156939</v>
+      </c>
+      <c r="S56" s="13" t="n"/>
+      <c r="T56" s="12" t="n">
         <v>17965048</v>
       </c>
-      <c r="U56" t="n">
+      <c r="U56" s="12" t="n">
         <v>160125607</v>
       </c>
-      <c r="V56" t="n">
+      <c r="V56" s="12" t="n">
         <v>6096061</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="W56" s="13" t="n"/>
+      <c r="X56" s="13" t="n"/>
+      <c r="Y56" s="12" t="n">
         <v>4739426</v>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA56" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>APVNOKQ</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -6640,29 +7105,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T57" t="n">
+      <c r="R57" s="12" t="n">
+        <v>3244119</v>
+      </c>
+      <c r="S57" s="13" t="n"/>
+      <c r="T57" s="12" t="n">
         <v>18035439</v>
       </c>
-      <c r="U57" t="n">
+      <c r="U57" s="12" t="n">
         <v>159926143</v>
       </c>
-      <c r="V57" t="n">
+      <c r="V57" s="12" t="n">
         <v>6170682</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="W57" s="13" t="n"/>
+      <c r="X57" s="13" t="n"/>
+      <c r="Y57" s="12" t="n">
         <v>4809742</v>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA57" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>K45OAVB</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -6742,26 +7218,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T58" t="n">
+      <c r="R58" s="12" t="n">
+        <v>3402399</v>
+      </c>
+      <c r="S58" s="13" t="n"/>
+      <c r="T58" s="12" t="n">
         <v>18024447</v>
       </c>
-      <c r="U58" t="n">
+      <c r="U58" s="12" t="n">
         <v>160324388</v>
       </c>
-      <c r="V58" t="n">
+      <c r="V58" s="12" t="n">
         <v>6556971</v>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA58" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W58" s="13" t="n"/>
+      <c r="X58" s="13" t="n"/>
+      <c r="Y58" s="13" t="n"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -6841,29 +7324,35 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="S59" t="n">
+      <c r="R59" s="12" t="n">
+        <v>3372302</v>
+      </c>
+      <c r="S59" s="12" t="n">
         <v>1558274</v>
       </c>
-      <c r="T59" t="n">
+      <c r="T59" s="12" t="n">
         <v>18147686</v>
       </c>
-      <c r="U59" t="n">
+      <c r="U59" s="12" t="n">
         <v>160059760</v>
       </c>
-      <c r="V59" t="n">
+      <c r="V59" s="12" t="n">
         <v>6823804</v>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA59" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
+      <c r="W59" s="13" t="n"/>
+      <c r="X59" s="13" t="n"/>
+      <c r="Y59" s="13" t="n"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB59" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -6947,26 +7436,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T60" t="n">
+      <c r="R60" s="12" t="n">
+        <v>3375179</v>
+      </c>
+      <c r="S60" s="13" t="n"/>
+      <c r="T60" s="12" t="n">
         <v>18012992</v>
       </c>
-      <c r="U60" t="n">
+      <c r="U60" s="12" t="n">
         <v>160231319</v>
       </c>
-      <c r="V60" t="n">
+      <c r="V60" s="12" t="n">
         <v>6498399</v>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA60" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="W60" s="13" t="n"/>
+      <c r="X60" s="13" t="n"/>
+      <c r="Y60" s="13" t="n"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB60" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -7050,32 +7546,37 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S61" t="n">
+      <c r="R61" s="12" t="n">
+        <v>3403880</v>
+      </c>
+      <c r="S61" s="12" t="n">
         <v>1437527</v>
       </c>
-      <c r="T61" t="n">
+      <c r="T61" s="12" t="n">
         <v>18077240</v>
       </c>
-      <c r="U61" t="n">
+      <c r="U61" s="12" t="n">
         <v>159997368</v>
       </c>
-      <c r="V61" t="n">
+      <c r="V61" s="12" t="n">
         <v>6297179</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="W61" s="13" t="n"/>
+      <c r="X61" s="13" t="n"/>
+      <c r="Y61" s="12" t="n">
         <v>2.305954083573339e+18</v>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA61" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB61" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -7159,26 +7660,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T62" t="n">
+      <c r="R62" s="12" t="n">
+        <v>3305716</v>
+      </c>
+      <c r="S62" s="13" t="n"/>
+      <c r="T62" s="12" t="n">
         <v>18028955</v>
       </c>
-      <c r="U62" t="n">
+      <c r="U62" s="12" t="n">
         <v>159955430</v>
       </c>
-      <c r="V62" t="n">
+      <c r="V62" s="12" t="n">
         <v>6368040</v>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA62" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W62" s="13" t="n"/>
+      <c r="X62" s="13" t="n"/>
+      <c r="Y62" s="13" t="n"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB62" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -7262,26 +7770,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T63" t="n">
+      <c r="R63" s="12" t="n">
+        <v>3405781</v>
+      </c>
+      <c r="S63" s="13" t="n"/>
+      <c r="T63" s="12" t="n">
         <v>17971634</v>
       </c>
-      <c r="U63" t="n">
+      <c r="U63" s="12" t="n">
         <v>160106809</v>
       </c>
-      <c r="V63" t="n">
+      <c r="V63" s="12" t="n">
         <v>6429661</v>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA63" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W63" s="13" t="n"/>
+      <c r="X63" s="13" t="n"/>
+      <c r="Y63" s="13" t="n"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB63" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -7361,26 +7876,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T64" t="n">
+      <c r="R64" s="12" t="n">
+        <v>3411071</v>
+      </c>
+      <c r="S64" s="13" t="n"/>
+      <c r="T64" s="12" t="n">
         <v>18176907</v>
       </c>
-      <c r="U64" t="n">
+      <c r="U64" s="12" t="n">
         <v>160686057</v>
       </c>
-      <c r="V64" t="n">
+      <c r="V64" s="12" t="n">
         <v>6783439</v>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA64" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W64" s="13" t="n"/>
+      <c r="X64" s="13" t="n"/>
+      <c r="Y64" s="13" t="n"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB64" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -7460,29 +7982,40 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T65" t="n">
+      <c r="R65" s="12" t="n">
+        <v>3231480</v>
+      </c>
+      <c r="S65" s="13" t="n"/>
+      <c r="T65" s="12" t="n">
         <v>18035548</v>
       </c>
-      <c r="U65" t="n">
+      <c r="U65" s="12" t="n">
         <v>159927892</v>
       </c>
-      <c r="V65" t="n">
+      <c r="V65" s="12" t="n">
         <v>6169440</v>
       </c>
-      <c r="Y65" t="n">
+      <c r="W65" s="13" t="n"/>
+      <c r="X65" s="13" t="n"/>
+      <c r="Y65" s="12" t="n">
         <v>4838321</v>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA65" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>PG5MJ29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -7566,26 +8099,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T66" t="n">
+      <c r="R66" s="12" t="n">
+        <v>3348463</v>
+      </c>
+      <c r="S66" s="13" t="n"/>
+      <c r="T66" s="12" t="n">
         <v>18069011</v>
       </c>
-      <c r="U66" t="n">
+      <c r="U66" s="12" t="n">
         <v>160479697</v>
       </c>
-      <c r="V66" t="n">
+      <c r="V66" s="12" t="n">
         <v>6651240</v>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA66" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W66" s="13" t="n"/>
+      <c r="X66" s="13" t="n"/>
+      <c r="Y66" s="13" t="n"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB66" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -7665,29 +8205,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T67" t="n">
+      <c r="R67" s="12" t="n">
+        <v>3244118</v>
+      </c>
+      <c r="S67" s="13" t="n"/>
+      <c r="T67" s="12" t="n">
         <v>18035349</v>
       </c>
-      <c r="U67" t="n">
+      <c r="U67" s="12" t="n">
         <v>159926144</v>
       </c>
-      <c r="V67" t="n">
+      <c r="V67" s="12" t="n">
         <v>6170684</v>
       </c>
-      <c r="Y67" t="n">
+      <c r="W67" s="13" t="n"/>
+      <c r="X67" s="13" t="n"/>
+      <c r="Y67" s="12" t="n">
         <v>4809741</v>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA67" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>K45OA2P</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -7771,26 +8322,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S68" t="n">
+      <c r="R68" s="12" t="n">
+        <v>3184321</v>
+      </c>
+      <c r="S68" s="12" t="n">
         <v>1286333</v>
       </c>
-      <c r="T68" t="n">
+      <c r="T68" s="12" t="n">
         <v>18169352</v>
       </c>
-      <c r="U68" t="n">
+      <c r="U68" s="12" t="n">
         <v>160427474</v>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA68" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
+      <c r="V68" s="13" t="n"/>
+      <c r="W68" s="13" t="n"/>
+      <c r="X68" s="13" t="n"/>
+      <c r="Y68" s="13" t="n"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -7870,29 +8428,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T69" t="n">
+      <c r="R69" s="12" t="n">
+        <v>3241111</v>
+      </c>
+      <c r="S69" s="13" t="n"/>
+      <c r="T69" s="12" t="n">
         <v>18024480</v>
       </c>
-      <c r="U69" t="n">
+      <c r="U69" s="12" t="n">
         <v>159917186</v>
       </c>
-      <c r="V69" t="n">
+      <c r="V69" s="12" t="n">
         <v>6172360</v>
       </c>
-      <c r="Y69" t="n">
+      <c r="W69" s="13" t="n"/>
+      <c r="X69" s="13" t="n"/>
+      <c r="Y69" s="12" t="n">
         <v>4836401</v>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA69" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>PG57EVW</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -7972,30 +8541,38 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R70" t="n">
+      <c r="R70" s="12" t="n">
         <v>3241024</v>
       </c>
-      <c r="T70" t="n">
+      <c r="S70" s="13" t="n"/>
+      <c r="T70" s="12" t="n">
         <v>18033319</v>
       </c>
-      <c r="U70" t="n">
+      <c r="U70" s="12" t="n">
         <v>159996527</v>
       </c>
-      <c r="V70" t="n">
+      <c r="V70" s="12" t="n">
         <v>6206976</v>
       </c>
-      <c r="Y70" t="n">
+      <c r="W70" s="13" t="n"/>
+      <c r="X70" s="13" t="n"/>
+      <c r="Y70" s="12" t="n">
         <v>4834990</v>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
+          <t>369O3WZ</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AA70" s="12" t="n">
+      <c r="AB70" t="n">
         <v>5</v>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -8077,26 +8654,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T71" t="n">
+      <c r="R71" s="12" t="n">
+        <v>3344850</v>
+      </c>
+      <c r="S71" s="13" t="n"/>
+      <c r="T71" s="12" t="n">
         <v>18147720</v>
       </c>
-      <c r="U71" t="n">
+      <c r="U71" s="12" t="n">
         <v>160059834</v>
       </c>
-      <c r="V71" t="n">
+      <c r="V71" s="12" t="n">
         <v>6823662</v>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA71" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="W71" s="13" t="n"/>
+      <c r="X71" s="13" t="n"/>
+      <c r="Y71" s="13" t="n"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -8180,32 +8764,37 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S72" t="n">
+      <c r="R72" s="12" t="n">
+        <v>3215461</v>
+      </c>
+      <c r="S72" s="12" t="n">
         <v>1437524</v>
       </c>
-      <c r="T72" t="n">
+      <c r="T72" s="12" t="n">
         <v>18093826</v>
       </c>
-      <c r="U72" t="n">
+      <c r="U72" s="12" t="n">
         <v>159997340</v>
       </c>
-      <c r="V72" t="n">
+      <c r="V72" s="12" t="n">
         <v>6296791</v>
       </c>
-      <c r="Y72" t="n">
+      <c r="W72" s="13" t="n"/>
+      <c r="X72" s="13" t="n"/>
+      <c r="Y72" s="12" t="n">
         <v>2.30595408357347e+18</v>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA72" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -8289,26 +8878,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T73" t="n">
+      <c r="R73" s="12" t="n">
+        <v>3386314</v>
+      </c>
+      <c r="S73" s="13" t="n"/>
+      <c r="T73" s="12" t="n">
         <v>18150142</v>
       </c>
-      <c r="U73" t="n">
+      <c r="U73" s="12" t="n">
         <v>160387041</v>
       </c>
-      <c r="V73" t="n">
+      <c r="V73" s="12" t="n">
         <v>6783269</v>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA73" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W73" s="13" t="n"/>
+      <c r="X73" s="13" t="n"/>
+      <c r="Y73" s="13" t="n"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -8392,26 +8988,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T74" t="n">
+      <c r="R74" s="12" t="n">
+        <v>3214788</v>
+      </c>
+      <c r="S74" s="13" t="n"/>
+      <c r="T74" s="12" t="n">
         <v>18094062</v>
       </c>
-      <c r="U74" t="n">
+      <c r="U74" s="12" t="n">
         <v>160021916</v>
       </c>
-      <c r="V74" t="n">
+      <c r="V74" s="12" t="n">
         <v>6297079</v>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA74" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W74" s="13" t="n"/>
+      <c r="X74" s="13" t="n"/>
+      <c r="Y74" s="13" t="n"/>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB74" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -8491,29 +9094,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T75" t="n">
+      <c r="R75" s="12" t="n">
+        <v>3241249</v>
+      </c>
+      <c r="S75" s="13" t="n"/>
+      <c r="T75" s="12" t="n">
         <v>18033437</v>
       </c>
-      <c r="U75" t="n">
+      <c r="U75" s="12" t="n">
         <v>159956994</v>
       </c>
-      <c r="V75" t="n">
+      <c r="V75" s="12" t="n">
         <v>6207021</v>
       </c>
-      <c r="Y75" t="n">
+      <c r="W75" s="13" t="n"/>
+      <c r="X75" s="13" t="n"/>
+      <c r="Y75" s="12" t="n">
         <v>4768283</v>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA75" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>6ZO9K94</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -8597,26 +9211,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S76" t="n">
+      <c r="R76" s="12" t="n">
+        <v>3433354</v>
+      </c>
+      <c r="S76" s="12" t="n">
         <v>1629864</v>
       </c>
-      <c r="T76" t="n">
+      <c r="T76" s="12" t="n">
         <v>18169354</v>
       </c>
-      <c r="U76" t="n">
+      <c r="U76" s="12" t="n">
         <v>160427482</v>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA76" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
+      <c r="V76" s="13" t="n"/>
+      <c r="W76" s="13" t="n"/>
+      <c r="X76" s="13" t="n"/>
+      <c r="Y76" s="13" t="n"/>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -8696,29 +9317,35 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="S77" t="n">
+      <c r="R77" s="12" t="n">
+        <v>3372305</v>
+      </c>
+      <c r="S77" s="12" t="n">
         <v>1558275</v>
       </c>
-      <c r="T77" t="n">
+      <c r="T77" s="12" t="n">
         <v>18147688</v>
       </c>
-      <c r="U77" t="n">
+      <c r="U77" s="12" t="n">
         <v>160752383</v>
       </c>
-      <c r="V77" t="n">
+      <c r="V77" s="12" t="n">
         <v>6823816</v>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA77" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_venue_datetime</t>
+      <c r="W77" s="13" t="n"/>
+      <c r="X77" s="13" t="n"/>
+      <c r="Y77" s="13" t="n"/>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -8802,24 +9429,29 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T78" t="n">
+      <c r="R78" s="13" t="n"/>
+      <c r="S78" s="13" t="n"/>
+      <c r="T78" s="12" t="n">
         <v>18012388</v>
       </c>
-      <c r="U78" t="n">
+      <c r="U78" s="12" t="n">
         <v>160285974</v>
       </c>
-      <c r="V78" t="n">
+      <c r="V78" s="12" t="n">
         <v>6529858</v>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="W78" s="13" t="n"/>
+      <c r="X78" s="13" t="n"/>
+      <c r="Y78" s="13" t="n"/>
+      <c r="AA78" t="inlineStr">
         <is>
           <t>SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AA78" s="12" t="n">
+      <c r="AB78" t="n">
         <v>3</v>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AC78" t="inlineStr">
         <is>
           <t>sg_events_paciolan_link</t>
         </is>
@@ -8901,29 +9533,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T79" t="n">
+      <c r="R79" s="12" t="n">
+        <v>3188644</v>
+      </c>
+      <c r="S79" s="13" t="n"/>
+      <c r="T79" s="12" t="n">
         <v>18033352</v>
       </c>
-      <c r="U79" t="n">
+      <c r="U79" s="12" t="n">
         <v>159996565</v>
       </c>
-      <c r="V79" t="n">
+      <c r="V79" s="12" t="n">
         <v>6209678</v>
       </c>
-      <c r="Y79" t="n">
+      <c r="W79" s="13" t="n"/>
+      <c r="X79" s="13" t="n"/>
+      <c r="Y79" s="12" t="n">
         <v>4833773</v>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA79" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>Y3OBZQV</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB79" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -9007,23 +9650,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T80" t="n">
+      <c r="R80" s="12" t="n">
+        <v>3305714</v>
+      </c>
+      <c r="S80" s="13" t="n"/>
+      <c r="T80" s="12" t="n">
         <v>18028959</v>
       </c>
-      <c r="U80" t="n">
+      <c r="U80" s="12" t="n">
         <v>159955440</v>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA80" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="V80" s="13" t="n"/>
+      <c r="W80" s="13" t="n"/>
+      <c r="X80" s="13" t="n"/>
+      <c r="Y80" s="13" t="n"/>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -9107,26 +9758,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T81" t="n">
+      <c r="R81" s="12" t="n">
+        <v>3321000</v>
+      </c>
+      <c r="S81" s="13" t="n"/>
+      <c r="T81" s="12" t="n">
         <v>18068940</v>
       </c>
-      <c r="U81" t="n">
+      <c r="U81" s="12" t="n">
         <v>160479652</v>
       </c>
-      <c r="V81" t="n">
+      <c r="V81" s="12" t="n">
         <v>6651180</v>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA81" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W81" s="13" t="n"/>
+      <c r="X81" s="13" t="n"/>
+      <c r="Y81" s="13" t="n"/>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -9206,29 +9864,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T82" t="n">
+      <c r="R82" s="12" t="n">
+        <v>3188624</v>
+      </c>
+      <c r="S82" s="13" t="n"/>
+      <c r="T82" s="12" t="n">
         <v>18033280</v>
       </c>
-      <c r="U82" t="n">
+      <c r="U82" s="12" t="n">
         <v>159996816</v>
       </c>
-      <c r="V82" t="n">
+      <c r="V82" s="12" t="n">
         <v>6209623</v>
       </c>
-      <c r="Y82" t="n">
+      <c r="W82" s="13" t="n"/>
+      <c r="X82" s="13" t="n"/>
+      <c r="Y82" s="12" t="n">
         <v>4767956</v>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA82" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>55BOEYM</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB82" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -9308,26 +9977,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T83" t="n">
+      <c r="R83" s="12" t="n">
+        <v>3243895</v>
+      </c>
+      <c r="S83" s="13" t="n"/>
+      <c r="T83" s="12" t="n">
         <v>18024449</v>
       </c>
-      <c r="U83" t="n">
+      <c r="U83" s="12" t="n">
         <v>159917034</v>
       </c>
-      <c r="V83" t="n">
+      <c r="V83" s="12" t="n">
         <v>6172353</v>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA83" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W83" s="13" t="n"/>
+      <c r="X83" s="13" t="n"/>
+      <c r="Y83" s="13" t="n"/>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB83" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -9407,29 +10083,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T84" t="n">
+      <c r="R84" s="12" t="n">
+        <v>3241108</v>
+      </c>
+      <c r="S84" s="13" t="n"/>
+      <c r="T84" s="12" t="n">
         <v>18024482</v>
       </c>
-      <c r="U84" t="n">
+      <c r="U84" s="12" t="n">
         <v>159917188</v>
       </c>
-      <c r="V84" t="n">
+      <c r="V84" s="12" t="n">
         <v>6172357</v>
       </c>
-      <c r="Y84" t="n">
+      <c r="W84" s="13" t="n"/>
+      <c r="X84" s="13" t="n"/>
+      <c r="Y84" s="12" t="n">
         <v>4827026</v>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA84" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>Y5V9NEN</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -9513,23 +10200,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T85" t="n">
+      <c r="R85" s="12" t="n">
+        <v>3375315</v>
+      </c>
+      <c r="S85" s="13" t="n"/>
+      <c r="T85" s="12" t="n">
         <v>18012994</v>
       </c>
-      <c r="U85" t="n">
+      <c r="U85" s="12" t="n">
         <v>160231330</v>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA85" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="V85" s="13" t="n"/>
+      <c r="W85" s="13" t="n"/>
+      <c r="X85" s="13" t="n"/>
+      <c r="Y85" s="13" t="n"/>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB85" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -9609,26 +10304,38 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T86" t="n">
+      <c r="R86" s="12" t="n">
+        <v>3188658</v>
+      </c>
+      <c r="S86" s="13" t="n"/>
+      <c r="T86" s="12" t="n">
         <v>18033351</v>
       </c>
-      <c r="U86" t="n">
+      <c r="U86" s="12" t="n">
         <v>159996563</v>
       </c>
-      <c r="V86" t="n">
+      <c r="V86" s="12" t="n">
         <v>6209669</v>
       </c>
+      <c r="W86" s="13" t="n"/>
+      <c r="X86" s="13" t="n"/>
+      <c r="Y86" s="13" t="n"/>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA86" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>AA43G5B</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB86" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -9708,26 +10415,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T87" t="n">
+      <c r="R87" s="12" t="n">
+        <v>3215551</v>
+      </c>
+      <c r="S87" s="13" t="n"/>
+      <c r="T87" s="12" t="n">
         <v>18094064</v>
       </c>
-      <c r="U87" t="n">
+      <c r="U87" s="12" t="n">
         <v>160021919</v>
       </c>
-      <c r="V87" t="n">
+      <c r="V87" s="12" t="n">
         <v>6297071</v>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA87" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W87" s="13" t="n"/>
+      <c r="X87" s="13" t="n"/>
+      <c r="Y87" s="13" t="n"/>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB87" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -9811,26 +10525,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T88" t="n">
+      <c r="R88" s="12" t="n">
+        <v>3405793</v>
+      </c>
+      <c r="S88" s="13" t="n"/>
+      <c r="T88" s="12" t="n">
         <v>17971636</v>
       </c>
-      <c r="U88" t="n">
+      <c r="U88" s="12" t="n">
         <v>160106945</v>
       </c>
-      <c r="V88" t="n">
+      <c r="V88" s="12" t="n">
         <v>6429657</v>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA88" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W88" s="13" t="n"/>
+      <c r="X88" s="13" t="n"/>
+      <c r="Y88" s="13" t="n"/>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB88" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -9910,26 +10631,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T89" t="n">
+      <c r="R89" s="12" t="n">
+        <v>3344854</v>
+      </c>
+      <c r="S89" s="13" t="n"/>
+      <c r="T89" s="12" t="n">
         <v>18147786</v>
       </c>
-      <c r="U89" t="n">
+      <c r="U89" s="12" t="n">
         <v>160059837</v>
       </c>
-      <c r="V89" t="n">
+      <c r="V89" s="12" t="n">
         <v>6823682</v>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA89" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="W89" s="13" t="n"/>
+      <c r="X89" s="13" t="n"/>
+      <c r="Y89" s="13" t="n"/>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB89" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -10009,29 +10737,40 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T90" t="n">
+      <c r="R90" s="12" t="n">
+        <v>3231483</v>
+      </c>
+      <c r="S90" s="13" t="n"/>
+      <c r="T90" s="12" t="n">
         <v>18035549</v>
       </c>
-      <c r="U90" t="n">
+      <c r="U90" s="12" t="n">
         <v>159927890</v>
       </c>
-      <c r="V90" t="n">
+      <c r="V90" s="12" t="n">
         <v>6169446</v>
       </c>
-      <c r="Y90" t="n">
+      <c r="W90" s="13" t="n"/>
+      <c r="X90" s="13" t="n"/>
+      <c r="Y90" s="12" t="n">
         <v>4838322</v>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA90" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>6ZMDYB7</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB90" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -10115,26 +10854,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T91" t="n">
+      <c r="R91" s="12" t="n">
+        <v>3348487</v>
+      </c>
+      <c r="S91" s="13" t="n"/>
+      <c r="T91" s="12" t="n">
         <v>18069013</v>
       </c>
-      <c r="U91" t="n">
+      <c r="U91" s="12" t="n">
         <v>160479699</v>
       </c>
-      <c r="V91" t="n">
+      <c r="V91" s="12" t="n">
         <v>6651242</v>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA91" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W91" s="13" t="n"/>
+      <c r="X91" s="13" t="n"/>
+      <c r="Y91" s="13" t="n"/>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB91" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -10214,23 +10960,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T92" t="n">
+      <c r="R92" s="12" t="n">
+        <v>3289430</v>
+      </c>
+      <c r="S92" s="13" t="n"/>
+      <c r="T92" s="12" t="n">
         <v>18033446</v>
       </c>
-      <c r="U92" t="n">
+      <c r="U92" s="12" t="n">
         <v>159996707</v>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA92" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="V92" s="13" t="n"/>
+      <c r="W92" s="13" t="n"/>
+      <c r="X92" s="13" t="n"/>
+      <c r="Y92" s="13" t="n"/>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB92" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -10310,29 +11064,40 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T93" t="n">
+      <c r="R93" s="12" t="n">
+        <v>3241049</v>
+      </c>
+      <c r="S93" s="13" t="n"/>
+      <c r="T93" s="12" t="n">
         <v>18024492</v>
       </c>
-      <c r="U93" t="n">
+      <c r="U93" s="12" t="n">
         <v>159917329</v>
       </c>
-      <c r="V93" t="n">
+      <c r="V93" s="12" t="n">
         <v>6172488</v>
       </c>
-      <c r="Y93" t="n">
+      <c r="W93" s="13" t="n"/>
+      <c r="X93" s="13" t="n"/>
+      <c r="Y93" s="12" t="n">
         <v>4827163</v>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA93" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>V6P9B2Q</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -10412,29 +11177,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T94" t="n">
+      <c r="R94" s="12" t="n">
+        <v>3188622</v>
+      </c>
+      <c r="S94" s="13" t="n"/>
+      <c r="T94" s="12" t="n">
         <v>18033281</v>
       </c>
-      <c r="U94" t="n">
+      <c r="U94" s="12" t="n">
         <v>159996813</v>
       </c>
-      <c r="V94" t="n">
+      <c r="V94" s="12" t="n">
         <v>6209621</v>
       </c>
-      <c r="Y94" t="n">
+      <c r="W94" s="13" t="n"/>
+      <c r="X94" s="13" t="n"/>
+      <c r="Y94" s="12" t="n">
         <v>4767957</v>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA94" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>6D5POJY</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB94" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -10514,29 +11290,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T95" t="n">
+      <c r="R95" s="12" t="n">
+        <v>3231495</v>
+      </c>
+      <c r="S95" s="13" t="n"/>
+      <c r="T95" s="12" t="n">
         <v>18035437</v>
       </c>
-      <c r="U95" t="n">
+      <c r="U95" s="12" t="n">
         <v>159918372</v>
       </c>
-      <c r="V95" t="n">
+      <c r="V95" s="12" t="n">
         <v>6166307</v>
       </c>
-      <c r="Y95" t="n">
+      <c r="W95" s="13" t="n"/>
+      <c r="X95" s="13" t="n"/>
+      <c r="Y95" s="12" t="n">
         <v>4844013</v>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA95" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>OOMOYZP</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB95" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -10616,29 +11403,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T96" t="n">
+      <c r="R96" s="12" t="n">
+        <v>3244121</v>
+      </c>
+      <c r="S96" s="13" t="n"/>
+      <c r="T96" s="12" t="n">
         <v>18035447</v>
       </c>
-      <c r="U96" t="n">
+      <c r="U96" s="12" t="n">
         <v>159926145</v>
       </c>
-      <c r="V96" t="n">
+      <c r="V96" s="12" t="n">
         <v>6170681</v>
       </c>
-      <c r="Y96" t="n">
+      <c r="W96" s="13" t="n"/>
+      <c r="X96" s="13" t="n"/>
+      <c r="Y96" s="12" t="n">
         <v>4809744</v>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA96" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>DPNZQXA</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB96" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -10718,30 +11516,38 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R97" t="n">
+      <c r="R97" s="12" t="n">
         <v>3241023</v>
       </c>
-      <c r="T97" t="n">
+      <c r="S97" s="13" t="n"/>
+      <c r="T97" s="12" t="n">
         <v>18033320</v>
       </c>
-      <c r="U97" t="n">
+      <c r="U97" s="12" t="n">
         <v>159996525</v>
       </c>
-      <c r="V97" t="n">
+      <c r="V97" s="12" t="n">
         <v>6206973</v>
       </c>
-      <c r="Y97" t="n">
+      <c r="W97" s="13" t="n"/>
+      <c r="X97" s="13" t="n"/>
+      <c r="Y97" s="12" t="n">
         <v>4834991</v>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
+          <t>K4EKY6B</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AA97" s="12" t="n">
+      <c r="AB97" t="n">
         <v>5</v>
       </c>
-      <c r="AB97" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -10827,21 +11633,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T98" t="n">
+      <c r="R98" s="13" t="n"/>
+      <c r="S98" s="13" t="n"/>
+      <c r="T98" s="12" t="n">
         <v>18012390</v>
       </c>
-      <c r="U98" t="n">
+      <c r="U98" s="12" t="n">
         <v>160418142</v>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="V98" s="13" t="n"/>
+      <c r="W98" s="13" t="n"/>
+      <c r="X98" s="13" t="n"/>
+      <c r="Y98" s="13" t="n"/>
+      <c r="AA98" t="inlineStr">
         <is>
           <t>SeatGeek, StubHub</t>
         </is>
       </c>
-      <c r="AA98" s="12" t="n">
+      <c r="AB98" t="n">
         <v>2</v>
       </c>
-      <c r="AB98" t="inlineStr">
+      <c r="AC98" t="inlineStr">
         <is>
           <t>sg_events_paciolan_link</t>
         </is>
@@ -10927,23 +11739,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T99" t="n">
+      <c r="R99" s="12" t="n">
+        <v>3374962</v>
+      </c>
+      <c r="S99" s="13" t="n"/>
+      <c r="T99" s="12" t="n">
         <v>18012996</v>
       </c>
-      <c r="U99" t="n">
+      <c r="U99" s="12" t="n">
         <v>160231338</v>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA99" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="V99" s="13" t="n"/>
+      <c r="W99" s="13" t="n"/>
+      <c r="X99" s="13" t="n"/>
+      <c r="Y99" s="13" t="n"/>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -11027,26 +11847,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T100" t="n">
+      <c r="R100" s="12" t="n">
+        <v>3405796</v>
+      </c>
+      <c r="S100" s="13" t="n"/>
+      <c r="T100" s="12" t="n">
         <v>17971638</v>
       </c>
-      <c r="U100" t="n">
+      <c r="U100" s="12" t="n">
         <v>160107010</v>
       </c>
-      <c r="V100" t="n">
+      <c r="V100" s="12" t="n">
         <v>6429653</v>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA100" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W100" s="13" t="n"/>
+      <c r="X100" s="13" t="n"/>
+      <c r="Y100" s="13" t="n"/>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB100" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -11126,26 +11953,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T101" t="n">
+      <c r="R101" s="12" t="n">
+        <v>3409552</v>
+      </c>
+      <c r="S101" s="13" t="n"/>
+      <c r="T101" s="12" t="n">
         <v>18176906</v>
       </c>
-      <c r="U101" t="n">
+      <c r="U101" s="12" t="n">
         <v>160712004</v>
       </c>
-      <c r="V101" t="n">
+      <c r="V101" s="12" t="n">
         <v>6783443</v>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA101" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W101" s="13" t="n"/>
+      <c r="X101" s="13" t="n"/>
+      <c r="Y101" s="13" t="n"/>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -11229,26 +12063,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T102" t="n">
+      <c r="R102" s="12" t="n">
+        <v>3372308</v>
+      </c>
+      <c r="S102" s="13" t="n"/>
+      <c r="T102" s="12" t="n">
         <v>18147690</v>
       </c>
-      <c r="U102" t="n">
+      <c r="U102" s="12" t="n">
         <v>160059758</v>
       </c>
-      <c r="V102" t="n">
+      <c r="V102" s="12" t="n">
         <v>6823826</v>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA102" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="W102" s="13" t="n"/>
+      <c r="X102" s="13" t="n"/>
+      <c r="Y102" s="13" t="n"/>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB102" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -11332,29 +12173,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T103" t="n">
+      <c r="R103" s="12" t="n">
+        <v>3250475</v>
+      </c>
+      <c r="S103" s="13" t="n"/>
+      <c r="T103" s="12" t="n">
         <v>18033353</v>
       </c>
-      <c r="U103" t="n">
+      <c r="U103" s="12" t="n">
         <v>160102222</v>
       </c>
-      <c r="V103" t="n">
+      <c r="V103" s="12" t="n">
         <v>6432387</v>
       </c>
-      <c r="Y103" t="n">
+      <c r="W103" s="13" t="n"/>
+      <c r="X103" s="13" t="n"/>
+      <c r="Y103" s="12" t="n">
         <v>4833775</v>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA103" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>D4DWYDA</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB103" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -11438,26 +12290,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T104" t="n">
+      <c r="R104" s="12" t="n">
+        <v>3320998</v>
+      </c>
+      <c r="S104" s="13" t="n"/>
+      <c r="T104" s="12" t="n">
         <v>18068941</v>
       </c>
-      <c r="U104" t="n">
+      <c r="U104" s="12" t="n">
         <v>160479653</v>
       </c>
-      <c r="V104" t="n">
+      <c r="V104" s="12" t="n">
         <v>6651182</v>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA104" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W104" s="13" t="n"/>
+      <c r="X104" s="13" t="n"/>
+      <c r="Y104" s="13" t="n"/>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -11537,26 +12396,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T105" t="n">
+      <c r="R105" s="12" t="n">
+        <v>3403984</v>
+      </c>
+      <c r="S105" s="13" t="n"/>
+      <c r="T105" s="12" t="n">
         <v>18150144</v>
       </c>
-      <c r="U105" t="n">
+      <c r="U105" s="12" t="n">
         <v>160686465</v>
       </c>
-      <c r="V105" t="n">
+      <c r="V105" s="12" t="n">
         <v>6783285</v>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA105" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W105" s="13" t="n"/>
+      <c r="X105" s="13" t="n"/>
+      <c r="Y105" s="13" t="n"/>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -11636,26 +12502,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S106" t="n">
+      <c r="R106" s="12" t="n">
+        <v>3402893</v>
+      </c>
+      <c r="S106" s="12" t="n">
         <v>1387473</v>
       </c>
-      <c r="T106" t="n">
+      <c r="T106" s="12" t="n">
         <v>17965066</v>
       </c>
-      <c r="U106" t="n">
+      <c r="U106" s="12" t="n">
         <v>160276830</v>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA106" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
+      <c r="V106" s="13" t="n"/>
+      <c r="W106" s="13" t="n"/>
+      <c r="X106" s="13" t="n"/>
+      <c r="Y106" s="13" t="n"/>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB106" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -11735,26 +12608,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T107" t="n">
+      <c r="R107" s="12" t="n">
+        <v>3243896</v>
+      </c>
+      <c r="S107" s="13" t="n"/>
+      <c r="T107" s="12" t="n">
         <v>18024451</v>
       </c>
-      <c r="U107" t="n">
+      <c r="U107" s="12" t="n">
         <v>159917031</v>
       </c>
-      <c r="V107" t="n">
+      <c r="V107" s="12" t="n">
         <v>6172354</v>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA107" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W107" s="13" t="n"/>
+      <c r="X107" s="13" t="n"/>
+      <c r="Y107" s="13" t="n"/>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB107" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -11834,26 +12714,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T108" t="n">
+      <c r="R108" s="12" t="n">
+        <v>3216347</v>
+      </c>
+      <c r="S108" s="13" t="n"/>
+      <c r="T108" s="12" t="n">
         <v>18094066</v>
       </c>
-      <c r="U108" t="n">
+      <c r="U108" s="12" t="n">
         <v>160021918</v>
       </c>
-      <c r="V108" t="n">
+      <c r="V108" s="12" t="n">
         <v>6297075</v>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA108" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W108" s="13" t="n"/>
+      <c r="X108" s="13" t="n"/>
+      <c r="Y108" s="13" t="n"/>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -11933,29 +12820,35 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T109" t="n">
+      <c r="R109" s="12" t="n">
+        <v>3215142</v>
+      </c>
+      <c r="S109" s="13" t="n"/>
+      <c r="T109" s="12" t="n">
         <v>18093828</v>
       </c>
-      <c r="U109" t="n">
+      <c r="U109" s="12" t="n">
         <v>159997343</v>
       </c>
-      <c r="V109" t="n">
+      <c r="V109" s="12" t="n">
         <v>6296787</v>
       </c>
-      <c r="Y109" t="n">
+      <c r="W109" s="13" t="n"/>
+      <c r="X109" s="13" t="n"/>
+      <c r="Y109" s="12" t="n">
         <v>2.305954083573535e+18</v>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA109" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB109" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -12039,23 +12932,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T110" t="n">
+      <c r="R110" s="12" t="n">
+        <v>3305718</v>
+      </c>
+      <c r="S110" s="13" t="n"/>
+      <c r="T110" s="12" t="n">
         <v>18028957</v>
       </c>
-      <c r="U110" t="n">
+      <c r="U110" s="12" t="n">
         <v>160357737</v>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA110" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="V110" s="13" t="n"/>
+      <c r="W110" s="13" t="n"/>
+      <c r="X110" s="13" t="n"/>
+      <c r="Y110" s="13" t="n"/>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -12135,29 +13036,40 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T111" t="n">
+      <c r="R111" s="12" t="n">
+        <v>3231482</v>
+      </c>
+      <c r="S111" s="13" t="n"/>
+      <c r="T111" s="12" t="n">
         <v>18035551</v>
       </c>
-      <c r="U111" t="n">
+      <c r="U111" s="12" t="n">
         <v>159927891</v>
       </c>
-      <c r="V111" t="n">
+      <c r="V111" s="12" t="n">
         <v>6169441</v>
       </c>
-      <c r="Y111" t="n">
+      <c r="W111" s="13" t="n"/>
+      <c r="X111" s="13" t="n"/>
+      <c r="Y111" s="12" t="n">
         <v>4838323</v>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA111" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>NZ5D9A6</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB111" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -12241,26 +13153,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest|diff_lasttwo</t>
         </is>
       </c>
-      <c r="T112" t="n">
+      <c r="R112" s="12" t="n">
+        <v>3372311</v>
+      </c>
+      <c r="S112" s="13" t="n"/>
+      <c r="T112" s="12" t="n">
         <v>18147692</v>
       </c>
-      <c r="U112" t="n">
+      <c r="U112" s="12" t="n">
         <v>160059759</v>
       </c>
-      <c r="V112" t="n">
+      <c r="V112" s="12" t="n">
         <v>6823838</v>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA112" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="W112" s="13" t="n"/>
+      <c r="X112" s="13" t="n"/>
+      <c r="Y112" s="13" t="n"/>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB112" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -12340,26 +13259,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T113" t="n">
+      <c r="R113" s="12" t="n">
+        <v>3344846</v>
+      </c>
+      <c r="S113" s="13" t="n"/>
+      <c r="T113" s="12" t="n">
         <v>18147788</v>
       </c>
-      <c r="U113" t="n">
+      <c r="U113" s="12" t="n">
         <v>160752729</v>
       </c>
-      <c r="V113" t="n">
+      <c r="V113" s="12" t="n">
         <v>6823708</v>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA113" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="W113" s="13" t="n"/>
+      <c r="X113" s="13" t="n"/>
+      <c r="Y113" s="13" t="n"/>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB113" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -12443,30 +13369,38 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R114" t="n">
+      <c r="R114" s="12" t="n">
         <v>3241021</v>
       </c>
-      <c r="T114" t="n">
+      <c r="S114" s="13" t="n"/>
+      <c r="T114" s="12" t="n">
         <v>18033321</v>
       </c>
-      <c r="U114" t="n">
+      <c r="U114" s="12" t="n">
         <v>159996526</v>
       </c>
-      <c r="V114" t="n">
+      <c r="V114" s="12" t="n">
         <v>6206972</v>
       </c>
-      <c r="Y114" t="n">
+      <c r="W114" s="13" t="n"/>
+      <c r="X114" s="13" t="n"/>
+      <c r="Y114" s="12" t="n">
         <v>4834992</v>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
+          <t>DPGW54A</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
-      <c r="AA114" s="12" t="n">
+      <c r="AB114" t="n">
         <v>5</v>
       </c>
-      <c r="AB114" t="inlineStr">
+      <c r="AC114" t="inlineStr">
         <is>
           <t>aq_hub_opponent_date</t>
         </is>
@@ -12548,26 +13482,33 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T115" t="n">
+      <c r="R115" s="12" t="n">
+        <v>3411022</v>
+      </c>
+      <c r="S115" s="13" t="n"/>
+      <c r="T115" s="12" t="n">
         <v>18150146</v>
       </c>
-      <c r="U115" t="n">
+      <c r="U115" s="12" t="n">
         <v>160686469</v>
       </c>
-      <c r="V115" t="n">
+      <c r="V115" s="12" t="n">
         <v>6783298</v>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA115" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W115" s="13" t="n"/>
+      <c r="X115" s="13" t="n"/>
+      <c r="Y115" s="13" t="n"/>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -12647,29 +13588,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T116" t="n">
+      <c r="R116" s="12" t="n">
+        <v>3188699</v>
+      </c>
+      <c r="S116" s="13" t="n"/>
+      <c r="T116" s="12" t="n">
         <v>18033283</v>
       </c>
-      <c r="U116" t="n">
+      <c r="U116" s="12" t="n">
         <v>159996812</v>
       </c>
-      <c r="V116" t="n">
+      <c r="V116" s="12" t="n">
         <v>6209619</v>
       </c>
-      <c r="Y116" t="n">
+      <c r="W116" s="13" t="n"/>
+      <c r="X116" s="13" t="n"/>
+      <c r="Y116" s="12" t="n">
         <v>4767955</v>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA116" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>Y3ONYX5</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB116" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -12749,29 +13701,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T117" t="n">
+      <c r="R117" s="12" t="n">
+        <v>3250476</v>
+      </c>
+      <c r="S117" s="13" t="n"/>
+      <c r="T117" s="12" t="n">
         <v>18033438</v>
       </c>
-      <c r="U117" t="n">
+      <c r="U117" s="12" t="n">
         <v>160102210</v>
       </c>
-      <c r="V117" t="n">
+      <c r="V117" s="12" t="n">
         <v>6207022</v>
       </c>
-      <c r="Y117" t="n">
+      <c r="W117" s="13" t="n"/>
+      <c r="X117" s="13" t="n"/>
+      <c r="Y117" s="12" t="n">
         <v>4768280</v>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA117" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>369WXW2</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB117" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -12855,26 +13818,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S118" t="n">
+      <c r="R118" s="12" t="n">
+        <v>3433355</v>
+      </c>
+      <c r="S118" s="12" t="n">
         <v>1629873</v>
       </c>
-      <c r="T118" t="n">
+      <c r="T118" s="12" t="n">
         <v>18169356</v>
       </c>
-      <c r="U118" t="n">
+      <c r="U118" s="12" t="n">
         <v>160427498</v>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA118" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
+      <c r="V118" s="13" t="n"/>
+      <c r="W118" s="13" t="n"/>
+      <c r="X118" s="13" t="n"/>
+      <c r="Y118" s="13" t="n"/>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB118" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -12954,29 +13924,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T119" t="n">
+      <c r="R119" s="12" t="n">
+        <v>3241110</v>
+      </c>
+      <c r="S119" s="13" t="n"/>
+      <c r="T119" s="12" t="n">
         <v>18024484</v>
       </c>
-      <c r="U119" t="n">
+      <c r="U119" s="12" t="n">
         <v>159917189</v>
       </c>
-      <c r="V119" t="n">
+      <c r="V119" s="12" t="n">
         <v>6172358</v>
       </c>
-      <c r="Y119" t="n">
+      <c r="W119" s="13" t="n"/>
+      <c r="X119" s="13" t="n"/>
+      <c r="Y119" s="12" t="n">
         <v>4836402</v>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA119" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>WQV629J</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB119" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -13056,29 +14037,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T120" t="n">
+      <c r="R120" s="12" t="n">
+        <v>3188627</v>
+      </c>
+      <c r="S120" s="13" t="n"/>
+      <c r="T120" s="12" t="n">
         <v>18033360</v>
       </c>
-      <c r="U120" t="n">
+      <c r="U120" s="12" t="n">
         <v>159996564</v>
       </c>
-      <c r="V120" t="n">
+      <c r="V120" s="12" t="n">
         <v>6209682</v>
       </c>
-      <c r="Y120" t="n">
+      <c r="W120" s="13" t="n"/>
+      <c r="X120" s="13" t="n"/>
+      <c r="Y120" s="12" t="n">
         <v>4833776</v>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA120" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>44MKXOD</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB120" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -13162,26 +14154,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T121" t="n">
+      <c r="R121" s="12" t="n">
+        <v>3305713</v>
+      </c>
+      <c r="S121" s="13" t="n"/>
+      <c r="T121" s="12" t="n">
         <v>18028961</v>
       </c>
-      <c r="U121" t="n">
+      <c r="U121" s="12" t="n">
         <v>159955445</v>
       </c>
-      <c r="V121" t="n">
+      <c r="V121" s="12" t="n">
         <v>6368052</v>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA121" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W121" s="13" t="n"/>
+      <c r="X121" s="13" t="n"/>
+      <c r="Y121" s="13" t="n"/>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -13265,26 +14264,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T122" t="n">
+      <c r="R122" s="12" t="n">
+        <v>3405784</v>
+      </c>
+      <c r="S122" s="13" t="n"/>
+      <c r="T122" s="12" t="n">
         <v>17971640</v>
       </c>
-      <c r="U122" t="n">
+      <c r="U122" s="12" t="n">
         <v>160106817</v>
       </c>
-      <c r="V122" t="n">
+      <c r="V122" s="12" t="n">
         <v>6429655</v>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA122" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W122" s="13" t="n"/>
+      <c r="X122" s="13" t="n"/>
+      <c r="Y122" s="13" t="n"/>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -13364,26 +14370,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T123" t="n">
+      <c r="R123" s="12" t="n">
+        <v>3411045</v>
+      </c>
+      <c r="S123" s="13" t="n"/>
+      <c r="T123" s="12" t="n">
         <v>18176909</v>
       </c>
-      <c r="U123" t="n">
+      <c r="U123" s="12" t="n">
         <v>160686058</v>
       </c>
-      <c r="V123" t="n">
+      <c r="V123" s="12" t="n">
         <v>6783447</v>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA123" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W123" s="13" t="n"/>
+      <c r="X123" s="13" t="n"/>
+      <c r="Y123" s="13" t="n"/>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -13467,26 +14480,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T124" t="n">
+      <c r="R124" s="12" t="n">
+        <v>3321004</v>
+      </c>
+      <c r="S124" s="13" t="n"/>
+      <c r="T124" s="12" t="n">
         <v>18069010</v>
       </c>
-      <c r="U124" t="n">
+      <c r="U124" s="12" t="n">
         <v>160479701</v>
       </c>
-      <c r="V124" t="n">
+      <c r="V124" s="12" t="n">
         <v>6651244</v>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA124" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="W124" s="13" t="n"/>
+      <c r="X124" s="13" t="n"/>
+      <c r="Y124" s="13" t="n"/>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB124" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -13570,23 +14590,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T125" t="n">
+      <c r="R125" s="12" t="n">
+        <v>3374422</v>
+      </c>
+      <c r="S125" s="13" t="n"/>
+      <c r="T125" s="12" t="n">
         <v>18012998</v>
       </c>
-      <c r="U125" t="n">
+      <c r="U125" s="12" t="n">
         <v>160230939</v>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA125" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="V125" s="13" t="n"/>
+      <c r="W125" s="13" t="n"/>
+      <c r="X125" s="13" t="n"/>
+      <c r="Y125" s="13" t="n"/>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -13670,26 +14698,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T126" t="n">
+      <c r="R126" s="12" t="n">
+        <v>3344853</v>
+      </c>
+      <c r="S126" s="13" t="n"/>
+      <c r="T126" s="12" t="n">
         <v>18147790</v>
       </c>
-      <c r="U126" t="n">
+      <c r="U126" s="12" t="n">
         <v>160059836</v>
       </c>
-      <c r="V126" t="n">
+      <c r="V126" s="12" t="n">
         <v>6823717</v>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA126" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="W126" s="13" t="n"/>
+      <c r="X126" s="13" t="n"/>
+      <c r="Y126" s="13" t="n"/>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB126" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -13769,29 +14804,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T127" t="n">
+      <c r="R127" s="12" t="n">
+        <v>3244120</v>
+      </c>
+      <c r="S127" s="13" t="n"/>
+      <c r="T127" s="12" t="n">
         <v>18035351</v>
       </c>
-      <c r="U127" t="n">
+      <c r="U127" s="12" t="n">
         <v>159926142</v>
       </c>
-      <c r="V127" t="n">
+      <c r="V127" s="12" t="n">
         <v>6170683</v>
       </c>
-      <c r="Y127" t="n">
+      <c r="W127" s="13" t="n"/>
+      <c r="X127" s="13" t="n"/>
+      <c r="Y127" s="12" t="n">
         <v>4809743</v>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA127" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>DPNZQ76</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB127" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -13871,23 +14917,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T128" t="n">
+      <c r="R128" s="12" t="n">
+        <v>3242970</v>
+      </c>
+      <c r="S128" s="13" t="n"/>
+      <c r="T128" s="12" t="n">
         <v>18024453</v>
       </c>
-      <c r="U128" t="n">
+      <c r="U128" s="12" t="n">
         <v>159917033</v>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA128" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="V128" s="13" t="n"/>
+      <c r="W128" s="13" t="n"/>
+      <c r="X128" s="13" t="n"/>
+      <c r="Y128" s="13" t="n"/>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -13967,29 +15021,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T129" t="n">
+      <c r="R129" s="12" t="n">
+        <v>3244107</v>
+      </c>
+      <c r="S129" s="13" t="n"/>
+      <c r="T129" s="12" t="n">
         <v>18035343</v>
       </c>
-      <c r="U129" t="n">
+      <c r="U129" s="12" t="n">
         <v>159918404</v>
       </c>
-      <c r="V129" t="n">
+      <c r="V129" s="12" t="n">
         <v>6166344</v>
       </c>
-      <c r="Y129" t="n">
+      <c r="W129" s="13" t="n"/>
+      <c r="X129" s="13" t="n"/>
+      <c r="Y129" s="12" t="n">
         <v>4844064</v>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA129" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>EQ5QW2Q</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB129" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -14073,26 +15138,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S130" t="n">
+      <c r="R130" s="12" t="n">
+        <v>3405825</v>
+      </c>
+      <c r="S130" s="12" t="n">
         <v>1629870</v>
       </c>
-      <c r="T130" t="n">
+      <c r="T130" s="12" t="n">
         <v>18169358</v>
       </c>
-      <c r="U130" t="n">
+      <c r="U130" s="12" t="n">
         <v>160427509</v>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>GoTickets, SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA130" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events</t>
+      <c r="V130" s="13" t="n"/>
+      <c r="W130" s="13" t="n"/>
+      <c r="X130" s="13" t="n"/>
+      <c r="Y130" s="13" t="n"/>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB130" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>gotickets_opponent_date+sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -14176,21 +15248,27 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T131" t="n">
+      <c r="R131" s="13" t="n"/>
+      <c r="S131" s="13" t="n"/>
+      <c r="T131" s="12" t="n">
         <v>18012392</v>
       </c>
-      <c r="U131" t="n">
+      <c r="U131" s="12" t="n">
         <v>160305642</v>
       </c>
-      <c r="Z131" t="inlineStr">
+      <c r="V131" s="13" t="n"/>
+      <c r="W131" s="13" t="n"/>
+      <c r="X131" s="13" t="n"/>
+      <c r="Y131" s="13" t="n"/>
+      <c r="AA131" t="inlineStr">
         <is>
           <t>SeatGeek, StubHub</t>
         </is>
       </c>
-      <c r="AA131" s="12" t="n">
+      <c r="AB131" t="n">
         <v>2</v>
       </c>
-      <c r="AB131" t="inlineStr">
+      <c r="AC131" t="inlineStr">
         <is>
           <t>sg_events_paciolan_link</t>
         </is>
@@ -14272,26 +15350,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T132" t="n">
+      <c r="R132" s="12" t="n">
+        <v>3214869</v>
+      </c>
+      <c r="S132" s="13" t="n"/>
+      <c r="T132" s="12" t="n">
         <v>18094071</v>
       </c>
-      <c r="U132" t="n">
+      <c r="U132" s="12" t="n">
         <v>160021917</v>
       </c>
-      <c r="V132" t="n">
+      <c r="V132" s="12" t="n">
         <v>6297077</v>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA132" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W132" s="13" t="n"/>
+      <c r="X132" s="13" t="n"/>
+      <c r="Y132" s="13" t="n"/>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB132" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -14371,29 +15456,35 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T133" t="n">
+      <c r="R133" s="12" t="n">
+        <v>3214107</v>
+      </c>
+      <c r="S133" s="13" t="n"/>
+      <c r="T133" s="12" t="n">
         <v>18093830</v>
       </c>
-      <c r="U133" t="n">
+      <c r="U133" s="12" t="n">
         <v>159997342</v>
       </c>
-      <c r="V133" t="n">
+      <c r="V133" s="12" t="n">
         <v>6296793</v>
       </c>
-      <c r="Y133" t="n">
+      <c r="W133" s="13" t="n"/>
+      <c r="X133" s="13" t="n"/>
+      <c r="Y133" s="12" t="n">
         <v>2.305954083573666e+18</v>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA133" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>sg_events_venue_datetime</t>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>sg_events_venue_datetime+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -14477,23 +15568,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T134" t="n">
+      <c r="R134" s="12" t="n">
+        <v>3305712</v>
+      </c>
+      <c r="S134" s="13" t="n"/>
+      <c r="T134" s="12" t="n">
         <v>18028963</v>
       </c>
-      <c r="U134" t="n">
+      <c r="U134" s="12" t="n">
         <v>160531089</v>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA134" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="V134" s="13" t="n"/>
+      <c r="W134" s="13" t="n"/>
+      <c r="X134" s="13" t="n"/>
+      <c r="Y134" s="13" t="n"/>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -14577,26 +15676,33 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T135" t="n">
+      <c r="R135" s="12" t="n">
+        <v>3343770</v>
+      </c>
+      <c r="S135" s="13" t="n"/>
+      <c r="T135" s="12" t="n">
         <v>18176908</v>
       </c>
-      <c r="U135" t="n">
+      <c r="U135" s="12" t="n">
         <v>160686141</v>
       </c>
-      <c r="V135" t="n">
+      <c r="V135" s="12" t="n">
         <v>6783457</v>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA135" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link</t>
+      <c r="W135" s="13" t="n"/>
+      <c r="X135" s="13" t="n"/>
+      <c r="Y135" s="13" t="n"/>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -14676,23 +15782,31 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T136" t="n">
+      <c r="R136" s="12" t="n">
+        <v>3348490</v>
+      </c>
+      <c r="S136" s="13" t="n"/>
+      <c r="T136" s="12" t="n">
         <v>18068942</v>
       </c>
-      <c r="U136" t="n">
+      <c r="U136" s="12" t="n">
         <v>160479655</v>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA136" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>opponent_tbd+sg_events_paciolan_link</t>
+      <c r="V136" s="13" t="n"/>
+      <c r="W136" s="13" t="n"/>
+      <c r="X136" s="13" t="n"/>
+      <c r="Y136" s="13" t="n"/>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>opponent_tbd+sg_events_paciolan_link+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -14772,23 +15886,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T137" t="n">
+      <c r="R137" s="12" t="n">
+        <v>3188751</v>
+      </c>
+      <c r="S137" s="13" t="n"/>
+      <c r="T137" s="12" t="n">
         <v>18033445</v>
       </c>
-      <c r="U137" t="n">
+      <c r="U137" s="12" t="n">
         <v>159996704</v>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA137" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>sg_events_paciolan_link+sh_performer_events</t>
+      <c r="V137" s="13" t="n"/>
+      <c r="W137" s="13" t="n"/>
+      <c r="X137" s="13" t="n"/>
+      <c r="Y137" s="13" t="n"/>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -14868,32 +15990,42 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="S138" t="n">
+      <c r="R138" s="12" t="n">
+        <v>3188704</v>
+      </c>
+      <c r="S138" s="12" t="n">
         <v>1377027</v>
       </c>
-      <c r="T138" t="n">
+      <c r="T138" s="12" t="n">
         <v>18033282</v>
       </c>
-      <c r="U138" t="n">
+      <c r="U138" s="12" t="n">
         <v>159996814</v>
       </c>
-      <c r="V138" t="n">
+      <c r="V138" s="12" t="n">
         <v>6209622</v>
       </c>
-      <c r="Y138" t="n">
+      <c r="W138" s="13" t="n"/>
+      <c r="X138" s="13" t="n"/>
+      <c r="Y138" s="12" t="n">
         <v>4767954</v>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA138" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date+gotickets_catalog_7d_pull</t>
+          <t>VZ3WVYX</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB138" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+gotickets_catalog_7d_pull+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -14973,26 +16105,38 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T139" t="n">
+      <c r="R139" s="12" t="n">
+        <v>3237288</v>
+      </c>
+      <c r="S139" s="13" t="n"/>
+      <c r="T139" s="12" t="n">
         <v>18033439</v>
       </c>
-      <c r="U139" t="n">
+      <c r="U139" s="12" t="n">
         <v>159956993</v>
       </c>
-      <c r="V139" t="n">
+      <c r="V139" s="12" t="n">
         <v>6207020</v>
       </c>
+      <c r="W139" s="13" t="n"/>
+      <c r="X139" s="13" t="n"/>
+      <c r="Y139" s="13" t="n"/>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
-        </is>
-      </c>
-      <c r="AA139" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>OO7G4GN</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+        </is>
+      </c>
+      <c r="AB139" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -15072,29 +16216,40 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T140" t="n">
+      <c r="R140" s="12" t="n">
+        <v>3241109</v>
+      </c>
+      <c r="S140" s="13" t="n"/>
+      <c r="T140" s="12" t="n">
         <v>18024486</v>
       </c>
-      <c r="U140" t="n">
+      <c r="U140" s="12" t="n">
         <v>159917187</v>
       </c>
-      <c r="V140" t="n">
+      <c r="V140" s="12" t="n">
         <v>6172359</v>
       </c>
-      <c r="Y140" t="n">
+      <c r="W140" s="13" t="n"/>
+      <c r="X140" s="13" t="n"/>
+      <c r="Y140" s="12" t="n">
         <v>4836403</v>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
-        </is>
-      </c>
-      <c r="AA140" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>aq_hub_opponent_date</t>
+          <t>MK57Y9O</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+        </is>
+      </c>
+      <c r="AB140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>aq_hub_opponent_date+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -15174,23 +16329,31 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="T141" t="n">
+      <c r="R141" s="12" t="n">
+        <v>3434001</v>
+      </c>
+      <c r="S141" s="13" t="n"/>
+      <c r="T141" s="12" t="n">
         <v>18069012</v>
       </c>
-      <c r="U141" t="n">
+      <c r="U141" s="12" t="n">
         <v>160479705</v>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>SeatGeek, StubHub</t>
-        </is>
-      </c>
-      <c r="AA141" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>opponent_tbd_flex+sg_events_paciolan_link+sh_performer_events</t>
+      <c r="V141" s="13" t="n"/>
+      <c r="W141" s="13" t="n"/>
+      <c r="X141" s="13" t="n"/>
+      <c r="Y141" s="13" t="n"/>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>Ticket Evolution, SeatGeek, StubHub</t>
+        </is>
+      </c>
+      <c r="AB141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>opponent_tbd_flex+sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
         </is>
       </c>
     </row>
@@ -15266,30 +16429,38 @@
           <t>blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R142" t="n">
+      <c r="R142" s="12" t="n">
         <v>3101506</v>
       </c>
-      <c r="S142" t="n">
+      <c r="S142" s="12" t="n">
         <v>1190236</v>
       </c>
-      <c r="T142" t="n">
+      <c r="T142" s="12" t="n">
         <v>17694063</v>
       </c>
-      <c r="U142" t="n">
+      <c r="U142" s="12" t="n">
         <v>159262247</v>
       </c>
-      <c r="V142" t="n">
+      <c r="V142" s="12" t="n">
         <v>5966797</v>
       </c>
+      <c r="W142" s="13" t="n"/>
+      <c r="X142" s="13" t="n"/>
+      <c r="Y142" s="13" t="n"/>
       <c r="Z142" t="inlineStr">
         <is>
+          <t>7P63X9D</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
           <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AA142" s="12" t="n">
+      <c r="AB142" t="n">
         <v>5</v>
       </c>
-      <c r="AB142" t="inlineStr">
+      <c r="AC142" t="inlineStr">
         <is>
           <t>venue_date_name_exact</t>
         </is>
@@ -15363,27 +16534,36 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R143" t="n">
+      <c r="R143" s="12" t="n">
         <v>3026271</v>
       </c>
-      <c r="T143" t="n">
+      <c r="S143" s="13" t="n"/>
+      <c r="T143" s="12" t="n">
         <v>17565134</v>
       </c>
-      <c r="U143" t="n">
+      <c r="U143" s="12" t="n">
         <v>158487337</v>
       </c>
-      <c r="V143" t="n">
+      <c r="V143" s="12" t="n">
         <v>5809770</v>
       </c>
+      <c r="W143" s="13" t="n"/>
+      <c r="X143" s="13" t="n"/>
+      <c r="Y143" s="13" t="n"/>
       <c r="Z143" t="inlineStr">
         <is>
+          <t>PGJDA73</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AA143" s="12" t="n">
+      <c r="AB143" t="n">
         <v>4</v>
       </c>
-      <c r="AB143" t="inlineStr">
+      <c r="AC143" t="inlineStr">
         <is>
           <t>day_level_zone_product</t>
         </is>
@@ -15457,27 +16637,36 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R144" t="n">
+      <c r="R144" s="12" t="n">
         <v>3026271</v>
       </c>
-      <c r="T144" t="n">
+      <c r="S144" s="13" t="n"/>
+      <c r="T144" s="12" t="n">
         <v>17565134</v>
       </c>
-      <c r="U144" t="n">
+      <c r="U144" s="12" t="n">
         <v>158487337</v>
       </c>
-      <c r="V144" t="n">
+      <c r="V144" s="12" t="n">
         <v>5809770</v>
       </c>
+      <c r="W144" s="13" t="n"/>
+      <c r="X144" s="13" t="n"/>
+      <c r="Y144" s="13" t="n"/>
       <c r="Z144" t="inlineStr">
         <is>
+          <t>PGJDA73</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AA144" s="12" t="n">
+      <c r="AB144" t="n">
         <v>4</v>
       </c>
-      <c r="AB144" t="inlineStr">
+      <c r="AC144" t="inlineStr">
         <is>
           <t>day_level_zone_product</t>
         </is>
@@ -15551,27 +16740,36 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R145" t="n">
+      <c r="R145" s="12" t="n">
         <v>3026272</v>
       </c>
-      <c r="T145" t="n">
+      <c r="S145" s="13" t="n"/>
+      <c r="T145" s="12" t="n">
         <v>17565136</v>
       </c>
-      <c r="U145" t="n">
+      <c r="U145" s="12" t="n">
         <v>158487348</v>
       </c>
-      <c r="V145" t="n">
+      <c r="V145" s="12" t="n">
         <v>5809771</v>
       </c>
+      <c r="W145" s="13" t="n"/>
+      <c r="X145" s="13" t="n"/>
+      <c r="Y145" s="13" t="n"/>
       <c r="Z145" t="inlineStr">
         <is>
+          <t>V6JQY9J</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AA145" s="12" t="n">
+      <c r="AB145" t="n">
         <v>4</v>
       </c>
-      <c r="AB145" t="inlineStr">
+      <c r="AC145" t="inlineStr">
         <is>
           <t>day_level_zone_product</t>
         </is>
@@ -15645,27 +16843,36 @@
           <t>blocks_0819_all|blocks_0819_latest|blocks_0821_latest</t>
         </is>
       </c>
-      <c r="R146" t="n">
+      <c r="R146" s="12" t="n">
         <v>3017608</v>
       </c>
-      <c r="T146" t="n">
+      <c r="S146" s="13" t="n"/>
+      <c r="T146" s="12" t="n">
         <v>17565120</v>
       </c>
-      <c r="U146" t="n">
+      <c r="U146" s="12" t="n">
         <v>158501986</v>
       </c>
-      <c r="V146" t="n">
+      <c r="V146" s="12" t="n">
         <v>5809736</v>
       </c>
+      <c r="W146" s="13" t="n"/>
+      <c r="X146" s="13" t="n"/>
+      <c r="Y146" s="13" t="n"/>
       <c r="Z146" t="inlineStr">
         <is>
+          <t>APYE67J</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
           <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
-      <c r="AA146" s="12" t="n">
+      <c r="AB146" t="n">
         <v>4</v>
       </c>
-      <c r="AB146" t="inlineStr">
+      <c r="AC146" t="inlineStr">
         <is>
           <t>venue_date_name_exact</t>
         </is>
@@ -15678,6 +16885,216 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Events mapped</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>of 145</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ticket Evolution</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>139</v>
+      </c>
+      <c r="C2" t="n">
+        <v>145</v>
+      </c>
+      <c r="D2" t="n">
+        <v>95.90000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GoTickets</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>145</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SeatGeek</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>145</v>
+      </c>
+      <c r="C4" t="n">
+        <v>145</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>StubHub</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>145</v>
+      </c>
+      <c r="C5" t="n">
+        <v>145</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vivid Seats</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>122</v>
+      </c>
+      <c r="C6" t="n">
+        <v>145</v>
+      </c>
+      <c r="D6" t="n">
+        <v>84.09999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TickPick</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>145</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gametime</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>145</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ticketmaster</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>54</v>
+      </c>
+      <c r="C9" t="n">
+        <v>145</v>
+      </c>
+      <c r="D9" t="n">
+        <v>37.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rows with &gt;= 1 source id</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>145</v>
+      </c>
+      <c r="C11" t="n">
+        <v>145</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Rows with &gt;= 3 source ids</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>143</v>
+      </c>
+      <c r="C12" t="n">
+        <v>145</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Average sources per row</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15905,7 +17322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16671,242 +18088,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>id column</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>events mapped</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>of total</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>coverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ticket Evolution</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>tevo_event_id</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D2" t="n">
-        <v>145</v>
-      </c>
-      <c r="E2" s="15" t="n">
-        <v>0.09660000000000001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>GoTickets</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>gotickets_event_id</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D3" t="n">
-        <v>145</v>
-      </c>
-      <c r="E3" s="15" t="n">
-        <v>0.1172</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SeatGeek</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>seatgeek_event_id</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>145</v>
-      </c>
-      <c r="D4" t="n">
-        <v>145</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>StubHub</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>stubhub_event_id</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>145</v>
-      </c>
-      <c r="D5" t="n">
-        <v>145</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Vivid Seats</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>vividseats_event_id</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>122</v>
-      </c>
-      <c r="D6" t="n">
-        <v>145</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.8414</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TickPick</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>tickpick_event_id</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>145</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gametime</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gametime_event_id</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>145</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ticketmaster</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ticketmaster_event_id</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>54</v>
-      </c>
-      <c r="D9" t="n">
-        <v>145</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.3724</v>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ANY source</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>145</v>
-      </c>
-      <c r="D11" t="n">
-        <v>145</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/evd_event_id_crosswalk_mapped.xlsx
+++ b/evd_event_id_crosswalk_mapped.xlsx
@@ -1036,7 +1036,9 @@
       <c r="R3" s="12" t="n">
         <v>3400622</v>
       </c>
-      <c r="S3" s="13" t="n"/>
+      <c r="S3" s="12" t="n">
+        <v>1435099</v>
+      </c>
       <c r="T3" s="12" t="n">
         <v>17965064</v>
       </c>
@@ -1051,15 +1053,15 @@
       <c r="Y3" s="13" t="n"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1148,9 @@
       <c r="R4" s="12" t="n">
         <v>3330200</v>
       </c>
-      <c r="S4" s="13" t="n"/>
+      <c r="S4" s="12" t="n">
+        <v>1464879</v>
+      </c>
       <c r="T4" s="12" t="n">
         <v>18024316</v>
       </c>
@@ -1168,15 +1172,15 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1267,9 @@
       <c r="R5" s="12" t="n">
         <v>3241119</v>
       </c>
-      <c r="S5" s="13" t="n"/>
+      <c r="S5" s="12" t="n">
+        <v>1373383</v>
+      </c>
       <c r="T5" s="12" t="n">
         <v>17986058</v>
       </c>
@@ -1278,15 +1284,15 @@
       <c r="Y5" s="13" t="n"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1379,9 @@
       <c r="R6" s="12" t="n">
         <v>3312472</v>
       </c>
-      <c r="S6" s="13" t="n"/>
+      <c r="S6" s="12" t="n">
+        <v>1369632</v>
+      </c>
       <c r="T6" s="12" t="n">
         <v>17936149</v>
       </c>
@@ -1395,15 +1403,15 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1498,9 @@
       <c r="R7" s="12" t="n">
         <v>3250473</v>
       </c>
-      <c r="S7" s="13" t="n"/>
+      <c r="S7" s="12" t="n">
+        <v>1335329</v>
+      </c>
       <c r="T7" s="12" t="n">
         <v>17997465</v>
       </c>
@@ -1510,15 +1520,15 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1615,9 @@
       <c r="R8" s="12" t="n">
         <v>3292251</v>
       </c>
-      <c r="S8" s="13" t="n"/>
+      <c r="S8" s="12" t="n">
+        <v>1287504</v>
+      </c>
       <c r="T8" s="12" t="n">
         <v>17984356</v>
       </c>
@@ -1627,15 +1639,15 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1734,9 @@
       <c r="R9" s="12" t="n">
         <v>3243786</v>
       </c>
-      <c r="S9" s="13" t="n"/>
+      <c r="S9" s="12" t="n">
+        <v>1447984</v>
+      </c>
       <c r="T9" s="12" t="n">
         <v>18024460</v>
       </c>
@@ -1744,15 +1758,15 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1853,9 @@
       <c r="R10" s="12" t="n">
         <v>3241022</v>
       </c>
-      <c r="S10" s="13" t="n"/>
+      <c r="S10" s="12" t="n">
+        <v>1356596</v>
+      </c>
       <c r="T10" s="12" t="n">
         <v>17965050</v>
       </c>
@@ -1861,15 +1877,15 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date</t>
+          <t>aq_hub_opponent_date+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1970,9 @@
         </is>
       </c>
       <c r="R11" s="13" t="n"/>
-      <c r="S11" s="13" t="n"/>
+      <c r="S11" s="12" t="n">
+        <v>1535536</v>
+      </c>
       <c r="T11" s="12" t="n">
         <v>18012988</v>
       </c>
@@ -1969,15 +1987,15 @@
       <c r="Y11" s="13" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
+          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime</t>
+          <t>sg_events_venue_datetime+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2082,9 @@
       <c r="R12" s="12" t="n">
         <v>3305715</v>
       </c>
-      <c r="S12" s="13" t="n"/>
+      <c r="S12" s="12" t="n">
+        <v>1348725</v>
+      </c>
       <c r="T12" s="12" t="n">
         <v>18028951</v>
       </c>
@@ -2079,15 +2099,15 @@
       <c r="Y12" s="13" t="n"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2194,9 @@
       <c r="R13" s="12" t="n">
         <v>3411070</v>
       </c>
-      <c r="S13" s="13" t="n"/>
+      <c r="S13" s="12" t="n">
+        <v>1526776</v>
+      </c>
       <c r="T13" s="12" t="n">
         <v>18127621</v>
       </c>
@@ -2189,15 +2211,15 @@
       <c r="Y13" s="13" t="n"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2306,9 @@
       <c r="R14" s="12" t="n">
         <v>3230772</v>
       </c>
-      <c r="S14" s="13" t="n"/>
+      <c r="S14" s="12" t="n">
+        <v>1376586</v>
+      </c>
       <c r="T14" s="12" t="n">
         <v>18024445</v>
       </c>
@@ -2299,15 +2323,15 @@
       <c r="Y14" s="13" t="n"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2537,9 @@
       <c r="R16" s="12" t="n">
         <v>3241118</v>
       </c>
-      <c r="S16" s="13" t="n"/>
+      <c r="S16" s="12" t="n">
+        <v>1368414</v>
+      </c>
       <c r="T16" s="12" t="n">
         <v>17986060</v>
       </c>
@@ -2528,15 +2554,15 @@
       <c r="Y16" s="13" t="n"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2649,9 @@
       <c r="R17" s="12" t="n">
         <v>3374128</v>
       </c>
-      <c r="S17" s="13" t="n"/>
+      <c r="S17" s="12" t="n">
+        <v>1521528</v>
+      </c>
       <c r="T17" s="12" t="n">
         <v>18150134</v>
       </c>
@@ -2638,15 +2666,15 @@
       <c r="Y17" s="13" t="n"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2761,9 @@
       <c r="R18" s="12" t="n">
         <v>3257923</v>
       </c>
-      <c r="S18" s="13" t="n"/>
+      <c r="S18" s="12" t="n">
+        <v>1425108</v>
+      </c>
       <c r="T18" s="12" t="n">
         <v>18012530</v>
       </c>
@@ -2755,15 +2785,15 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2880,9 @@
       <c r="R19" s="12" t="n">
         <v>3392398</v>
       </c>
-      <c r="S19" s="13" t="n"/>
+      <c r="S19" s="12" t="n">
+        <v>1432066</v>
+      </c>
       <c r="T19" s="12" t="n">
         <v>17965046</v>
       </c>
@@ -2872,15 +2904,15 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2999,9 @@
       <c r="R20" s="12" t="n">
         <v>3238532</v>
       </c>
-      <c r="S20" s="13" t="n"/>
+      <c r="S20" s="12" t="n">
+        <v>1335330</v>
+      </c>
       <c r="T20" s="12" t="n">
         <v>17997467</v>
       </c>
@@ -2989,15 +3023,15 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3118,9 @@
       <c r="R21" s="12" t="n">
         <v>3292249</v>
       </c>
-      <c r="S21" s="13" t="n"/>
+      <c r="S21" s="12" t="n">
+        <v>1287505</v>
+      </c>
       <c r="T21" s="12" t="n">
         <v>17984355</v>
       </c>
@@ -3106,15 +3142,15 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3347,9 @@
       <c r="R23" s="12" t="n">
         <v>3283497</v>
       </c>
-      <c r="S23" s="13" t="n"/>
+      <c r="S23" s="12" t="n">
+        <v>1353404</v>
+      </c>
       <c r="T23" s="12" t="n">
         <v>18024476</v>
       </c>
@@ -3333,15 +3371,15 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3466,9 @@
       <c r="R24" s="12" t="n">
         <v>3241020</v>
       </c>
-      <c r="S24" s="13" t="n"/>
+      <c r="S24" s="12" t="n">
+        <v>1356597</v>
+      </c>
       <c r="T24" s="12" t="n">
         <v>17965052</v>
       </c>
@@ -3450,15 +3490,15 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date</t>
+          <t>aq_hub_opponent_date+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3585,9 @@
       <c r="R25" s="12" t="n">
         <v>3258720</v>
       </c>
-      <c r="S25" s="13" t="n"/>
+      <c r="S25" s="12" t="n">
+        <v>1405765</v>
+      </c>
       <c r="T25" s="12" t="n">
         <v>18094058</v>
       </c>
@@ -3560,15 +3602,15 @@
       <c r="Y25" s="13" t="n"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3697,9 @@
       <c r="R26" s="12" t="n">
         <v>3400156</v>
       </c>
-      <c r="S26" s="13" t="n"/>
+      <c r="S26" s="12" t="n">
+        <v>1437526</v>
+      </c>
       <c r="T26" s="12" t="n">
         <v>18077238</v>
       </c>
@@ -3672,15 +3716,15 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3811,9 @@
       <c r="R27" s="12" t="n">
         <v>3291900</v>
       </c>
-      <c r="S27" s="13" t="n"/>
+      <c r="S27" s="12" t="n">
+        <v>1348726</v>
+      </c>
       <c r="T27" s="12" t="n">
         <v>18028953</v>
       </c>
@@ -3782,15 +3828,15 @@
       <c r="Y27" s="13" t="n"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3923,9 @@
       <c r="R28" s="12" t="n">
         <v>3405791</v>
       </c>
-      <c r="S28" s="13" t="n"/>
+      <c r="S28" s="12" t="n">
+        <v>1642263</v>
+      </c>
       <c r="T28" s="12" t="n">
         <v>17971632</v>
       </c>
@@ -3892,15 +3940,15 @@
       <c r="Y28" s="13" t="n"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -3987,7 +4035,9 @@
       <c r="R29" s="12" t="n">
         <v>3428106</v>
       </c>
-      <c r="S29" s="13" t="n"/>
+      <c r="S29" s="12" t="n">
+        <v>1537826</v>
+      </c>
       <c r="T29" s="12" t="n">
         <v>18147714</v>
       </c>
@@ -4002,15 +4052,15 @@
       <c r="Y29" s="13" t="n"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4147,9 @@
       <c r="R30" s="12" t="n">
         <v>3231484</v>
       </c>
-      <c r="S30" s="13" t="n"/>
+      <c r="S30" s="12" t="n">
+        <v>1287420</v>
+      </c>
       <c r="T30" s="12" t="n">
         <v>17936235</v>
       </c>
@@ -4119,15 +4171,15 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date</t>
+          <t>aq_hub_opponent_date+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4266,9 @@
       <c r="R31" s="12" t="n">
         <v>3241019</v>
       </c>
-      <c r="S31" s="13" t="n"/>
+      <c r="S31" s="12" t="n">
+        <v>1356595</v>
+      </c>
       <c r="T31" s="12" t="n">
         <v>18033318</v>
       </c>
@@ -4236,15 +4290,15 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date</t>
+          <t>aq_hub_opponent_date+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4385,9 @@
       <c r="R32" s="12" t="n">
         <v>3188803</v>
       </c>
-      <c r="S32" s="13" t="n"/>
+      <c r="S32" s="12" t="n">
+        <v>1376969</v>
+      </c>
       <c r="T32" s="12" t="n">
         <v>18033447</v>
       </c>
@@ -4344,15 +4400,15 @@
       <c r="Y32" s="13" t="n"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sg_canonical_opponent_date+sh_performer_events+tevo_performer_search</t>
+          <t>sg_canonical_opponent_date+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4495,9 @@
       <c r="R33" s="12" t="n">
         <v>3241117</v>
       </c>
-      <c r="S33" s="13" t="n"/>
+      <c r="S33" s="12" t="n">
+        <v>1368415</v>
+      </c>
       <c r="T33" s="12" t="n">
         <v>17986062</v>
       </c>
@@ -4459,15 +4517,15 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+sg_events_paciolan_link+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4612,9 @@
       <c r="R34" s="12" t="n">
         <v>3292250</v>
       </c>
-      <c r="S34" s="13" t="n"/>
+      <c r="S34" s="12" t="n">
+        <v>1287506</v>
+      </c>
       <c r="T34" s="12" t="n">
         <v>17984354</v>
       </c>
@@ -4576,15 +4636,15 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4842,9 @@
       <c r="R36" s="12" t="n">
         <v>3244108</v>
       </c>
-      <c r="S36" s="13" t="n"/>
+      <c r="S36" s="12" t="n">
+        <v>1334771</v>
+      </c>
       <c r="T36" s="12" t="n">
         <v>18035333</v>
       </c>
@@ -4804,15 +4866,15 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4961,9 @@
       <c r="R37" s="12" t="n">
         <v>3282210</v>
       </c>
-      <c r="S37" s="13" t="n"/>
+      <c r="S37" s="12" t="n">
+        <v>1377504</v>
+      </c>
       <c r="T37" s="12" t="n">
         <v>18024478</v>
       </c>
@@ -4919,15 +4983,15 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5078,9 @@
       <c r="R38" s="12" t="n">
         <v>3405808</v>
       </c>
-      <c r="S38" s="13" t="n"/>
+      <c r="S38" s="12" t="n">
+        <v>1526777</v>
+      </c>
       <c r="T38" s="12" t="n">
         <v>18176904</v>
       </c>
@@ -5029,15 +5095,15 @@
       <c r="Y38" s="13" t="n"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5190,9 @@
       <c r="R39" s="12" t="n">
         <v>3320459</v>
       </c>
-      <c r="S39" s="13" t="n"/>
+      <c r="S39" s="12" t="n">
+        <v>1642276</v>
+      </c>
       <c r="T39" s="12" t="n">
         <v>18147716</v>
       </c>
@@ -5137,15 +5205,15 @@
       <c r="Y39" s="13" t="n"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>sg_canonical_opponent_date+sg_links_sh+tevo_performer_search</t>
+          <t>sg_canonical_opponent_date+sg_links_sh+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5300,9 @@
       <c r="R40" s="12" t="n">
         <v>3290889</v>
       </c>
-      <c r="S40" s="13" t="n"/>
+      <c r="S40" s="12" t="n">
+        <v>1431973</v>
+      </c>
       <c r="T40" s="12" t="n">
         <v>17962246</v>
       </c>
@@ -5254,15 +5324,15 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5419,9 @@
       <c r="R41" s="12" t="n">
         <v>3348484</v>
       </c>
-      <c r="S41" s="13" t="n"/>
+      <c r="S41" s="12" t="n">
+        <v>1460937</v>
+      </c>
       <c r="T41" s="12" t="n">
         <v>18069009</v>
       </c>
@@ -5364,15 +5436,15 @@
       <c r="Y41" s="13" t="n"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5531,9 @@
       <c r="R42" s="12" t="n">
         <v>3352338</v>
       </c>
-      <c r="S42" s="13" t="n"/>
+      <c r="S42" s="12" t="n">
+        <v>1521529</v>
+      </c>
       <c r="T42" s="12" t="n">
         <v>18150136</v>
       </c>
@@ -5474,15 +5548,15 @@
       <c r="Y42" s="13" t="n"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5643,9 @@
       <c r="R43" s="12" t="n">
         <v>3215527</v>
       </c>
-      <c r="S43" s="13" t="n"/>
+      <c r="S43" s="12" t="n">
+        <v>1437521</v>
+      </c>
       <c r="T43" s="12" t="n">
         <v>18093824</v>
       </c>
@@ -5586,15 +5662,15 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5757,9 @@
       <c r="R44" s="12" t="n">
         <v>3289280</v>
       </c>
-      <c r="S44" s="13" t="n"/>
+      <c r="S44" s="12" t="n">
+        <v>1417051</v>
+      </c>
       <c r="T44" s="12" t="n">
         <v>17965054</v>
       </c>
@@ -5703,15 +5781,15 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date</t>
+          <t>aq_hub_opponent_date+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6200,9 @@
       <c r="R48" s="12" t="n">
         <v>3219684</v>
       </c>
-      <c r="S48" s="13" t="n"/>
+      <c r="S48" s="12" t="n">
+        <v>1368950</v>
+      </c>
       <c r="T48" s="12" t="n">
         <v>18033350</v>
       </c>
@@ -6144,15 +6224,15 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+td_events_sg_links+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+td_events_sg_links+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6315,9 @@
       <c r="R49" s="12" t="n">
         <v>3261229</v>
       </c>
-      <c r="S49" s="13" t="n"/>
+      <c r="S49" s="12" t="n">
+        <v>1405766</v>
+      </c>
       <c r="T49" s="12" t="n">
         <v>18094060</v>
       </c>
@@ -6250,15 +6332,15 @@
       <c r="Y49" s="13" t="n"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6423,9 @@
       <c r="R50" s="12" t="n">
         <v>3336180</v>
       </c>
-      <c r="S50" s="13" t="n"/>
+      <c r="S50" s="12" t="n">
+        <v>1537827</v>
+      </c>
       <c r="T50" s="12" t="n">
         <v>18147718</v>
       </c>
@@ -6356,15 +6440,15 @@
       <c r="Y50" s="13" t="n"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6535,9 @@
       <c r="R51" s="12" t="n">
         <v>3348485</v>
       </c>
-      <c r="S51" s="13" t="n"/>
+      <c r="S51" s="12" t="n">
+        <v>1460938</v>
+      </c>
       <c r="T51" s="12" t="n">
         <v>18041102</v>
       </c>
@@ -6466,15 +6552,15 @@
       <c r="Y51" s="13" t="n"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6647,9 @@
       <c r="R52" s="12" t="n">
         <v>3320999</v>
       </c>
-      <c r="S52" s="13" t="n"/>
+      <c r="S52" s="12" t="n">
+        <v>1471001</v>
+      </c>
       <c r="T52" s="12" t="n">
         <v>18068939</v>
       </c>
@@ -6581,15 +6669,15 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+sg_events_paciolan_link+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6760,9 @@
       <c r="R53" s="12" t="n">
         <v>3411023</v>
       </c>
-      <c r="S53" s="13" t="n"/>
+      <c r="S53" s="12" t="n">
+        <v>1521530</v>
+      </c>
       <c r="T53" s="12" t="n">
         <v>18150140</v>
       </c>
@@ -6687,15 +6777,15 @@
       <c r="Y53" s="13" t="n"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6868,9 @@
       <c r="R54" s="12" t="n">
         <v>3188735</v>
       </c>
-      <c r="S54" s="13" t="n"/>
+      <c r="S54" s="12" t="n">
+        <v>1376970</v>
+      </c>
       <c r="T54" s="12" t="n">
         <v>18033444</v>
       </c>
@@ -6791,15 +6883,15 @@
       <c r="Y54" s="13" t="n"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6974,9 @@
       <c r="R55" s="12" t="n">
         <v>3241048</v>
       </c>
-      <c r="S55" s="13" t="n"/>
+      <c r="S55" s="12" t="n">
+        <v>1368428</v>
+      </c>
       <c r="T55" s="12" t="n">
         <v>18024488</v>
       </c>
@@ -6904,15 +6998,15 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -6995,7 +7089,9 @@
       <c r="R56" s="12" t="n">
         <v>3156939</v>
       </c>
-      <c r="S56" s="13" t="n"/>
+      <c r="S56" s="12" t="n">
+        <v>1432067</v>
+      </c>
       <c r="T56" s="12" t="n">
         <v>17965048</v>
       </c>
@@ -7017,15 +7113,15 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7204,9 @@
       <c r="R57" s="12" t="n">
         <v>3244119</v>
       </c>
-      <c r="S57" s="13" t="n"/>
+      <c r="S57" s="12" t="n">
+        <v>1360030</v>
+      </c>
       <c r="T57" s="12" t="n">
         <v>18035439</v>
       </c>
@@ -7130,15 +7228,15 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7319,9 @@
       <c r="R58" s="12" t="n">
         <v>3402399</v>
       </c>
-      <c r="S58" s="13" t="n"/>
+      <c r="S58" s="12" t="n">
+        <v>1518652</v>
+      </c>
       <c r="T58" s="12" t="n">
         <v>18024447</v>
       </c>
@@ -7236,15 +7336,15 @@
       <c r="Y58" s="13" t="n"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7539,9 @@
       <c r="R60" s="12" t="n">
         <v>3375179</v>
       </c>
-      <c r="S60" s="13" t="n"/>
+      <c r="S60" s="12" t="n">
+        <v>1535538</v>
+      </c>
       <c r="T60" s="12" t="n">
         <v>18012992</v>
       </c>
@@ -7454,15 +7556,15 @@
       <c r="Y60" s="13" t="n"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7765,9 @@
       <c r="R62" s="12" t="n">
         <v>3305716</v>
       </c>
-      <c r="S62" s="13" t="n"/>
+      <c r="S62" s="12" t="n">
+        <v>1348728</v>
+      </c>
       <c r="T62" s="12" t="n">
         <v>18028955</v>
       </c>
@@ -7678,15 +7782,15 @@
       <c r="Y62" s="13" t="n"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7877,9 @@
       <c r="R63" s="12" t="n">
         <v>3405781</v>
       </c>
-      <c r="S63" s="13" t="n"/>
+      <c r="S63" s="12" t="n">
+        <v>1567283</v>
+      </c>
       <c r="T63" s="12" t="n">
         <v>17971634</v>
       </c>
@@ -7788,15 +7894,15 @@
       <c r="Y63" s="13" t="n"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7985,9 @@
       <c r="R64" s="12" t="n">
         <v>3411071</v>
       </c>
-      <c r="S64" s="13" t="n"/>
+      <c r="S64" s="12" t="n">
+        <v>1526778</v>
+      </c>
       <c r="T64" s="12" t="n">
         <v>18176907</v>
       </c>
@@ -7894,15 +8002,15 @@
       <c r="Y64" s="13" t="n"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -7985,7 +8093,9 @@
       <c r="R65" s="12" t="n">
         <v>3231480</v>
       </c>
-      <c r="S65" s="13" t="n"/>
+      <c r="S65" s="12" t="n">
+        <v>1335688</v>
+      </c>
       <c r="T65" s="12" t="n">
         <v>18035548</v>
       </c>
@@ -8007,15 +8117,15 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8212,9 @@
       <c r="R66" s="12" t="n">
         <v>3348463</v>
       </c>
-      <c r="S66" s="13" t="n"/>
+      <c r="S66" s="12" t="n">
+        <v>1460939</v>
+      </c>
       <c r="T66" s="12" t="n">
         <v>18069011</v>
       </c>
@@ -8117,15 +8229,15 @@
       <c r="Y66" s="13" t="n"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8320,9 @@
       <c r="R67" s="12" t="n">
         <v>3244118</v>
       </c>
-      <c r="S67" s="13" t="n"/>
+      <c r="S67" s="12" t="n">
+        <v>1360029</v>
+      </c>
       <c r="T67" s="12" t="n">
         <v>18035349</v>
       </c>
@@ -8230,15 +8344,15 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8545,9 @@
       <c r="R69" s="12" t="n">
         <v>3241111</v>
       </c>
-      <c r="S69" s="13" t="n"/>
+      <c r="S69" s="12" t="n">
+        <v>1353403</v>
+      </c>
       <c r="T69" s="12" t="n">
         <v>18024480</v>
       </c>
@@ -8453,15 +8569,15 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8660,9 @@
       <c r="R70" s="12" t="n">
         <v>3241024</v>
       </c>
-      <c r="S70" s="13" t="n"/>
+      <c r="S70" s="12" t="n">
+        <v>1356594</v>
+      </c>
       <c r="T70" s="12" t="n">
         <v>18033319</v>
       </c>
@@ -8566,15 +8684,15 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date</t>
+          <t>aq_hub_opponent_date+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8775,9 @@
       <c r="R71" s="12" t="n">
         <v>3344850</v>
       </c>
-      <c r="S71" s="13" t="n"/>
+      <c r="S71" s="12" t="n">
+        <v>1537828</v>
+      </c>
       <c r="T71" s="12" t="n">
         <v>18147720</v>
       </c>
@@ -8672,15 +8792,15 @@
       <c r="Y71" s="13" t="n"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -8881,7 +9001,9 @@
       <c r="R73" s="12" t="n">
         <v>3386314</v>
       </c>
-      <c r="S73" s="13" t="n"/>
+      <c r="S73" s="12" t="n">
+        <v>1521531</v>
+      </c>
       <c r="T73" s="12" t="n">
         <v>18150142</v>
       </c>
@@ -8896,15 +9018,15 @@
       <c r="Y73" s="13" t="n"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -8991,7 +9113,9 @@
       <c r="R74" s="12" t="n">
         <v>3214788</v>
       </c>
-      <c r="S74" s="13" t="n"/>
+      <c r="S74" s="12" t="n">
+        <v>1377055</v>
+      </c>
       <c r="T74" s="12" t="n">
         <v>18094062</v>
       </c>
@@ -9006,15 +9130,15 @@
       <c r="Y74" s="13" t="n"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -9097,7 +9221,9 @@
       <c r="R75" s="12" t="n">
         <v>3241249</v>
       </c>
-      <c r="S75" s="13" t="n"/>
+      <c r="S75" s="12" t="n">
+        <v>1335326</v>
+      </c>
       <c r="T75" s="12" t="n">
         <v>18033437</v>
       </c>
@@ -9119,15 +9245,15 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9556,9 @@
         </is>
       </c>
       <c r="R78" s="13" t="n"/>
-      <c r="S78" s="13" t="n"/>
+      <c r="S78" s="12" t="n">
+        <v>1722873</v>
+      </c>
       <c r="T78" s="12" t="n">
         <v>18012388</v>
       </c>
@@ -9445,15 +9573,15 @@
       <c r="Y78" s="13" t="n"/>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub, Vivid Seats</t>
+          <t>GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -9536,7 +9664,9 @@
       <c r="R79" s="12" t="n">
         <v>3188644</v>
       </c>
-      <c r="S79" s="13" t="n"/>
+      <c r="S79" s="12" t="n">
+        <v>1368947</v>
+      </c>
       <c r="T79" s="12" t="n">
         <v>18033352</v>
       </c>
@@ -9558,15 +9688,15 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -9653,7 +9783,9 @@
       <c r="R80" s="12" t="n">
         <v>3305714</v>
       </c>
-      <c r="S80" s="13" t="n"/>
+      <c r="S80" s="12" t="n">
+        <v>1348729</v>
+      </c>
       <c r="T80" s="12" t="n">
         <v>18028959</v>
       </c>
@@ -9666,15 +9798,15 @@
       <c r="Y80" s="13" t="n"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9893,9 @@
       <c r="R81" s="12" t="n">
         <v>3321000</v>
       </c>
-      <c r="S81" s="13" t="n"/>
+      <c r="S81" s="12" t="n">
+        <v>1471002</v>
+      </c>
       <c r="T81" s="12" t="n">
         <v>18068940</v>
       </c>
@@ -9776,15 +9910,15 @@
       <c r="Y81" s="13" t="n"/>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -9867,7 +10001,9 @@
       <c r="R82" s="12" t="n">
         <v>3188624</v>
       </c>
-      <c r="S82" s="13" t="n"/>
+      <c r="S82" s="12" t="n">
+        <v>1377028</v>
+      </c>
       <c r="T82" s="12" t="n">
         <v>18033280</v>
       </c>
@@ -9889,15 +10025,15 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -9980,7 +10116,9 @@
       <c r="R83" s="12" t="n">
         <v>3243895</v>
       </c>
-      <c r="S83" s="13" t="n"/>
+      <c r="S83" s="12" t="n">
+        <v>1367464</v>
+      </c>
       <c r="T83" s="12" t="n">
         <v>18024449</v>
       </c>
@@ -9995,15 +10133,15 @@
       <c r="Y83" s="13" t="n"/>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10224,9 @@
       <c r="R84" s="12" t="n">
         <v>3241108</v>
       </c>
-      <c r="S84" s="13" t="n"/>
+      <c r="S84" s="12" t="n">
+        <v>1353400</v>
+      </c>
       <c r="T84" s="12" t="n">
         <v>18024482</v>
       </c>
@@ -10108,15 +10248,15 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10343,9 @@
       <c r="R85" s="12" t="n">
         <v>3375315</v>
       </c>
-      <c r="S85" s="13" t="n"/>
+      <c r="S85" s="12" t="n">
+        <v>1535539</v>
+      </c>
       <c r="T85" s="12" t="n">
         <v>18012994</v>
       </c>
@@ -10216,15 +10358,15 @@
       <c r="Y85" s="13" t="n"/>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -10307,7 +10449,9 @@
       <c r="R86" s="12" t="n">
         <v>3188658</v>
       </c>
-      <c r="S86" s="13" t="n"/>
+      <c r="S86" s="12" t="n">
+        <v>1368946</v>
+      </c>
       <c r="T86" s="12" t="n">
         <v>18033351</v>
       </c>
@@ -10327,15 +10471,15 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10562,9 @@
       <c r="R87" s="12" t="n">
         <v>3215551</v>
       </c>
-      <c r="S87" s="13" t="n"/>
+      <c r="S87" s="12" t="n">
+        <v>1377058</v>
+      </c>
       <c r="T87" s="12" t="n">
         <v>18094064</v>
       </c>
@@ -10433,15 +10579,15 @@
       <c r="Y87" s="13" t="n"/>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -10528,7 +10674,9 @@
       <c r="R88" s="12" t="n">
         <v>3405793</v>
       </c>
-      <c r="S88" s="13" t="n"/>
+      <c r="S88" s="12" t="n">
+        <v>1567284</v>
+      </c>
       <c r="T88" s="12" t="n">
         <v>17971636</v>
       </c>
@@ -10543,15 +10691,15 @@
       <c r="Y88" s="13" t="n"/>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10782,9 @@
       <c r="R89" s="12" t="n">
         <v>3344854</v>
       </c>
-      <c r="S89" s="13" t="n"/>
+      <c r="S89" s="12" t="n">
+        <v>1537829</v>
+      </c>
       <c r="T89" s="12" t="n">
         <v>18147786</v>
       </c>
@@ -10649,15 +10799,15 @@
       <c r="Y89" s="13" t="n"/>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10890,9 @@
       <c r="R90" s="12" t="n">
         <v>3231483</v>
       </c>
-      <c r="S90" s="13" t="n"/>
+      <c r="S90" s="12" t="n">
+        <v>1431978</v>
+      </c>
       <c r="T90" s="12" t="n">
         <v>18035549</v>
       </c>
@@ -10762,15 +10914,15 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -10857,7 +11009,9 @@
       <c r="R91" s="12" t="n">
         <v>3348487</v>
       </c>
-      <c r="S91" s="13" t="n"/>
+      <c r="S91" s="12" t="n">
+        <v>1460940</v>
+      </c>
       <c r="T91" s="12" t="n">
         <v>18069013</v>
       </c>
@@ -10872,15 +11026,15 @@
       <c r="Y91" s="13" t="n"/>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -10963,7 +11117,9 @@
       <c r="R92" s="12" t="n">
         <v>3289430</v>
       </c>
-      <c r="S92" s="13" t="n"/>
+      <c r="S92" s="12" t="n">
+        <v>1376971</v>
+      </c>
       <c r="T92" s="12" t="n">
         <v>18033446</v>
       </c>
@@ -10976,15 +11132,15 @@
       <c r="Y92" s="13" t="n"/>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11223,9 @@
       <c r="R93" s="12" t="n">
         <v>3241049</v>
       </c>
-      <c r="S93" s="13" t="n"/>
+      <c r="S93" s="12" t="n">
+        <v>1368430</v>
+      </c>
       <c r="T93" s="12" t="n">
         <v>18024492</v>
       </c>
@@ -11089,15 +11247,15 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11338,9 @@
       <c r="R94" s="12" t="n">
         <v>3188622</v>
       </c>
-      <c r="S94" s="13" t="n"/>
+      <c r="S94" s="12" t="n">
+        <v>1377026</v>
+      </c>
       <c r="T94" s="12" t="n">
         <v>18033281</v>
       </c>
@@ -11202,15 +11362,15 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11453,9 @@
       <c r="R95" s="12" t="n">
         <v>3231495</v>
       </c>
-      <c r="S95" s="13" t="n"/>
+      <c r="S95" s="12" t="n">
+        <v>1368476</v>
+      </c>
       <c r="T95" s="12" t="n">
         <v>18035437</v>
       </c>
@@ -11315,15 +11477,15 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11568,9 @@
       <c r="R96" s="12" t="n">
         <v>3244121</v>
       </c>
-      <c r="S96" s="13" t="n"/>
+      <c r="S96" s="12" t="n">
+        <v>1360032</v>
+      </c>
       <c r="T96" s="12" t="n">
         <v>18035447</v>
       </c>
@@ -11428,15 +11592,15 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -11519,7 +11683,9 @@
       <c r="R97" s="12" t="n">
         <v>3241023</v>
       </c>
-      <c r="S97" s="13" t="n"/>
+      <c r="S97" s="12" t="n">
+        <v>1356593</v>
+      </c>
       <c r="T97" s="12" t="n">
         <v>18033320</v>
       </c>
@@ -11541,15 +11707,15 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date</t>
+          <t>aq_hub_opponent_date+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11800,9 @@
         </is>
       </c>
       <c r="R98" s="13" t="n"/>
-      <c r="S98" s="13" t="n"/>
+      <c r="S98" s="12" t="n">
+        <v>1722874</v>
+      </c>
       <c r="T98" s="12" t="n">
         <v>18012390</v>
       </c>
@@ -11647,15 +11815,15 @@
       <c r="Y98" s="13" t="n"/>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub</t>
+          <t>GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -11742,7 +11910,9 @@
       <c r="R99" s="12" t="n">
         <v>3374962</v>
       </c>
-      <c r="S99" s="13" t="n"/>
+      <c r="S99" s="12" t="n">
+        <v>1535540</v>
+      </c>
       <c r="T99" s="12" t="n">
         <v>18012996</v>
       </c>
@@ -11755,15 +11925,15 @@
       <c r="Y99" s="13" t="n"/>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -11850,7 +12020,9 @@
       <c r="R100" s="12" t="n">
         <v>3405796</v>
       </c>
-      <c r="S100" s="13" t="n"/>
+      <c r="S100" s="12" t="n">
+        <v>1567285</v>
+      </c>
       <c r="T100" s="12" t="n">
         <v>17971638</v>
       </c>
@@ -11865,15 +12037,15 @@
       <c r="Y100" s="13" t="n"/>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -11956,7 +12128,9 @@
       <c r="R101" s="12" t="n">
         <v>3409552</v>
       </c>
-      <c r="S101" s="13" t="n"/>
+      <c r="S101" s="12" t="n">
+        <v>1526779</v>
+      </c>
       <c r="T101" s="12" t="n">
         <v>18176906</v>
       </c>
@@ -11971,15 +12145,15 @@
       <c r="Y101" s="13" t="n"/>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12240,9 @@
       <c r="R102" s="12" t="n">
         <v>3372308</v>
       </c>
-      <c r="S102" s="13" t="n"/>
+      <c r="S102" s="12" t="n">
+        <v>1558276</v>
+      </c>
       <c r="T102" s="12" t="n">
         <v>18147690</v>
       </c>
@@ -12081,15 +12257,15 @@
       <c r="Y102" s="13" t="n"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12352,9 @@
       <c r="R103" s="12" t="n">
         <v>3250475</v>
       </c>
-      <c r="S103" s="13" t="n"/>
+      <c r="S103" s="12" t="n">
+        <v>1644492</v>
+      </c>
       <c r="T103" s="12" t="n">
         <v>18033353</v>
       </c>
@@ -12198,15 +12376,15 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12471,9 @@
       <c r="R104" s="12" t="n">
         <v>3320998</v>
       </c>
-      <c r="S104" s="13" t="n"/>
+      <c r="S104" s="12" t="n">
+        <v>1471003</v>
+      </c>
       <c r="T104" s="12" t="n">
         <v>18068941</v>
       </c>
@@ -12308,15 +12488,15 @@
       <c r="Y104" s="13" t="n"/>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -12399,7 +12579,9 @@
       <c r="R105" s="12" t="n">
         <v>3403984</v>
       </c>
-      <c r="S105" s="13" t="n"/>
+      <c r="S105" s="12" t="n">
+        <v>1521532</v>
+      </c>
       <c r="T105" s="12" t="n">
         <v>18150144</v>
       </c>
@@ -12414,15 +12596,15 @@
       <c r="Y105" s="13" t="n"/>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -12611,7 +12793,9 @@
       <c r="R107" s="12" t="n">
         <v>3243896</v>
       </c>
-      <c r="S107" s="13" t="n"/>
+      <c r="S107" s="12" t="n">
+        <v>1367465</v>
+      </c>
       <c r="T107" s="12" t="n">
         <v>18024451</v>
       </c>
@@ -12626,15 +12810,15 @@
       <c r="Y107" s="13" t="n"/>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12901,9 @@
       <c r="R108" s="12" t="n">
         <v>3216347</v>
       </c>
-      <c r="S108" s="13" t="n"/>
+      <c r="S108" s="12" t="n">
+        <v>1377057</v>
+      </c>
       <c r="T108" s="12" t="n">
         <v>18094066</v>
       </c>
@@ -12732,15 +12918,15 @@
       <c r="Y108" s="13" t="n"/>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -12823,7 +13009,9 @@
       <c r="R109" s="12" t="n">
         <v>3215142</v>
       </c>
-      <c r="S109" s="13" t="n"/>
+      <c r="S109" s="12" t="n">
+        <v>1437525</v>
+      </c>
       <c r="T109" s="12" t="n">
         <v>18093828</v>
       </c>
@@ -12840,15 +13028,15 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -12935,7 +13123,9 @@
       <c r="R110" s="12" t="n">
         <v>3305718</v>
       </c>
-      <c r="S110" s="13" t="n"/>
+      <c r="S110" s="12" t="n">
+        <v>1348727</v>
+      </c>
       <c r="T110" s="12" t="n">
         <v>18028957</v>
       </c>
@@ -12948,15 +13138,15 @@
       <c r="Y110" s="13" t="n"/>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -13039,7 +13229,9 @@
       <c r="R111" s="12" t="n">
         <v>3231482</v>
       </c>
-      <c r="S111" s="13" t="n"/>
+      <c r="S111" s="12" t="n">
+        <v>1335690</v>
+      </c>
       <c r="T111" s="12" t="n">
         <v>18035551</v>
       </c>
@@ -13061,15 +13253,15 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13348,9 @@
       <c r="R112" s="12" t="n">
         <v>3372311</v>
       </c>
-      <c r="S112" s="13" t="n"/>
+      <c r="S112" s="12" t="n">
+        <v>1558277</v>
+      </c>
       <c r="T112" s="12" t="n">
         <v>18147692</v>
       </c>
@@ -13171,15 +13365,15 @@
       <c r="Y112" s="13" t="n"/>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -13262,7 +13456,9 @@
       <c r="R113" s="12" t="n">
         <v>3344846</v>
       </c>
-      <c r="S113" s="13" t="n"/>
+      <c r="S113" s="12" t="n">
+        <v>1537830</v>
+      </c>
       <c r="T113" s="12" t="n">
         <v>18147788</v>
       </c>
@@ -13277,15 +13473,15 @@
       <c r="Y113" s="13" t="n"/>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -13372,7 +13568,9 @@
       <c r="R114" s="12" t="n">
         <v>3241021</v>
       </c>
-      <c r="S114" s="13" t="n"/>
+      <c r="S114" s="12" t="n">
+        <v>1356592</v>
+      </c>
       <c r="T114" s="12" t="n">
         <v>18033321</v>
       </c>
@@ -13394,15 +13592,15 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date</t>
+          <t>aq_hub_opponent_date+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13683,9 @@
       <c r="R115" s="12" t="n">
         <v>3411022</v>
       </c>
-      <c r="S115" s="13" t="n"/>
+      <c r="S115" s="12" t="n">
+        <v>1521533</v>
+      </c>
       <c r="T115" s="12" t="n">
         <v>18150146</v>
       </c>
@@ -13500,15 +13700,15 @@
       <c r="Y115" s="13" t="n"/>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -13591,7 +13791,9 @@
       <c r="R116" s="12" t="n">
         <v>3188699</v>
       </c>
-      <c r="S116" s="13" t="n"/>
+      <c r="S116" s="12" t="n">
+        <v>1377025</v>
+      </c>
       <c r="T116" s="12" t="n">
         <v>18033283</v>
       </c>
@@ -13613,15 +13815,15 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13906,9 @@
       <c r="R117" s="12" t="n">
         <v>3250476</v>
       </c>
-      <c r="S117" s="13" t="n"/>
+      <c r="S117" s="12" t="n">
+        <v>1394318</v>
+      </c>
       <c r="T117" s="12" t="n">
         <v>18033438</v>
       </c>
@@ -13726,15 +13930,15 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -13927,7 +14131,9 @@
       <c r="R119" s="12" t="n">
         <v>3241110</v>
       </c>
-      <c r="S119" s="13" t="n"/>
+      <c r="S119" s="12" t="n">
+        <v>1353401</v>
+      </c>
       <c r="T119" s="12" t="n">
         <v>18024484</v>
       </c>
@@ -13949,15 +14155,15 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB119" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14246,9 @@
       <c r="R120" s="12" t="n">
         <v>3188627</v>
       </c>
-      <c r="S120" s="13" t="n"/>
+      <c r="S120" s="12" t="n">
+        <v>1368948</v>
+      </c>
       <c r="T120" s="12" t="n">
         <v>18033360</v>
       </c>
@@ -14062,15 +14270,15 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -14157,7 +14365,9 @@
       <c r="R121" s="12" t="n">
         <v>3305713</v>
       </c>
-      <c r="S121" s="13" t="n"/>
+      <c r="S121" s="12" t="n">
+        <v>1348730</v>
+      </c>
       <c r="T121" s="12" t="n">
         <v>18028961</v>
       </c>
@@ -14172,15 +14382,15 @@
       <c r="Y121" s="13" t="n"/>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -14267,7 +14477,9 @@
       <c r="R122" s="12" t="n">
         <v>3405784</v>
       </c>
-      <c r="S122" s="13" t="n"/>
+      <c r="S122" s="12" t="n">
+        <v>1642797</v>
+      </c>
       <c r="T122" s="12" t="n">
         <v>17971640</v>
       </c>
@@ -14282,15 +14494,15 @@
       <c r="Y122" s="13" t="n"/>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -14373,7 +14585,9 @@
       <c r="R123" s="12" t="n">
         <v>3411045</v>
       </c>
-      <c r="S123" s="13" t="n"/>
+      <c r="S123" s="12" t="n">
+        <v>1526780</v>
+      </c>
       <c r="T123" s="12" t="n">
         <v>18176909</v>
       </c>
@@ -14388,15 +14602,15 @@
       <c r="Y123" s="13" t="n"/>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14697,9 @@
       <c r="R124" s="12" t="n">
         <v>3321004</v>
       </c>
-      <c r="S124" s="13" t="n"/>
+      <c r="S124" s="12" t="n">
+        <v>1460941</v>
+      </c>
       <c r="T124" s="12" t="n">
         <v>18069010</v>
       </c>
@@ -14498,15 +14714,15 @@
       <c r="Y124" s="13" t="n"/>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -14593,7 +14809,9 @@
       <c r="R125" s="12" t="n">
         <v>3374422</v>
       </c>
-      <c r="S125" s="13" t="n"/>
+      <c r="S125" s="12" t="n">
+        <v>1535541</v>
+      </c>
       <c r="T125" s="12" t="n">
         <v>18012998</v>
       </c>
@@ -14606,15 +14824,15 @@
       <c r="Y125" s="13" t="n"/>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14919,9 @@
       <c r="R126" s="12" t="n">
         <v>3344853</v>
       </c>
-      <c r="S126" s="13" t="n"/>
+      <c r="S126" s="12" t="n">
+        <v>1537831</v>
+      </c>
       <c r="T126" s="12" t="n">
         <v>18147790</v>
       </c>
@@ -14716,15 +14936,15 @@
       <c r="Y126" s="13" t="n"/>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -14807,7 +15027,9 @@
       <c r="R127" s="12" t="n">
         <v>3244120</v>
       </c>
-      <c r="S127" s="13" t="n"/>
+      <c r="S127" s="12" t="n">
+        <v>1360031</v>
+      </c>
       <c r="T127" s="12" t="n">
         <v>18035351</v>
       </c>
@@ -14829,15 +15051,15 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -14920,7 +15142,9 @@
       <c r="R128" s="12" t="n">
         <v>3242970</v>
       </c>
-      <c r="S128" s="13" t="n"/>
+      <c r="S128" s="12" t="n">
+        <v>1367463</v>
+      </c>
       <c r="T128" s="12" t="n">
         <v>18024453</v>
       </c>
@@ -14933,15 +15157,15 @@
       <c r="Y128" s="13" t="n"/>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15248,9 @@
       <c r="R129" s="12" t="n">
         <v>3244107</v>
       </c>
-      <c r="S129" s="13" t="n"/>
+      <c r="S129" s="12" t="n">
+        <v>1334768</v>
+      </c>
       <c r="T129" s="12" t="n">
         <v>18035343</v>
       </c>
@@ -15046,15 +15272,15 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -15249,7 +15475,9 @@
         </is>
       </c>
       <c r="R131" s="13" t="n"/>
-      <c r="S131" s="13" t="n"/>
+      <c r="S131" s="12" t="n">
+        <v>1722875</v>
+      </c>
       <c r="T131" s="12" t="n">
         <v>18012392</v>
       </c>
@@ -15262,15 +15490,15 @@
       <c r="Y131" s="13" t="n"/>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>SeatGeek, StubHub</t>
+          <t>GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link</t>
+          <t>sg_events_paciolan_link+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15581,9 @@
       <c r="R132" s="12" t="n">
         <v>3214869</v>
       </c>
-      <c r="S132" s="13" t="n"/>
+      <c r="S132" s="12" t="n">
+        <v>1377056</v>
+      </c>
       <c r="T132" s="12" t="n">
         <v>18094071</v>
       </c>
@@ -15368,15 +15598,15 @@
       <c r="Y132" s="13" t="n"/>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB132" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15689,9 @@
       <c r="R133" s="12" t="n">
         <v>3214107</v>
       </c>
-      <c r="S133" s="13" t="n"/>
+      <c r="S133" s="12" t="n">
+        <v>1437523</v>
+      </c>
       <c r="T133" s="12" t="n">
         <v>18093830</v>
       </c>
@@ -15476,15 +15708,15 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB133" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>sg_events_venue_datetime+tevo_performer_search</t>
+          <t>sg_events_venue_datetime+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -15571,7 +15803,9 @@
       <c r="R134" s="12" t="n">
         <v>3305712</v>
       </c>
-      <c r="S134" s="13" t="n"/>
+      <c r="S134" s="12" t="n">
+        <v>1449864</v>
+      </c>
       <c r="T134" s="12" t="n">
         <v>18028963</v>
       </c>
@@ -15584,15 +15818,15 @@
       <c r="Y134" s="13" t="n"/>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15913,9 @@
       <c r="R135" s="12" t="n">
         <v>3343770</v>
       </c>
-      <c r="S135" s="13" t="n"/>
+      <c r="S135" s="12" t="n">
+        <v>1547670</v>
+      </c>
       <c r="T135" s="12" t="n">
         <v>18176908</v>
       </c>
@@ -15694,15 +15930,15 @@
       <c r="Y135" s="13" t="n"/>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB135" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -15785,7 +16021,9 @@
       <c r="R136" s="12" t="n">
         <v>3348490</v>
       </c>
-      <c r="S136" s="13" t="n"/>
+      <c r="S136" s="12" t="n">
+        <v>1509672</v>
+      </c>
       <c r="T136" s="12" t="n">
         <v>18068942</v>
       </c>
@@ -15798,15 +16036,15 @@
       <c r="Y136" s="13" t="n"/>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>opponent_tbd+sg_events_paciolan_link+tevo_performer_search</t>
+          <t>opponent_tbd+sg_events_paciolan_link+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -15889,7 +16127,9 @@
       <c r="R137" s="12" t="n">
         <v>3188751</v>
       </c>
-      <c r="S137" s="13" t="n"/>
+      <c r="S137" s="12" t="n">
+        <v>1376968</v>
+      </c>
       <c r="T137" s="12" t="n">
         <v>18033445</v>
       </c>
@@ -15902,15 +16142,15 @@
       <c r="Y137" s="13" t="n"/>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16348,9 @@
       <c r="R139" s="12" t="n">
         <v>3237288</v>
       </c>
-      <c r="S139" s="13" t="n"/>
+      <c r="S139" s="12" t="n">
+        <v>1335332</v>
+      </c>
       <c r="T139" s="12" t="n">
         <v>18033439</v>
       </c>
@@ -16128,15 +16370,15 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB139" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16461,9 @@
       <c r="R140" s="12" t="n">
         <v>3241109</v>
       </c>
-      <c r="S140" s="13" t="n"/>
+      <c r="S140" s="12" t="n">
+        <v>1353402</v>
+      </c>
       <c r="T140" s="12" t="n">
         <v>18024486</v>
       </c>
@@ -16241,15 +16485,15 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats, Ticketmaster</t>
         </is>
       </c>
       <c r="AB140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>aq_hub_opponent_date+tevo_performer_search</t>
+          <t>aq_hub_opponent_date+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -16332,7 +16576,9 @@
       <c r="R141" s="12" t="n">
         <v>3434001</v>
       </c>
-      <c r="S141" s="13" t="n"/>
+      <c r="S141" s="12" t="n">
+        <v>1509669</v>
+      </c>
       <c r="T141" s="12" t="n">
         <v>18069012</v>
       </c>
@@ -16345,15 +16591,15 @@
       <c r="Y141" s="13" t="n"/>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub</t>
         </is>
       </c>
       <c r="AB141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>opponent_tbd_flex+sg_events_paciolan_link+sh_performer_events+tevo_performer_search</t>
+          <t>opponent_tbd_flex+sg_events_paciolan_link+sh_performer_events+tevo_performer_search+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -16537,7 +16783,9 @@
       <c r="R143" s="12" t="n">
         <v>3026271</v>
       </c>
-      <c r="S143" s="13" t="n"/>
+      <c r="S143" s="12" t="n">
+        <v>1356495</v>
+      </c>
       <c r="T143" s="12" t="n">
         <v>17565134</v>
       </c>
@@ -16557,15 +16805,15 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB143" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>day_level_zone_product</t>
+          <t>day_level_zone_product+gt_day_level_zone_product</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16888,9 @@
       <c r="R144" s="12" t="n">
         <v>3026271</v>
       </c>
-      <c r="S144" s="13" t="n"/>
+      <c r="S144" s="12" t="n">
+        <v>1356495</v>
+      </c>
       <c r="T144" s="12" t="n">
         <v>17565134</v>
       </c>
@@ -16660,15 +16910,15 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>day_level_zone_product</t>
+          <t>day_level_zone_product+gt_day_level_zone_product</t>
         </is>
       </c>
     </row>
@@ -16743,7 +16993,9 @@
       <c r="R145" s="12" t="n">
         <v>3026272</v>
       </c>
-      <c r="S145" s="13" t="n"/>
+      <c r="S145" s="12" t="n">
+        <v>1356496</v>
+      </c>
       <c r="T145" s="12" t="n">
         <v>17565136</v>
       </c>
@@ -16763,15 +17015,15 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB145" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>day_level_zone_product</t>
+          <t>day_level_zone_product+gt_day_level_zone_product</t>
         </is>
       </c>
     </row>
@@ -16846,7 +17098,9 @@
       <c r="R146" s="12" t="n">
         <v>3017608</v>
       </c>
-      <c r="S146" s="13" t="n"/>
+      <c r="S146" s="12" t="n">
+        <v>1057019</v>
+      </c>
       <c r="T146" s="12" t="n">
         <v>17565120</v>
       </c>
@@ -16866,15 +17120,15 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>Ticket Evolution, SeatGeek, StubHub, Vivid Seats</t>
+          <t>Ticket Evolution, GoTickets, SeatGeek, StubHub, Vivid Seats</t>
         </is>
       </c>
       <c r="AB146" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>venue_date_name_exact</t>
+          <t>venue_date_name_exact+gt_catalog_venue_date</t>
         </is>
       </c>
     </row>
@@ -16944,13 +17198,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="C3" t="n">
         <v>145</v>
       </c>
       <c r="D3" t="n">
-        <v>11.7</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="4">
@@ -17070,7 +17324,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C12" t="n">
         <v>145</v>
@@ -17084,7 +17338,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.29</v>
+        <v>5.17</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
